--- a/TMS Database mapping.xlsx
+++ b/TMS Database mapping.xlsx
@@ -5,43 +5,31 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\paulandrie.coronel\Desktop\andrie\laravel\practice\tms query\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\paulandrie.coronel.FISHERMALL\Desktop\db mapping python\tms query\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7635" firstSheet="1" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7635" firstSheet="4" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="lists of all tables" sheetId="1" r:id="rId1"/>
     <sheet name="Dropdowns" sheetId="5" r:id="rId2"/>
     <sheet name="new tms" sheetId="3" r:id="rId3"/>
     <sheet name="old tms" sheetId="2" r:id="rId4"/>
-    <sheet name="old ebm" sheetId="4" r:id="rId5"/>
+    <sheet name="old ebm" sheetId="14" r:id="rId5"/>
     <sheet name="Progress" sheetId="6" r:id="rId6"/>
     <sheet name="OPS" sheetId="7" r:id="rId7"/>
     <sheet name="Acct" sheetId="8" r:id="rId8"/>
     <sheet name="Sheet1" sheetId="9" r:id="rId9"/>
     <sheet name="Sheet4" sheetId="12" r:id="rId10"/>
+    <sheet name="ebm" sheetId="13" r:id="rId11"/>
   </sheets>
   <calcPr calcId="152511"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11458" uniqueCount="2191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11520" uniqueCount="2206">
   <si>
     <t>new TMS</t>
   </si>
@@ -6789,12 +6777,57 @@
   <si>
     <t>seeder</t>
   </si>
+  <si>
+    <t>doc_type</t>
+  </si>
+  <si>
+    <t>eventclass</t>
+  </si>
+  <si>
+    <t>mode_refund_dsc</t>
+  </si>
+  <si>
+    <t>payment_type_dsc</t>
+  </si>
+  <si>
+    <t>statusdsc</t>
+  </si>
+  <si>
+    <t>rank</t>
+  </si>
+  <si>
+    <t>taxcde</t>
+  </si>
+  <si>
+    <t>present_id</t>
+  </si>
+  <si>
+    <t>eventsched_id</t>
+  </si>
+  <si>
+    <t>lessee_repto</t>
+  </si>
+  <si>
+    <t>time_toto</t>
+  </si>
+  <si>
+    <t>oc_id</t>
+  </si>
+  <si>
+    <t>total_bal</t>
+  </si>
+  <si>
+    <t>clientoffer_id</t>
+  </si>
+  <si>
+    <t>lessor_position</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6818,8 +6851,16 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6871,6 +6912,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -6953,7 +7000,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -7053,6 +7100,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7062,13 +7118,6 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.39997558519241921"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7111,6 +7160,13 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="8" tint="0.39997558519241921"/>
         </patternFill>
       </fill>
     </dxf>
@@ -9611,27 +9667,27 @@
     <sortCondition ref="B116"/>
   </sortState>
   <conditionalFormatting sqref="J9">
-    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
+      <formula>"OLD EBM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"OLD TMS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="5" operator="equal">
-      <formula>"OLD EBM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J12">
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+      <formula>"OLD EBM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
       <formula>"OLD TMS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
-      <formula>"OLD EBM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J19">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+      <formula>"OLD EBM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"OLD TMS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
-      <formula>"OLD EBM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1 J3:J8 J10:J11 J13:J18 J20:J30 J41:J43 J46:J1048576 J36:J39">
@@ -10392,6 +10448,15 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -55902,5785 +55967,2331 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:BL68"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <dimension ref="A2:BK69"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="11.85546875" customWidth="1"/>
-    <col min="7" max="7" width="21.85546875" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="11.85546875" customWidth="1"/>
-    <col min="12" max="12" width="14" customWidth="1"/>
-    <col min="13" max="13" width="15.28515625" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" customWidth="1"/>
-    <col min="16" max="16" width="28.140625" customWidth="1"/>
-    <col min="17" max="17" width="24.28515625" customWidth="1"/>
-    <col min="18" max="18" width="22.5703125" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" customWidth="1"/>
-    <col min="20" max="20" width="13.7109375" customWidth="1"/>
-    <col min="21" max="21" width="21.140625" customWidth="1"/>
-    <col min="22" max="22" width="13.140625" customWidth="1"/>
-    <col min="23" max="24" width="11.85546875" customWidth="1"/>
-    <col min="25" max="25" width="29.85546875" customWidth="1"/>
-    <col min="26" max="26" width="20.42578125" customWidth="1"/>
-    <col min="27" max="27" width="25.5703125" customWidth="1"/>
-    <col min="28" max="28" width="29.7109375" customWidth="1"/>
-    <col min="29" max="29" width="29.85546875" customWidth="1"/>
-    <col min="30" max="30" width="20.28515625" customWidth="1"/>
-    <col min="31" max="31" width="16.28515625" customWidth="1"/>
-    <col min="32" max="32" width="28.5703125" customWidth="1"/>
-    <col min="33" max="33" width="16.7109375" customWidth="1"/>
-    <col min="34" max="34" width="21.140625" customWidth="1"/>
-    <col min="35" max="35" width="18.140625" customWidth="1"/>
-    <col min="36" max="36" width="17.5703125" customWidth="1"/>
-    <col min="37" max="37" width="16.28515625" customWidth="1"/>
-    <col min="38" max="38" width="19" customWidth="1"/>
-    <col min="39" max="39" width="16.5703125" customWidth="1"/>
-    <col min="40" max="40" width="19.85546875" customWidth="1"/>
-    <col min="41" max="41" width="16.28515625" customWidth="1"/>
-    <col min="42" max="42" width="22.140625" customWidth="1"/>
-    <col min="43" max="43" width="17" customWidth="1"/>
-    <col min="44" max="44" width="26.7109375" customWidth="1"/>
-    <col min="45" max="45" width="19.42578125" customWidth="1"/>
-    <col min="46" max="46" width="17.42578125" customWidth="1"/>
-    <col min="47" max="47" width="20.28515625" customWidth="1"/>
-    <col min="48" max="48" width="13.140625" customWidth="1"/>
-    <col min="49" max="49" width="17" customWidth="1"/>
-    <col min="50" max="50" width="21.7109375" customWidth="1"/>
-    <col min="51" max="51" width="19" customWidth="1"/>
-    <col min="52" max="52" width="14.28515625" customWidth="1"/>
-    <col min="53" max="53" width="12.7109375" customWidth="1"/>
-    <col min="54" max="54" width="21.7109375" customWidth="1"/>
-    <col min="55" max="55" width="17.5703125" customWidth="1"/>
-    <col min="56" max="56" width="15.42578125" customWidth="1"/>
-    <col min="57" max="57" width="20.7109375" customWidth="1"/>
-    <col min="58" max="58" width="17.85546875" customWidth="1"/>
-    <col min="59" max="59" width="9.85546875" customWidth="1"/>
-    <col min="60" max="60" width="11.42578125" customWidth="1"/>
-    <col min="61" max="61" width="18.85546875" customWidth="1"/>
-    <col min="62" max="62" width="23.85546875" customWidth="1"/>
-    <col min="63" max="63" width="17.5703125" customWidth="1"/>
-    <col min="64" max="64" width="24.5703125" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" customWidth="1"/>
+    <col min="10" max="10" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="19" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="22.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:64" s="26" customFormat="1">
-      <c r="A2" s="22"/>
-      <c r="B2" s="22" t="s">
+    <row r="2" spans="1:63" s="33" customFormat="1">
+      <c r="A2" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="B2" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="C2" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="D2" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="E2" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="22" t="s">
+      <c r="F2" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="H2" s="22" t="s">
+      <c r="G2" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="I2" s="22" t="s">
+      <c r="H2" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="J2" s="22" t="s">
+      <c r="I2" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="K2" s="22" t="s">
+      <c r="J2" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="L2" s="22" t="s">
+      <c r="K2" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="M2" s="22" t="s">
+      <c r="L2" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="N2" s="22" t="s">
+      <c r="M2" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="O2" s="22" t="s">
+      <c r="N2" s="33" t="s">
         <v>71</v>
       </c>
-      <c r="P2" s="22" t="s">
+      <c r="O2" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="Q2" s="22" t="s">
+      <c r="P2" s="34" t="s">
         <v>78</v>
       </c>
-      <c r="R2" s="22" t="s">
+      <c r="Q2" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="S2" s="22" t="s">
+      <c r="R2" s="33" t="s">
         <v>87</v>
       </c>
-      <c r="T2" s="22" t="s">
+      <c r="S2" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="U2" s="22" t="s">
+      <c r="T2" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="V2" s="22" t="s">
+      <c r="U2" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="W2" s="22" t="s">
+      <c r="V2" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="X2" s="22" t="s">
+      <c r="W2" s="33" t="s">
         <v>100</v>
       </c>
-      <c r="Y2" s="22" t="s">
+      <c r="X2" s="35" t="s">
         <v>103</v>
       </c>
-      <c r="Z2" s="22" t="s">
+      <c r="Y2" s="35" t="s">
         <v>105</v>
       </c>
-      <c r="AA2" s="22" t="s">
+      <c r="Z2" s="35" t="s">
         <v>108</v>
       </c>
-      <c r="AB2" s="22" t="s">
+      <c r="AA2" s="35" t="s">
         <v>113</v>
       </c>
-      <c r="AC2" s="22" t="s">
+      <c r="AB2" s="35" t="s">
         <v>117</v>
       </c>
-      <c r="AD2" s="22" t="s">
+      <c r="AC2" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="AE2" s="22" t="s">
+      <c r="AD2" s="33" t="s">
         <v>125</v>
       </c>
-      <c r="AF2" s="22" t="s">
+      <c r="AE2" s="33" t="s">
         <v>130</v>
       </c>
-      <c r="AG2" s="22" t="s">
+      <c r="AF2" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="AH2" s="22" t="s">
+      <c r="AG2" s="34" t="s">
         <v>137</v>
       </c>
-      <c r="AI2" s="22" t="s">
+      <c r="AH2" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="AJ2" s="22" t="s">
+      <c r="AI2" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="AK2" s="22" t="s">
+      <c r="AJ2" s="33" t="s">
         <v>147</v>
       </c>
-      <c r="AL2" s="22" t="s">
+      <c r="AK2" s="33" t="s">
         <v>150</v>
       </c>
-      <c r="AM2" s="22" t="s">
+      <c r="AL2" s="33" t="s">
         <v>154</v>
       </c>
-      <c r="AN2" s="22" t="s">
+      <c r="AM2" s="33" t="s">
         <v>158</v>
       </c>
-      <c r="AO2" s="22" t="s">
+      <c r="AN2" s="33" t="s">
         <v>161</v>
       </c>
-      <c r="AP2" s="22" t="s">
+      <c r="AO2" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="AQ2" s="22" t="s">
+      <c r="AP2" s="34" t="s">
         <v>168</v>
       </c>
-      <c r="AR2" s="22" t="s">
+      <c r="AQ2" s="34" t="s">
         <v>172</v>
       </c>
-      <c r="AS2" s="22" t="s">
+      <c r="AR2" s="33" t="s">
         <v>176</v>
       </c>
-      <c r="AT2" s="22" t="s">
+      <c r="AS2" s="33" t="s">
         <v>179</v>
       </c>
-      <c r="AU2" s="22" t="s">
+      <c r="AT2" s="33" t="s">
         <v>181</v>
       </c>
-      <c r="AV2" s="22" t="s">
+      <c r="AU2" s="34" t="s">
         <v>183</v>
       </c>
-      <c r="AW2" s="22" t="s">
+      <c r="AV2" s="33" t="s">
         <v>190</v>
       </c>
-      <c r="AX2" s="22" t="s">
+      <c r="AW2" s="34" t="s">
         <v>194</v>
       </c>
-      <c r="AY2" s="22" t="s">
+      <c r="AX2" s="34" t="s">
         <v>196</v>
       </c>
-      <c r="AZ2" s="22" t="s">
+      <c r="AY2" s="33" t="s">
         <v>202</v>
       </c>
-      <c r="BA2" s="22" t="s">
+      <c r="AZ2" s="33" t="s">
         <v>205</v>
       </c>
-      <c r="BB2" s="22" t="s">
+      <c r="BA2" s="34" t="s">
         <v>208</v>
       </c>
-      <c r="BC2" s="22" t="s">
+      <c r="BB2" s="33" t="s">
         <v>211</v>
       </c>
-      <c r="BD2" s="22" t="s">
+      <c r="BC2" s="33" t="s">
         <v>215</v>
       </c>
-      <c r="BE2" s="22" t="s">
+      <c r="BD2" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="BF2" s="22" t="s">
+      <c r="BE2" s="33" t="s">
         <v>223</v>
       </c>
-      <c r="BG2" s="22" t="s">
+      <c r="BF2" s="33" t="s">
         <v>227</v>
       </c>
-      <c r="BH2" s="22" t="s">
+      <c r="BG2" s="34" t="s">
         <v>231</v>
       </c>
-      <c r="BI2" s="22" t="s">
+      <c r="BH2" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="BJ2" s="22" t="s">
+      <c r="BI2" s="33" t="s">
         <v>236</v>
       </c>
-      <c r="BK2" s="22" t="s">
+      <c r="BJ2" s="33" t="s">
         <v>238</v>
       </c>
-      <c r="BL2" s="22" t="s">
+      <c r="BK2" s="33" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="3" spans="1:64">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1" t="s">
+    <row r="3" spans="1:63">
+      <c r="A3" t="s">
         <v>360</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="B3" t="s">
         <v>360</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="C3" t="s">
         <v>360</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="D3" t="s">
         <v>360</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="E3" t="s">
         <v>360</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="F3" t="s">
         <v>360</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="G3" t="s">
         <v>360</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="H3" t="s">
         <v>360</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="I3" t="s">
         <v>360</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="J3" t="s">
         <v>360</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="K3" t="s">
         <v>360</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="L3" t="s">
         <v>360</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="M3" t="s">
         <v>360</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="N3" t="s">
         <v>360</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="O3" t="s">
         <v>360</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="P3" t="s">
         <v>360</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="Q3" t="s">
         <v>360</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="R3" t="s">
         <v>360</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="S3" t="s">
         <v>360</v>
       </c>
-      <c r="U3" s="1" t="s">
+      <c r="T3" t="s">
         <v>360</v>
       </c>
-      <c r="V3" s="1" t="s">
+      <c r="U3" t="s">
         <v>360</v>
       </c>
-      <c r="W3" s="1" t="s">
+      <c r="V3" t="s">
         <v>360</v>
       </c>
-      <c r="X3" s="1" t="s">
+      <c r="W3" t="s">
         <v>360</v>
       </c>
-      <c r="Y3" s="1" t="s">
+      <c r="X3" t="s">
         <v>360</v>
       </c>
-      <c r="Z3" s="1" t="s">
+      <c r="Y3" t="s">
         <v>360</v>
       </c>
-      <c r="AA3" s="1" t="s">
+      <c r="Z3" t="s">
         <v>360</v>
       </c>
-      <c r="AB3" s="1" t="s">
+      <c r="AA3" t="s">
         <v>360</v>
       </c>
-      <c r="AC3" s="1" t="s">
+      <c r="AB3" t="s">
         <v>360</v>
       </c>
-      <c r="AD3" s="1" t="s">
+      <c r="AC3" t="s">
         <v>360</v>
       </c>
-      <c r="AE3" s="1" t="s">
+      <c r="AD3" t="s">
         <v>360</v>
       </c>
-      <c r="AF3" s="1" t="s">
+      <c r="AE3" t="s">
         <v>360</v>
       </c>
-      <c r="AG3" s="1" t="s">
+      <c r="AF3" t="s">
         <v>360</v>
       </c>
-      <c r="AH3" s="1" t="s">
+      <c r="AG3" t="s">
         <v>360</v>
       </c>
-      <c r="AI3" s="1" t="s">
+      <c r="AH3" t="s">
         <v>360</v>
       </c>
-      <c r="AJ3" s="1" t="s">
+      <c r="AI3" t="s">
         <v>360</v>
       </c>
-      <c r="AK3" s="1" t="s">
+      <c r="AJ3" t="s">
         <v>360</v>
       </c>
-      <c r="AL3" s="1" t="s">
+      <c r="AK3" t="s">
         <v>360</v>
       </c>
-      <c r="AM3" s="1" t="s">
+      <c r="AL3" t="s">
         <v>360</v>
       </c>
-      <c r="AN3" s="1" t="s">
+      <c r="AM3" t="s">
         <v>360</v>
       </c>
-      <c r="AO3" s="1" t="s">
+      <c r="AN3" t="s">
         <v>360</v>
       </c>
-      <c r="AP3" s="1" t="s">
+      <c r="AO3" t="s">
         <v>360</v>
       </c>
-      <c r="AQ3" s="1" t="s">
+      <c r="AP3" t="s">
         <v>360</v>
       </c>
-      <c r="AR3" s="1" t="s">
+      <c r="AQ3" t="s">
         <v>360</v>
       </c>
-      <c r="AS3" s="1" t="s">
+      <c r="AR3" t="s">
         <v>360</v>
       </c>
-      <c r="AT3" s="1" t="s">
+      <c r="AS3" t="s">
         <v>360</v>
       </c>
-      <c r="AU3" s="1" t="s">
+      <c r="AT3" t="s">
         <v>360</v>
       </c>
-      <c r="AV3" s="1" t="s">
+      <c r="AU3" t="s">
         <v>360</v>
       </c>
-      <c r="AW3" s="1" t="s">
+      <c r="AV3" t="s">
         <v>360</v>
       </c>
-      <c r="AX3" s="1" t="s">
+      <c r="AW3" t="s">
         <v>360</v>
       </c>
-      <c r="AY3" s="1" t="s">
+      <c r="AX3" t="s">
         <v>360</v>
       </c>
-      <c r="AZ3" s="1" t="s">
+      <c r="AY3" t="s">
         <v>360</v>
       </c>
-      <c r="BA3" s="1" t="s">
+      <c r="AZ3" t="s">
         <v>360</v>
       </c>
-      <c r="BB3" s="1" t="s">
+      <c r="BA3" t="s">
         <v>360</v>
       </c>
-      <c r="BC3" s="1" t="s">
+      <c r="BB3" t="s">
         <v>360</v>
       </c>
-      <c r="BD3" s="1" t="s">
+      <c r="BC3" t="s">
         <v>360</v>
       </c>
-      <c r="BE3" s="1" t="s">
+      <c r="BD3" t="s">
         <v>360</v>
       </c>
-      <c r="BF3" s="1" t="s">
+      <c r="BE3" t="s">
         <v>360</v>
       </c>
-      <c r="BG3" s="1" t="s">
+      <c r="BF3" t="s">
         <v>360</v>
       </c>
-      <c r="BH3" s="1" t="s">
+      <c r="BG3" t="s">
         <v>360</v>
       </c>
-      <c r="BI3" s="1" t="s">
+      <c r="BH3" t="s">
         <v>360</v>
       </c>
-      <c r="BJ3" s="1" t="s">
+      <c r="BI3" t="s">
         <v>360</v>
       </c>
-      <c r="BK3" s="1" t="s">
+      <c r="BJ3" t="s">
         <v>360</v>
       </c>
-      <c r="BL3" s="1" t="s">
+      <c r="BK3" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="4" spans="1:64">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1" t="s">
+    <row r="4" spans="1:63">
+      <c r="A4" t="s">
         <v>548</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1" t="s">
+      <c r="B4" t="s">
+        <v>1950</v>
+      </c>
+      <c r="C4" t="s">
         <v>888</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="D4" t="s">
         <v>1453</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="E4" t="s">
         <v>1453</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="F4" t="s">
         <v>891</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="G4" t="s">
         <v>1949</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="H4" t="s">
         <v>895</v>
       </c>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1" t="s">
+      <c r="I4" t="s">
+        <v>601</v>
+      </c>
+      <c r="J4" t="s">
+        <v>2191</v>
+      </c>
+      <c r="K4" t="s">
         <v>960</v>
       </c>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1" t="s">
+      <c r="L4" t="s">
+        <v>2191</v>
+      </c>
+      <c r="M4" t="s">
+        <v>1964</v>
+      </c>
+      <c r="N4" t="s">
+        <v>2192</v>
+      </c>
+      <c r="O4" t="s">
         <v>944</v>
       </c>
-      <c r="Q4" s="1" t="s">
+      <c r="P4" t="s">
         <v>1950</v>
       </c>
-      <c r="R4" s="1" t="s">
+      <c r="Q4" t="s">
         <v>1951</v>
       </c>
-      <c r="S4" s="1" t="s">
+      <c r="R4" t="s">
         <v>1952</v>
       </c>
-      <c r="T4" s="1" t="s">
+      <c r="S4" t="s">
         <v>1089</v>
       </c>
-      <c r="U4" s="1" t="s">
+      <c r="T4" t="s">
         <v>1953</v>
       </c>
-      <c r="V4" s="1" t="s">
+      <c r="U4" t="s">
         <v>1453</v>
       </c>
-      <c r="W4" s="1" t="s">
+      <c r="V4" t="s">
         <v>977</v>
       </c>
-      <c r="X4" s="1" t="s">
+      <c r="W4" t="s">
         <v>1453</v>
       </c>
-      <c r="Y4" s="1" t="s">
+      <c r="X4" t="s">
         <v>881</v>
       </c>
-      <c r="Z4" s="1" t="s">
+      <c r="Y4" t="s">
         <v>881</v>
       </c>
-      <c r="AA4" s="1" t="s">
+      <c r="Z4" t="s">
         <v>881</v>
       </c>
-      <c r="AB4" s="1" t="s">
+      <c r="AA4" t="s">
         <v>881</v>
       </c>
-      <c r="AC4" s="1" t="s">
+      <c r="AB4" t="s">
         <v>881</v>
       </c>
-      <c r="AD4" s="1" t="s">
+      <c r="AC4" t="s">
         <v>1954</v>
       </c>
-      <c r="AE4" s="1" t="s">
+      <c r="AD4" t="s">
         <v>1955</v>
       </c>
-      <c r="AF4" s="1" t="s">
+      <c r="AE4" t="s">
         <v>1950</v>
       </c>
-      <c r="AG4" s="1" t="s">
+      <c r="AF4" t="s">
         <v>1453</v>
       </c>
-      <c r="AH4" s="1" t="s">
+      <c r="AG4" t="s">
         <v>1951</v>
       </c>
-      <c r="AI4" s="1" t="s">
+      <c r="AH4" t="s">
         <v>1453</v>
       </c>
-      <c r="AJ4" s="1" t="s">
+      <c r="AI4" t="s">
         <v>1453</v>
       </c>
-      <c r="AK4" s="1" t="s">
+      <c r="AJ4" t="s">
         <v>1453</v>
       </c>
-      <c r="AL4" s="1" t="s">
+      <c r="AK4" t="s">
         <v>376</v>
       </c>
-      <c r="AM4" s="1" t="s">
+      <c r="AL4" t="s">
         <v>1453</v>
       </c>
-      <c r="AN4" s="1" t="s">
+      <c r="AM4" t="s">
         <v>1453</v>
       </c>
-      <c r="AO4" s="1" t="s">
+      <c r="AN4" t="s">
         <v>1453</v>
       </c>
-      <c r="AP4" s="1" t="s">
+      <c r="AO4" t="s">
         <v>1453</v>
       </c>
-      <c r="AQ4" s="1" t="s">
+      <c r="AP4" t="s">
         <v>372</v>
       </c>
-      <c r="AR4" s="1" t="s">
+      <c r="AQ4" t="s">
         <v>1956</v>
       </c>
-      <c r="AS4" s="1"/>
-      <c r="AT4" s="1" t="s">
+      <c r="AR4" t="s">
+        <v>2193</v>
+      </c>
+      <c r="AS4" t="s">
         <v>1957</v>
       </c>
-      <c r="AU4" s="1"/>
-      <c r="AV4" s="1" t="s">
+      <c r="AT4" t="s">
+        <v>2194</v>
+      </c>
+      <c r="AU4" t="s">
         <v>1958</v>
       </c>
-      <c r="AW4" s="1" t="s">
+      <c r="AV4" t="s">
         <v>1957</v>
       </c>
-      <c r="AX4" s="1" t="s">
+      <c r="AW4" t="s">
         <v>643</v>
       </c>
-      <c r="AY4" s="1" t="s">
+      <c r="AX4" t="s">
         <v>372</v>
       </c>
-      <c r="AZ4" s="1"/>
-      <c r="BA4" s="1" t="s">
+      <c r="AY4" t="s">
+        <v>1521</v>
+      </c>
+      <c r="AZ4" t="s">
         <v>1959</v>
       </c>
-      <c r="BB4" s="1" t="s">
+      <c r="BA4" t="s">
         <v>1960</v>
       </c>
-      <c r="BC4" s="1" t="s">
+      <c r="BB4" t="s">
         <v>1453</v>
       </c>
-      <c r="BD4" s="1" t="s">
+      <c r="BC4" t="s">
         <v>1453</v>
       </c>
-      <c r="BE4" s="1" t="s">
+      <c r="BD4" t="s">
         <v>1961</v>
       </c>
-      <c r="BF4" s="1" t="s">
+      <c r="BE4" t="s">
         <v>1453</v>
       </c>
-      <c r="BG4" s="1"/>
-      <c r="BH4" s="1" t="s">
+      <c r="BF4" t="s">
+        <v>2195</v>
+      </c>
+      <c r="BG4" t="s">
         <v>525</v>
       </c>
-      <c r="BI4" s="1" t="s">
+      <c r="BH4" t="s">
         <v>938</v>
       </c>
-      <c r="BJ4" s="1" t="s">
+      <c r="BI4" t="s">
         <v>1962</v>
       </c>
-      <c r="BK4" s="1" t="s">
+      <c r="BJ4" t="s">
         <v>887</v>
       </c>
-      <c r="BL4" s="1" t="s">
+      <c r="BK4" t="s">
         <v>948</v>
       </c>
     </row>
-    <row r="5" spans="1:64">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1" t="s">
+    <row r="5" spans="1:63">
+      <c r="A5" t="s">
         <v>458</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1" t="s">
+      <c r="C5" t="s">
         <v>889</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="D5" t="s">
         <v>1963</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="E5" t="s">
         <v>1963</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="F5" t="s">
         <v>958</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="G5" t="s">
         <v>1453</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="H5" t="s">
         <v>643</v>
       </c>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1" t="s">
+      <c r="K5" t="s">
         <v>1964</v>
       </c>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1" t="s">
+      <c r="O5" t="s">
         <v>1190</v>
       </c>
-      <c r="Q5" s="1" t="s">
+      <c r="P5" t="s">
         <v>1965</v>
       </c>
-      <c r="R5" s="1" t="s">
+      <c r="Q5" t="s">
         <v>944</v>
       </c>
-      <c r="S5" s="1"/>
-      <c r="T5" s="1" t="s">
+      <c r="R5" t="s">
+        <v>2196</v>
+      </c>
+      <c r="S5" t="s">
         <v>1148</v>
       </c>
-      <c r="U5" s="1" t="s">
+      <c r="T5" t="s">
         <v>376</v>
       </c>
-      <c r="V5" s="1" t="s">
+      <c r="U5" t="s">
         <v>1963</v>
       </c>
-      <c r="W5" s="1" t="s">
+      <c r="V5" t="s">
         <v>1420</v>
       </c>
-      <c r="X5" s="1" t="s">
+      <c r="W5" t="s">
         <v>1963</v>
       </c>
-      <c r="Y5" s="1" t="s">
+      <c r="X5" t="s">
         <v>1966</v>
       </c>
-      <c r="Z5" s="1" t="s">
+      <c r="Y5" t="s">
         <v>1967</v>
       </c>
-      <c r="AA5" s="1" t="s">
+      <c r="Z5" t="s">
         <v>1521</v>
       </c>
-      <c r="AB5" s="1" t="s">
+      <c r="AA5" t="s">
         <v>1968</v>
       </c>
-      <c r="AC5" s="1" t="s">
+      <c r="AB5" t="s">
         <v>1969</v>
       </c>
-      <c r="AD5" s="1" t="s">
+      <c r="AC5" t="s">
         <v>1453</v>
       </c>
-      <c r="AE5" s="1" t="s">
+      <c r="AD5" t="s">
         <v>1453</v>
       </c>
-      <c r="AF5" s="1" t="s">
+      <c r="AE5" t="s">
         <v>1965</v>
       </c>
-      <c r="AG5" s="1" t="s">
+      <c r="AF5" t="s">
         <v>1970</v>
       </c>
-      <c r="AH5" s="1" t="s">
+      <c r="AG5" t="s">
         <v>1971</v>
       </c>
-      <c r="AI5" s="1" t="s">
+      <c r="AH5" t="s">
         <v>1972</v>
       </c>
-      <c r="AJ5" s="1" t="s">
+      <c r="AI5" t="s">
         <v>1973</v>
       </c>
-      <c r="AK5" s="1" t="s">
+      <c r="AJ5" t="s">
         <v>1974</v>
       </c>
-      <c r="AL5" s="1" t="s">
+      <c r="AK5" t="s">
         <v>1975</v>
       </c>
-      <c r="AM5" s="1" t="s">
+      <c r="AL5" t="s">
         <v>376</v>
       </c>
-      <c r="AN5" s="1" t="s">
+      <c r="AM5" t="s">
         <v>376</v>
       </c>
-      <c r="AO5" s="1"/>
-      <c r="AP5" s="1" t="s">
+      <c r="AN5" t="s">
         <v>376</v>
       </c>
-      <c r="AQ5" s="1" t="s">
+      <c r="AO5" t="s">
         <v>376</v>
       </c>
-      <c r="AR5" s="1" t="s">
+      <c r="AP5" t="s">
+        <v>376</v>
+      </c>
+      <c r="AQ5" t="s">
         <v>1976</v>
       </c>
-      <c r="AS5" s="1"/>
-      <c r="AT5" s="1" t="s">
+      <c r="AS5" t="s">
         <v>1977</v>
       </c>
-      <c r="AU5" s="1"/>
-      <c r="AV5" s="1" t="s">
+      <c r="AU5" t="s">
         <v>643</v>
       </c>
-      <c r="AW5" s="1" t="s">
+      <c r="AV5" t="s">
         <v>1977</v>
       </c>
-      <c r="AX5" s="1" t="s">
+      <c r="AW5" t="s">
         <v>889</v>
       </c>
-      <c r="AY5" s="1" t="s">
+      <c r="AX5" t="s">
         <v>1975</v>
       </c>
-      <c r="AZ5" s="1"/>
-      <c r="BA5" s="1"/>
-      <c r="BB5" s="1" t="s">
+      <c r="AZ5" t="s">
+        <v>1457</v>
+      </c>
+      <c r="BA5" t="s">
         <v>376</v>
       </c>
-      <c r="BC5" s="1" t="s">
+      <c r="BB5" t="s">
         <v>1963</v>
       </c>
-      <c r="BD5" s="1" t="s">
+      <c r="BC5" t="s">
         <v>1963</v>
       </c>
-      <c r="BE5" s="1" t="s">
+      <c r="BD5" t="s">
         <v>1978</v>
       </c>
-      <c r="BF5" s="1" t="s">
+      <c r="BE5" t="s">
         <v>1963</v>
       </c>
-      <c r="BG5" s="1"/>
-      <c r="BH5" s="1"/>
-      <c r="BI5" s="1" t="s">
+      <c r="BG5" t="s">
+        <v>2197</v>
+      </c>
+      <c r="BH5" t="s">
         <v>1002</v>
       </c>
-      <c r="BJ5" s="1" t="s">
+      <c r="BI5" t="s">
         <v>372</v>
       </c>
-      <c r="BK5" s="1" t="s">
+      <c r="BJ5" t="s">
         <v>1979</v>
       </c>
-      <c r="BL5" s="1" t="s">
+      <c r="BK5" t="s">
         <v>1010</v>
       </c>
     </row>
-    <row r="6" spans="1:64">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1" t="s">
+    <row r="6" spans="1:63">
+      <c r="A6" t="s">
         <v>1018</v>
       </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1" t="s">
+      <c r="C6" t="s">
         <v>911</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="D6" t="s">
         <v>1089</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="E6" t="s">
         <v>1089</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="F6" t="s">
         <v>920</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="G6" t="s">
         <v>1089</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="H6" t="s">
         <v>1067</v>
       </c>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1" t="s">
+      <c r="K6" t="s">
+        <v>2035</v>
+      </c>
+      <c r="O6" t="s">
         <v>1980</v>
       </c>
-      <c r="Q6" s="1" t="s">
+      <c r="P6" t="s">
         <v>1981</v>
       </c>
-      <c r="R6" s="1" t="s">
+      <c r="Q6" t="s">
         <v>1962</v>
       </c>
-      <c r="S6" s="1"/>
-      <c r="T6" s="1" t="s">
+      <c r="S6" t="s">
         <v>1949</v>
       </c>
-      <c r="U6" s="1" t="s">
+      <c r="T6" t="s">
         <v>1228</v>
       </c>
-      <c r="V6" s="1" t="s">
+      <c r="U6" t="s">
         <v>1089</v>
       </c>
-      <c r="W6" s="1" t="s">
+      <c r="V6" t="s">
         <v>889</v>
       </c>
-      <c r="X6" s="1" t="s">
+      <c r="W6" t="s">
         <v>1089</v>
       </c>
-      <c r="Y6" s="1" t="s">
+      <c r="X6" t="s">
         <v>1982</v>
       </c>
-      <c r="Z6" s="1" t="s">
+      <c r="Y6" t="s">
         <v>991</v>
       </c>
-      <c r="AA6" s="1" t="s">
+      <c r="Z6" t="s">
         <v>1142</v>
       </c>
-      <c r="AB6" s="1" t="s">
+      <c r="AA6" t="s">
         <v>1983</v>
       </c>
-      <c r="AC6" s="1" t="s">
+      <c r="AB6" t="s">
         <v>1984</v>
       </c>
-      <c r="AD6" s="1" t="s">
+      <c r="AC6" t="s">
         <v>376</v>
       </c>
-      <c r="AE6" s="1" t="s">
+      <c r="AD6" t="s">
         <v>376</v>
       </c>
-      <c r="AF6" s="1" t="s">
+      <c r="AE6" t="s">
         <v>1981</v>
       </c>
-      <c r="AG6" s="1" t="s">
+      <c r="AF6" t="s">
         <v>376</v>
       </c>
-      <c r="AH6" s="1" t="s">
+      <c r="AG6" t="s">
         <v>640</v>
       </c>
-      <c r="AI6" s="1"/>
-      <c r="AJ6" s="1" t="s">
+      <c r="AH6" t="s">
         <v>376</v>
       </c>
-      <c r="AK6" s="1" t="s">
+      <c r="AI6" t="s">
         <v>376</v>
       </c>
-      <c r="AL6" s="1" t="s">
+      <c r="AJ6" t="s">
+        <v>376</v>
+      </c>
+      <c r="AK6" t="s">
         <v>525</v>
       </c>
-      <c r="AM6" s="1" t="s">
+      <c r="AL6" t="s">
         <v>1985</v>
       </c>
-      <c r="AN6" s="1" t="s">
+      <c r="AM6" t="s">
         <v>1986</v>
       </c>
-      <c r="AO6" s="1"/>
-      <c r="AP6" s="1" t="s">
+      <c r="AO6" t="s">
         <v>1987</v>
       </c>
-      <c r="AQ6" s="1" t="s">
+      <c r="AP6" t="s">
         <v>1988</v>
       </c>
-      <c r="AR6" s="1" t="s">
+      <c r="AQ6" t="s">
         <v>640</v>
       </c>
-      <c r="AS6" s="1"/>
-      <c r="AT6" s="1" t="s">
+      <c r="AS6" t="s">
         <v>1521</v>
       </c>
-      <c r="AU6" s="1"/>
-      <c r="AV6" s="1" t="s">
+      <c r="AU6" t="s">
         <v>1989</v>
       </c>
-      <c r="AW6" s="1"/>
-      <c r="AX6" s="1" t="s">
+      <c r="AV6" t="s">
+        <v>1521</v>
+      </c>
+      <c r="AW6" t="s">
         <v>1785</v>
       </c>
-      <c r="AY6" s="1" t="s">
+      <c r="AX6" t="s">
         <v>525</v>
       </c>
-      <c r="AZ6" s="1"/>
-      <c r="BA6" s="1"/>
-      <c r="BB6" s="1" t="s">
+      <c r="BA6" t="s">
         <v>636</v>
       </c>
-      <c r="BC6" s="1" t="s">
+      <c r="BB6" t="s">
         <v>1089</v>
       </c>
-      <c r="BD6" s="1" t="s">
+      <c r="BC6" t="s">
         <v>1089</v>
       </c>
-      <c r="BE6" s="1" t="s">
+      <c r="BD6" t="s">
         <v>1990</v>
       </c>
-      <c r="BF6" s="1" t="s">
+      <c r="BE6" t="s">
         <v>1089</v>
       </c>
-      <c r="BG6" s="1"/>
-      <c r="BH6" s="1"/>
-      <c r="BI6" s="1" t="s">
+      <c r="BH6" t="s">
         <v>1067</v>
       </c>
-      <c r="BJ6" s="1" t="s">
+      <c r="BI6" t="s">
         <v>1991</v>
       </c>
-      <c r="BK6" s="1" t="s">
+      <c r="BJ6" t="s">
         <v>1077</v>
       </c>
-      <c r="BL6" s="1" t="s">
+      <c r="BK6" t="s">
         <v>1078</v>
       </c>
     </row>
-    <row r="7" spans="1:64">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1" t="s">
+    <row r="7" spans="1:63">
+      <c r="A7" t="s">
         <v>1084</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1" t="s">
+      <c r="C7" t="s">
         <v>956</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="D7" t="s">
         <v>1148</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="E7" t="s">
         <v>1148</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="F7" t="s">
         <v>1087</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="G7" t="s">
         <v>1148</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="H7" t="s">
         <v>926</v>
       </c>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1" t="s">
+      <c r="O7" t="s">
         <v>1965</v>
       </c>
-      <c r="Q7" s="1" t="s">
+      <c r="P7" t="s">
         <v>372</v>
       </c>
-      <c r="R7" s="1" t="s">
+      <c r="Q7" t="s">
         <v>1992</v>
       </c>
-      <c r="S7" s="1"/>
-      <c r="T7" s="1" t="s">
+      <c r="S7" t="s">
         <v>1022</v>
       </c>
-      <c r="U7" s="1" t="s">
+      <c r="T7" t="s">
         <v>644</v>
       </c>
-      <c r="V7" s="1" t="s">
+      <c r="U7" t="s">
         <v>1148</v>
       </c>
-      <c r="W7" s="1" t="s">
+      <c r="V7" t="s">
         <v>899</v>
       </c>
-      <c r="X7" s="1" t="s">
+      <c r="W7" t="s">
         <v>1148</v>
       </c>
-      <c r="Y7" s="1" t="s">
+      <c r="X7" t="s">
         <v>1993</v>
       </c>
-      <c r="Z7" s="1" t="s">
+      <c r="Y7" t="s">
         <v>889</v>
       </c>
-      <c r="AA7" s="1"/>
-      <c r="AB7" s="1" t="s">
+      <c r="Z7" t="s">
+        <v>1201</v>
+      </c>
+      <c r="AA7" t="s">
         <v>1994</v>
       </c>
-      <c r="AC7" s="1" t="s">
+      <c r="AB7" t="s">
         <v>1995</v>
       </c>
-      <c r="AD7" s="1" t="s">
+      <c r="AC7" t="s">
         <v>1089</v>
       </c>
-      <c r="AE7" s="1" t="s">
+      <c r="AD7" t="s">
         <v>1089</v>
       </c>
-      <c r="AF7" s="1" t="s">
+      <c r="AE7" t="s">
         <v>372</v>
       </c>
-      <c r="AG7" s="1" t="s">
+      <c r="AF7" t="s">
         <v>1089</v>
       </c>
-      <c r="AH7" s="1" t="s">
+      <c r="AG7" t="s">
         <v>1996</v>
       </c>
-      <c r="AI7" s="1"/>
-      <c r="AJ7" s="1" t="s">
+      <c r="AI7" t="s">
         <v>1089</v>
       </c>
-      <c r="AK7" s="1" t="s">
+      <c r="AJ7" t="s">
         <v>1089</v>
       </c>
-      <c r="AL7" s="1" t="s">
+      <c r="AK7" t="s">
         <v>1997</v>
       </c>
-      <c r="AM7" s="1" t="s">
+      <c r="AL7" t="s">
         <v>1089</v>
       </c>
-      <c r="AN7" s="1" t="s">
+      <c r="AM7" t="s">
         <v>1089</v>
       </c>
-      <c r="AO7" s="1"/>
-      <c r="AP7" s="1" t="s">
+      <c r="AO7" t="s">
         <v>1089</v>
       </c>
-      <c r="AQ7" s="1"/>
-      <c r="AR7" s="1" t="s">
+      <c r="AP7" t="s">
+        <v>2198</v>
+      </c>
+      <c r="AQ7" t="s">
         <v>1998</v>
       </c>
-      <c r="AS7" s="1"/>
-      <c r="AT7" s="1"/>
-      <c r="AU7" s="1"/>
-      <c r="AV7" s="1" t="s">
+      <c r="AS7" t="s">
+        <v>421</v>
+      </c>
+      <c r="AU7" t="s">
         <v>1821</v>
       </c>
-      <c r="AW7" s="1"/>
-      <c r="AX7" s="1" t="s">
+      <c r="AW7" t="s">
         <v>1821</v>
       </c>
-      <c r="AY7" s="1" t="s">
+      <c r="AX7" t="s">
         <v>1997</v>
       </c>
-      <c r="AZ7" s="1"/>
-      <c r="BA7" s="1"/>
-      <c r="BB7" s="1"/>
-      <c r="BC7" s="1" t="s">
+      <c r="BA7" t="s">
+        <v>525</v>
+      </c>
+      <c r="BB7" t="s">
         <v>1148</v>
       </c>
-      <c r="BD7" s="1" t="s">
+      <c r="BC7" t="s">
         <v>1148</v>
       </c>
-      <c r="BE7" s="1"/>
-      <c r="BF7" s="1" t="s">
+      <c r="BD7" t="s">
+        <v>376</v>
+      </c>
+      <c r="BE7" t="s">
         <v>1148</v>
       </c>
-      <c r="BG7" s="1"/>
-      <c r="BH7" s="1"/>
-      <c r="BI7" s="1" t="s">
+      <c r="BH7" t="s">
         <v>1125</v>
       </c>
-      <c r="BJ7" s="1" t="s">
+      <c r="BI7" t="s">
         <v>1963</v>
       </c>
-      <c r="BK7" s="1" t="s">
+      <c r="BJ7" t="s">
         <v>1999</v>
       </c>
-      <c r="BL7" s="1"/>
-    </row>
-    <row r="8" spans="1:64">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1" t="s">
+    </row>
+    <row r="8" spans="1:63">
+      <c r="A8" t="s">
         <v>590</v>
       </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1" t="s">
+      <c r="C8" t="s">
         <v>899</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="D8" t="s">
         <v>1949</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="E8" t="s">
         <v>1949</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="F8" t="s">
         <v>1146</v>
       </c>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1" t="s">
+      <c r="G8" t="s">
+        <v>1022</v>
+      </c>
+      <c r="H8" t="s">
+        <v>761</v>
+      </c>
+      <c r="O8" t="s">
         <v>2000</v>
       </c>
-      <c r="Q8" s="1" t="s">
+      <c r="P8" t="s">
         <v>770</v>
       </c>
-      <c r="R8" s="1" t="s">
+      <c r="Q8" t="s">
         <v>2001</v>
       </c>
-      <c r="S8" s="1"/>
-      <c r="T8" s="1"/>
-      <c r="U8" s="1" t="s">
+      <c r="S8" t="s">
+        <v>1453</v>
+      </c>
+      <c r="T8" t="s">
         <v>2002</v>
       </c>
-      <c r="V8" s="1" t="s">
+      <c r="U8" t="s">
         <v>1949</v>
       </c>
-      <c r="W8" s="1" t="s">
+      <c r="V8" t="s">
         <v>1034</v>
       </c>
-      <c r="X8" s="1" t="s">
+      <c r="W8" t="s">
         <v>1949</v>
       </c>
-      <c r="Y8" s="1" t="s">
+      <c r="X8" t="s">
         <v>2003</v>
       </c>
-      <c r="Z8" s="1" t="s">
+      <c r="Y8" t="s">
         <v>926</v>
       </c>
-      <c r="AA8" s="1"/>
-      <c r="AB8" s="1" t="s">
+      <c r="AA8" t="s">
         <v>2004</v>
       </c>
-      <c r="AC8" s="1" t="s">
+      <c r="AB8" t="s">
         <v>2005</v>
       </c>
-      <c r="AD8" s="1" t="s">
+      <c r="AC8" t="s">
         <v>1148</v>
       </c>
-      <c r="AE8" s="1" t="s">
+      <c r="AD8" t="s">
         <v>1148</v>
       </c>
-      <c r="AF8" s="1" t="s">
+      <c r="AE8" t="s">
         <v>770</v>
       </c>
-      <c r="AG8" s="1" t="s">
+      <c r="AF8" t="s">
         <v>1148</v>
       </c>
-      <c r="AH8" s="1" t="s">
+      <c r="AG8" t="s">
         <v>2006</v>
       </c>
-      <c r="AI8" s="1"/>
-      <c r="AJ8" s="1" t="s">
+      <c r="AI8" t="s">
         <v>1148</v>
       </c>
-      <c r="AK8" s="1" t="s">
+      <c r="AJ8" t="s">
         <v>1148</v>
       </c>
-      <c r="AL8" s="1" t="s">
+      <c r="AK8" t="s">
         <v>891</v>
       </c>
-      <c r="AM8" s="1" t="s">
+      <c r="AL8" t="s">
         <v>1148</v>
       </c>
-      <c r="AN8" s="1" t="s">
+      <c r="AM8" t="s">
         <v>1148</v>
       </c>
-      <c r="AO8" s="1"/>
-      <c r="AP8" s="1" t="s">
+      <c r="AO8" t="s">
         <v>1148</v>
       </c>
-      <c r="AQ8" s="1"/>
-      <c r="AR8" s="1" t="s">
+      <c r="AQ8" t="s">
         <v>2007</v>
       </c>
-      <c r="AS8" s="1"/>
-      <c r="AT8" s="1"/>
-      <c r="AU8" s="1"/>
-      <c r="AV8" s="1"/>
-      <c r="AW8" s="1"/>
-      <c r="AX8" s="1" t="s">
+      <c r="AU8" t="s">
+        <v>761</v>
+      </c>
+      <c r="AW8" t="s">
         <v>2008</v>
       </c>
-      <c r="AY8" s="1" t="s">
+      <c r="AX8" t="s">
         <v>891</v>
       </c>
-      <c r="AZ8" s="1"/>
-      <c r="BA8" s="1"/>
-      <c r="BB8" s="1"/>
-      <c r="BC8" s="1" t="s">
+      <c r="BB8" t="s">
         <v>1949</v>
       </c>
-      <c r="BD8" s="1" t="s">
+      <c r="BC8" t="s">
         <v>1949</v>
       </c>
-      <c r="BE8" s="1"/>
-      <c r="BF8" s="1" t="s">
+      <c r="BE8" t="s">
         <v>1949</v>
       </c>
-      <c r="BG8" s="1"/>
-      <c r="BH8" s="1"/>
-      <c r="BI8" s="1" t="s">
+      <c r="BH8" t="s">
         <v>1403</v>
       </c>
-      <c r="BJ8" s="1" t="s">
+      <c r="BI8" t="s">
         <v>608</v>
       </c>
-      <c r="BK8" s="1" t="s">
+      <c r="BJ8" t="s">
         <v>1136</v>
       </c>
-      <c r="BL8" s="1"/>
-    </row>
-    <row r="9" spans="1:64">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1" t="s">
+    </row>
+    <row r="9" spans="1:63">
+      <c r="A9" t="s">
+        <v>366</v>
+      </c>
+      <c r="C9" t="s">
         <v>1206</v>
       </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1" t="s">
+      <c r="D9" t="s">
+        <v>1022</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1022</v>
+      </c>
+      <c r="F9" t="s">
         <v>1183</v>
       </c>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1" t="s">
+      <c r="O9" t="s">
         <v>2009</v>
       </c>
-      <c r="Q9" s="1" t="s">
+      <c r="P9" t="s">
         <v>2010</v>
       </c>
-      <c r="R9" s="1" t="s">
+      <c r="Q9" t="s">
         <v>2011</v>
       </c>
-      <c r="S9" s="1"/>
-      <c r="T9" s="1"/>
-      <c r="U9" s="1"/>
-      <c r="V9" s="1"/>
-      <c r="W9" s="1" t="s">
+      <c r="T9" t="s">
+        <v>2199</v>
+      </c>
+      <c r="U9" t="s">
+        <v>1022</v>
+      </c>
+      <c r="V9" t="s">
         <v>1104</v>
       </c>
-      <c r="X9" s="1"/>
-      <c r="Y9" s="1" t="s">
+      <c r="W9" t="s">
+        <v>1022</v>
+      </c>
+      <c r="X9" t="s">
         <v>2012</v>
       </c>
-      <c r="Z9" s="1" t="s">
+      <c r="Y9" t="s">
         <v>699</v>
       </c>
-      <c r="AA9" s="1"/>
-      <c r="AB9" s="1" t="s">
+      <c r="AA9" t="s">
         <v>2013</v>
       </c>
-      <c r="AC9" s="1" t="s">
+      <c r="AB9" t="s">
         <v>2014</v>
       </c>
-      <c r="AD9" s="1"/>
-      <c r="AE9" s="1"/>
-      <c r="AF9" s="1" t="s">
+      <c r="AC9" t="s">
+        <v>1022</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>1022</v>
+      </c>
+      <c r="AE9" t="s">
         <v>2010</v>
       </c>
-      <c r="AG9" s="1"/>
-      <c r="AH9" s="1" t="s">
+      <c r="AF9" t="s">
+        <v>1022</v>
+      </c>
+      <c r="AG9" t="s">
         <v>2015</v>
       </c>
-      <c r="AI9" s="1"/>
-      <c r="AJ9" s="1"/>
-      <c r="AK9" s="1"/>
-      <c r="AL9" s="1" t="s">
+      <c r="AI9" t="s">
+        <v>1022</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>1022</v>
+      </c>
+      <c r="AK9" t="s">
         <v>770</v>
       </c>
-      <c r="AM9" s="1"/>
-      <c r="AN9" s="1"/>
-      <c r="AO9" s="1"/>
-      <c r="AP9" s="1"/>
-      <c r="AQ9" s="1"/>
-      <c r="AR9" s="1" t="s">
+      <c r="AL9" t="s">
+        <v>1022</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>1022</v>
+      </c>
+      <c r="AO9" t="s">
+        <v>1022</v>
+      </c>
+      <c r="AQ9" t="s">
         <v>2016</v>
       </c>
-      <c r="AS9" s="1"/>
-      <c r="AT9" s="1"/>
-      <c r="AU9" s="1"/>
-      <c r="AV9" s="1"/>
-      <c r="AW9" s="1"/>
-      <c r="AX9" s="1" t="s">
+      <c r="AW9" t="s">
         <v>2017</v>
       </c>
-      <c r="AY9" s="1" t="s">
+      <c r="AX9" t="s">
         <v>770</v>
       </c>
-      <c r="AZ9" s="1"/>
-      <c r="BA9" s="1"/>
-      <c r="BB9" s="1"/>
-      <c r="BC9" s="1"/>
-      <c r="BD9" s="1"/>
-      <c r="BE9" s="1"/>
-      <c r="BF9" s="1"/>
-      <c r="BG9" s="1"/>
-      <c r="BH9" s="1"/>
-      <c r="BI9" s="1" t="s">
+      <c r="BB9" t="s">
+        <v>1022</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>1022</v>
+      </c>
+      <c r="BE9" t="s">
+        <v>1022</v>
+      </c>
+      <c r="BH9" t="s">
         <v>899</v>
       </c>
-      <c r="BJ9" s="1" t="s">
+      <c r="BI9" t="s">
         <v>644</v>
       </c>
-      <c r="BK9" s="1" t="s">
+      <c r="BJ9" t="s">
         <v>1197</v>
       </c>
-      <c r="BL9" s="1"/>
-    </row>
-    <row r="10" spans="1:64">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1" t="s">
+    </row>
+    <row r="10" spans="1:63">
+      <c r="C10" t="s">
         <v>1246</v>
       </c>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1" t="s">
+      <c r="F10" t="s">
         <v>1115</v>
       </c>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1" t="s">
+      <c r="O10" t="s">
         <v>1981</v>
       </c>
-      <c r="Q10" s="1" t="s">
+      <c r="P10" t="s">
         <v>525</v>
       </c>
-      <c r="R10" s="1" t="s">
+      <c r="Q10" t="s">
         <v>2018</v>
       </c>
-      <c r="S10" s="1"/>
-      <c r="T10" s="1"/>
-      <c r="U10" s="1"/>
-      <c r="V10" s="1"/>
-      <c r="W10" s="1" t="s">
+      <c r="V10" t="s">
         <v>1161</v>
       </c>
-      <c r="X10" s="1"/>
-      <c r="Y10" s="1" t="s">
+      <c r="X10" t="s">
         <v>2019</v>
       </c>
-      <c r="Z10" s="1" t="s">
+      <c r="Y10" t="s">
         <v>1813</v>
       </c>
-      <c r="AA10" s="1"/>
-      <c r="AB10" s="1" t="s">
+      <c r="AA10" t="s">
         <v>2020</v>
       </c>
-      <c r="AC10" s="1"/>
-      <c r="AD10" s="1"/>
-      <c r="AE10" s="1"/>
-      <c r="AF10" s="1"/>
-      <c r="AG10" s="1"/>
-      <c r="AH10" s="1" t="s">
+      <c r="AB10" t="s">
+        <v>2200</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>525</v>
+      </c>
+      <c r="AG10" t="s">
         <v>944</v>
       </c>
-      <c r="AI10" s="1"/>
-      <c r="AJ10" s="1"/>
-      <c r="AK10" s="1"/>
-      <c r="AL10" s="1" t="s">
+      <c r="AK10" t="s">
         <v>626</v>
       </c>
-      <c r="AM10" s="1"/>
-      <c r="AN10" s="1"/>
-      <c r="AO10" s="1"/>
-      <c r="AP10" s="1"/>
-      <c r="AQ10" s="1"/>
-      <c r="AR10" s="1" t="s">
+      <c r="AQ10" t="s">
         <v>2021</v>
       </c>
-      <c r="AS10" s="1"/>
-      <c r="AT10" s="1"/>
-      <c r="AU10" s="1"/>
-      <c r="AV10" s="1"/>
-      <c r="AW10" s="1"/>
-      <c r="AX10" s="1" t="s">
+      <c r="AW10" t="s">
         <v>370</v>
       </c>
-      <c r="AY10" s="1" t="s">
+      <c r="AX10" t="s">
         <v>626</v>
       </c>
-      <c r="AZ10" s="1"/>
-      <c r="BA10" s="1"/>
-      <c r="BB10" s="1"/>
-      <c r="BC10" s="1"/>
-      <c r="BD10" s="1"/>
-      <c r="BE10" s="1"/>
-      <c r="BF10" s="1"/>
-      <c r="BG10" s="1"/>
-      <c r="BH10" s="1"/>
-      <c r="BI10" s="1" t="s">
+      <c r="BH10" t="s">
         <v>977</v>
       </c>
-      <c r="BJ10" s="1"/>
-      <c r="BK10" s="1" t="s">
+      <c r="BI10" t="s">
+        <v>366</v>
+      </c>
+      <c r="BJ10" t="s">
         <v>687</v>
       </c>
-      <c r="BL10" s="1"/>
-    </row>
-    <row r="11" spans="1:64">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1" t="s">
+    </row>
+    <row r="11" spans="1:63">
+      <c r="C11" t="s">
         <v>1294</v>
       </c>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1" t="s">
+      <c r="F11" t="s">
         <v>899</v>
       </c>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1" t="s">
+      <c r="O11" t="s">
         <v>2022</v>
       </c>
-      <c r="Q11" s="1" t="s">
+      <c r="P11" t="s">
         <v>376</v>
       </c>
-      <c r="R11" s="1" t="s">
+      <c r="Q11" t="s">
         <v>2023</v>
       </c>
-      <c r="S11" s="1"/>
-      <c r="T11" s="1"/>
-      <c r="U11" s="1"/>
-      <c r="V11" s="1"/>
-      <c r="W11" s="1" t="s">
+      <c r="V11" t="s">
         <v>1058</v>
       </c>
-      <c r="X11" s="1"/>
-      <c r="Y11" s="1" t="s">
+      <c r="X11" t="s">
         <v>2024</v>
       </c>
-      <c r="Z11" s="1" t="s">
+      <c r="Y11" t="s">
         <v>2025</v>
       </c>
-      <c r="AA11" s="1"/>
-      <c r="AB11" s="1" t="s">
+      <c r="AA11" t="s">
         <v>2026</v>
       </c>
-      <c r="AC11" s="1"/>
-      <c r="AD11" s="1"/>
-      <c r="AE11" s="1"/>
-      <c r="AF11" s="1"/>
-      <c r="AG11" s="1"/>
-      <c r="AH11" s="1" t="s">
+      <c r="AG11" t="s">
         <v>808</v>
       </c>
-      <c r="AI11" s="1"/>
-      <c r="AJ11" s="1"/>
-      <c r="AK11" s="1"/>
-      <c r="AL11" s="1"/>
-      <c r="AM11" s="1"/>
-      <c r="AN11" s="1"/>
-      <c r="AO11" s="1"/>
-      <c r="AP11" s="1"/>
-      <c r="AQ11" s="1"/>
-      <c r="AR11" s="1" t="s">
+      <c r="AK11" t="s">
+        <v>590</v>
+      </c>
+      <c r="AQ11" t="s">
         <v>376</v>
       </c>
-      <c r="AS11" s="1"/>
-      <c r="AT11" s="1"/>
-      <c r="AU11" s="1"/>
-      <c r="AV11" s="1"/>
-      <c r="AW11" s="1"/>
-      <c r="AX11" s="1" t="s">
+      <c r="AW11" t="s">
         <v>991</v>
       </c>
-      <c r="AY11" s="1" t="s">
+      <c r="AX11" t="s">
         <v>590</v>
       </c>
-      <c r="AZ11" s="1"/>
-      <c r="BA11" s="1"/>
-      <c r="BB11" s="1"/>
-      <c r="BC11" s="1"/>
-      <c r="BD11" s="1"/>
-      <c r="BE11" s="1"/>
-      <c r="BF11" s="1"/>
-      <c r="BG11" s="1"/>
-      <c r="BH11" s="1"/>
-      <c r="BI11" s="1" t="s">
+      <c r="BH11" t="s">
         <v>1506</v>
       </c>
-      <c r="BJ11" s="1"/>
-      <c r="BK11" s="1" t="s">
+      <c r="BJ11" t="s">
         <v>948</v>
       </c>
-      <c r="BL11" s="1"/>
-    </row>
-    <row r="12" spans="1:64">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1" t="s">
+    </row>
+    <row r="12" spans="1:63">
+      <c r="C12" t="s">
         <v>984</v>
       </c>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1" t="s">
+      <c r="F12" t="s">
         <v>1331</v>
       </c>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1" t="s">
+      <c r="O12" t="s">
         <v>438</v>
       </c>
-      <c r="Q12" s="1" t="s">
+      <c r="P12" t="s">
         <v>1110</v>
       </c>
-      <c r="R12" s="1" t="s">
+      <c r="Q12" t="s">
         <v>2027</v>
       </c>
-      <c r="S12" s="1"/>
-      <c r="T12" s="1"/>
-      <c r="U12" s="1"/>
-      <c r="V12" s="1"/>
-      <c r="W12" s="1" t="s">
+      <c r="V12" t="s">
         <v>1032</v>
       </c>
-      <c r="X12" s="1"/>
-      <c r="Y12" s="1" t="s">
+      <c r="X12" t="s">
         <v>2028</v>
       </c>
-      <c r="Z12" s="1" t="s">
+      <c r="Y12" t="s">
         <v>553</v>
       </c>
-      <c r="AA12" s="1"/>
-      <c r="AB12" s="1" t="s">
+      <c r="AA12" t="s">
         <v>2029</v>
       </c>
-      <c r="AC12" s="1"/>
-      <c r="AD12" s="1"/>
-      <c r="AE12" s="1"/>
-      <c r="AF12" s="1"/>
-      <c r="AG12" s="1"/>
-      <c r="AH12" s="1" t="s">
+      <c r="AG12" t="s">
         <v>2030</v>
       </c>
-      <c r="AI12" s="1"/>
-      <c r="AJ12" s="1"/>
-      <c r="AK12" s="1"/>
-      <c r="AL12" s="1"/>
-      <c r="AM12" s="1"/>
-      <c r="AN12" s="1"/>
-      <c r="AO12" s="1"/>
-      <c r="AP12" s="1"/>
-      <c r="AQ12" s="1"/>
-      <c r="AR12" s="1" t="s">
+      <c r="AQ12" t="s">
         <v>2031</v>
       </c>
-      <c r="AS12" s="1"/>
-      <c r="AT12" s="1"/>
-      <c r="AU12" s="1"/>
-      <c r="AV12" s="1"/>
-      <c r="AW12" s="1"/>
-      <c r="AX12" s="1" t="s">
+      <c r="AW12" t="s">
         <v>1836</v>
       </c>
-      <c r="AY12" s="1" t="s">
+      <c r="AX12" t="s">
         <v>376</v>
       </c>
-      <c r="AZ12" s="1"/>
-      <c r="BA12" s="1"/>
-      <c r="BB12" s="1"/>
-      <c r="BC12" s="1"/>
-      <c r="BD12" s="1"/>
-      <c r="BE12" s="1"/>
-      <c r="BF12" s="1"/>
-      <c r="BG12" s="1"/>
-      <c r="BH12" s="1"/>
-      <c r="BI12" s="1" t="s">
+      <c r="BH12" t="s">
         <v>1226</v>
       </c>
-      <c r="BJ12" s="1"/>
-      <c r="BK12" s="1" t="s">
+      <c r="BJ12" t="s">
         <v>1084</v>
       </c>
-      <c r="BL12" s="1"/>
-    </row>
-    <row r="13" spans="1:64">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1" t="s">
+    </row>
+    <row r="13" spans="1:63">
+      <c r="C13" t="s">
         <v>1041</v>
       </c>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1" t="s">
+      <c r="F13" t="s">
         <v>1222</v>
       </c>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
-      <c r="P13" s="1" t="s">
+      <c r="O13" t="s">
         <v>2032</v>
       </c>
-      <c r="Q13" s="1" t="s">
+      <c r="P13" t="s">
         <v>1165</v>
       </c>
-      <c r="R13" s="1" t="s">
+      <c r="Q13" t="s">
         <v>372</v>
       </c>
-      <c r="S13" s="1"/>
-      <c r="T13" s="1"/>
-      <c r="U13" s="1"/>
-      <c r="V13" s="1"/>
-      <c r="W13" s="1" t="s">
+      <c r="V13" t="s">
         <v>1259</v>
       </c>
-      <c r="X13" s="1"/>
-      <c r="Y13" s="1" t="s">
+      <c r="X13" t="s">
         <v>2033</v>
       </c>
-      <c r="Z13" s="1"/>
-      <c r="AA13" s="1"/>
-      <c r="AB13" s="1" t="s">
+      <c r="Y13" t="s">
+        <v>2092</v>
+      </c>
+      <c r="AA13" t="s">
         <v>2034</v>
       </c>
-      <c r="AC13" s="1"/>
-      <c r="AD13" s="1"/>
-      <c r="AE13" s="1"/>
-      <c r="AF13" s="1"/>
-      <c r="AG13" s="1"/>
-      <c r="AH13" s="1" t="s">
+      <c r="AG13" t="s">
         <v>2035</v>
       </c>
-      <c r="AI13" s="1"/>
-      <c r="AJ13" s="1"/>
-      <c r="AK13" s="1"/>
-      <c r="AL13" s="1"/>
-      <c r="AM13" s="1"/>
-      <c r="AN13" s="1"/>
-      <c r="AO13" s="1"/>
-      <c r="AP13" s="1"/>
-      <c r="AQ13" s="1"/>
-      <c r="AR13" s="1" t="s">
+      <c r="AQ13" t="s">
         <v>2036</v>
       </c>
-      <c r="AS13" s="1"/>
-      <c r="AT13" s="1"/>
-      <c r="AU13" s="1"/>
-      <c r="AV13" s="1"/>
-      <c r="AW13" s="1"/>
-      <c r="AX13" s="1" t="s">
+      <c r="AW13" t="s">
         <v>761</v>
       </c>
-      <c r="AY13" s="1" t="s">
+      <c r="AX13" t="s">
         <v>2037</v>
       </c>
-      <c r="AZ13" s="1"/>
-      <c r="BA13" s="1"/>
-      <c r="BB13" s="1"/>
-      <c r="BC13" s="1"/>
-      <c r="BD13" s="1"/>
-      <c r="BE13" s="1"/>
-      <c r="BF13" s="1"/>
-      <c r="BG13" s="1"/>
-      <c r="BH13" s="1"/>
-      <c r="BI13" s="1" t="s">
+      <c r="BH13" t="s">
         <v>1275</v>
       </c>
-      <c r="BJ13" s="1"/>
-      <c r="BK13" s="1" t="s">
+      <c r="BJ13" t="s">
         <v>2038</v>
       </c>
-      <c r="BL13" s="1"/>
-    </row>
-    <row r="14" spans="1:64">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1" t="s">
+    </row>
+    <row r="14" spans="1:63">
+      <c r="C14" t="s">
         <v>1111</v>
       </c>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1" t="s">
+      <c r="F14" t="s">
         <v>1388</v>
       </c>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-      <c r="P14" s="1" t="s">
+      <c r="O14" t="s">
         <v>2039</v>
       </c>
-      <c r="Q14" s="1"/>
-      <c r="R14" s="1" t="s">
+      <c r="P14" t="s">
+        <v>590</v>
+      </c>
+      <c r="Q14" t="s">
         <v>2040</v>
       </c>
-      <c r="S14" s="1"/>
-      <c r="T14" s="1"/>
-      <c r="U14" s="1"/>
-      <c r="V14" s="1"/>
-      <c r="W14" s="1"/>
-      <c r="X14" s="1"/>
-      <c r="Y14" s="1"/>
-      <c r="Z14" s="1"/>
-      <c r="AA14" s="1"/>
-      <c r="AB14" s="1" t="s">
+      <c r="V14" t="s">
+        <v>560</v>
+      </c>
+      <c r="X14" t="s">
+        <v>2201</v>
+      </c>
+      <c r="AA14" t="s">
         <v>2041</v>
       </c>
-      <c r="AC14" s="1"/>
-      <c r="AD14" s="1"/>
-      <c r="AE14" s="1"/>
-      <c r="AF14" s="1"/>
-      <c r="AG14" s="1"/>
-      <c r="AH14" s="1" t="s">
+      <c r="AG14" t="s">
         <v>2042</v>
       </c>
-      <c r="AI14" s="1"/>
-      <c r="AJ14" s="1"/>
-      <c r="AK14" s="1"/>
-      <c r="AL14" s="1"/>
-      <c r="AM14" s="1"/>
-      <c r="AN14" s="1"/>
-      <c r="AO14" s="1"/>
-      <c r="AP14" s="1"/>
-      <c r="AQ14" s="1"/>
-      <c r="AR14" s="1" t="s">
+      <c r="AQ14" t="s">
         <v>1084</v>
       </c>
-      <c r="AS14" s="1"/>
-      <c r="AT14" s="1"/>
-      <c r="AU14" s="1"/>
-      <c r="AV14" s="1"/>
-      <c r="AW14" s="1"/>
-      <c r="AX14" s="1" t="s">
+      <c r="AW14" t="s">
         <v>699</v>
       </c>
-      <c r="AY14" s="1" t="s">
+      <c r="AX14" t="s">
         <v>2008</v>
       </c>
-      <c r="AZ14" s="1"/>
-      <c r="BA14" s="1"/>
-      <c r="BB14" s="1"/>
-      <c r="BC14" s="1"/>
-      <c r="BD14" s="1"/>
-      <c r="BE14" s="1"/>
-      <c r="BF14" s="1"/>
-      <c r="BG14" s="1"/>
-      <c r="BH14" s="1"/>
-      <c r="BI14" s="1" t="s">
+      <c r="BH14" t="s">
         <v>1315</v>
       </c>
-      <c r="BJ14" s="1"/>
-      <c r="BK14" s="1" t="s">
+      <c r="BJ14" t="s">
         <v>1010</v>
       </c>
-      <c r="BL14" s="1"/>
-    </row>
-    <row r="15" spans="1:64">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1" t="s">
+    </row>
+    <row r="15" spans="1:63">
+      <c r="C15" t="s">
         <v>1167</v>
       </c>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1" t="s">
+      <c r="F15" t="s">
         <v>1266</v>
       </c>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-      <c r="P15" s="1" t="s">
+      <c r="O15" t="s">
         <v>769</v>
       </c>
-      <c r="Q15" s="1"/>
-      <c r="R15" s="1" t="s">
+      <c r="Q15" t="s">
         <v>2043</v>
       </c>
-      <c r="S15" s="1"/>
-      <c r="T15" s="1"/>
-      <c r="U15" s="1"/>
-      <c r="V15" s="1"/>
-      <c r="W15" s="1"/>
-      <c r="X15" s="1"/>
-      <c r="Y15" s="1"/>
-      <c r="Z15" s="1"/>
-      <c r="AA15" s="1"/>
-      <c r="AB15" s="1" t="s">
+      <c r="AA15" t="s">
         <v>1876</v>
       </c>
-      <c r="AC15" s="1"/>
-      <c r="AD15" s="1"/>
-      <c r="AE15" s="1"/>
-      <c r="AF15" s="1"/>
-      <c r="AG15" s="1"/>
-      <c r="AH15" s="1" t="s">
+      <c r="AG15" t="s">
         <v>1960</v>
       </c>
-      <c r="AI15" s="1"/>
-      <c r="AJ15" s="1"/>
-      <c r="AK15" s="1"/>
-      <c r="AL15" s="1"/>
-      <c r="AM15" s="1"/>
-      <c r="AN15" s="1"/>
-      <c r="AO15" s="1"/>
-      <c r="AP15" s="1"/>
-      <c r="AQ15" s="1"/>
-      <c r="AR15" s="1" t="s">
+      <c r="AQ15" t="s">
         <v>2044</v>
       </c>
-      <c r="AS15" s="1"/>
-      <c r="AT15" s="1"/>
-      <c r="AU15" s="1"/>
-      <c r="AV15" s="1"/>
-      <c r="AW15" s="1"/>
-      <c r="AX15" s="1" t="s">
+      <c r="AW15" t="s">
         <v>1813</v>
       </c>
-      <c r="AY15" s="1" t="s">
+      <c r="AX15" t="s">
         <v>2017</v>
       </c>
-      <c r="AZ15" s="1"/>
-      <c r="BA15" s="1"/>
-      <c r="BB15" s="1"/>
-      <c r="BC15" s="1"/>
-      <c r="BD15" s="1"/>
-      <c r="BE15" s="1"/>
-      <c r="BF15" s="1"/>
-      <c r="BG15" s="1"/>
-      <c r="BH15" s="1"/>
-      <c r="BI15" s="1" t="s">
+      <c r="BH15" t="s">
         <v>1429</v>
       </c>
-      <c r="BJ15" s="1"/>
-      <c r="BK15" s="1" t="s">
+      <c r="BJ15" t="s">
         <v>1536</v>
       </c>
-      <c r="BL15" s="1"/>
-    </row>
-    <row r="16" spans="1:64">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1" t="s">
+    </row>
+    <row r="16" spans="1:63">
+      <c r="C16" t="s">
         <v>1231</v>
       </c>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1" t="s">
+      <c r="F16" t="s">
         <v>590</v>
       </c>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1" t="s">
+      <c r="O16" t="s">
         <v>2045</v>
       </c>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1" t="s">
+      <c r="Q16" t="s">
         <v>2046</v>
       </c>
-      <c r="S16" s="1"/>
-      <c r="T16" s="1"/>
-      <c r="U16" s="1"/>
-      <c r="V16" s="1"/>
-      <c r="W16" s="1"/>
-      <c r="X16" s="1"/>
-      <c r="Y16" s="1"/>
-      <c r="Z16" s="1"/>
-      <c r="AA16" s="1"/>
-      <c r="AB16" s="1" t="s">
+      <c r="AA16" t="s">
         <v>1412</v>
       </c>
-      <c r="AC16" s="1"/>
-      <c r="AD16" s="1"/>
-      <c r="AE16" s="1"/>
-      <c r="AF16" s="1"/>
-      <c r="AG16" s="1"/>
-      <c r="AH16" s="1" t="s">
+      <c r="AG16" t="s">
         <v>2047</v>
       </c>
-      <c r="AI16" s="1"/>
-      <c r="AJ16" s="1"/>
-      <c r="AK16" s="1"/>
-      <c r="AL16" s="1"/>
-      <c r="AM16" s="1"/>
-      <c r="AN16" s="1"/>
-      <c r="AO16" s="1"/>
-      <c r="AP16" s="1"/>
-      <c r="AQ16" s="1"/>
-      <c r="AR16" s="1" t="s">
+      <c r="AQ16" t="s">
         <v>962</v>
       </c>
-      <c r="AS16" s="1"/>
-      <c r="AT16" s="1"/>
-      <c r="AU16" s="1"/>
-      <c r="AV16" s="1"/>
-      <c r="AW16" s="1"/>
-      <c r="AX16" s="1" t="s">
+      <c r="AW16" t="s">
         <v>1770</v>
       </c>
-      <c r="AY16" s="1"/>
-      <c r="AZ16" s="1"/>
-      <c r="BA16" s="1"/>
-      <c r="BB16" s="1"/>
-      <c r="BC16" s="1"/>
-      <c r="BD16" s="1"/>
-      <c r="BE16" s="1"/>
-      <c r="BF16" s="1"/>
-      <c r="BG16" s="1"/>
-      <c r="BH16" s="1"/>
-      <c r="BI16" s="1" t="s">
+      <c r="AX16" t="s">
+        <v>2202</v>
+      </c>
+      <c r="BH16" t="s">
         <v>1454</v>
       </c>
-      <c r="BJ16" s="1"/>
-      <c r="BK16" s="1" t="s">
+      <c r="BJ16" t="s">
         <v>1460</v>
       </c>
-      <c r="BL16" s="1"/>
-    </row>
-    <row r="17" spans="1:64">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1" t="s">
+    </row>
+    <row r="17" spans="3:62">
+      <c r="C17" t="s">
         <v>1279</v>
       </c>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1" t="s">
+      <c r="F17" t="s">
         <v>1464</v>
       </c>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1" t="s">
+      <c r="O17" t="s">
         <v>1574</v>
       </c>
-      <c r="Q17" s="1"/>
-      <c r="R17" s="1" t="s">
+      <c r="Q17" t="s">
         <v>2048</v>
       </c>
-      <c r="S17" s="1"/>
-      <c r="T17" s="1"/>
-      <c r="U17" s="1"/>
-      <c r="V17" s="1"/>
-      <c r="W17" s="1"/>
-      <c r="X17" s="1"/>
-      <c r="Y17" s="1"/>
-      <c r="Z17" s="1"/>
-      <c r="AA17" s="1"/>
-      <c r="AB17" s="1" t="s">
+      <c r="AA17" t="s">
         <v>1880</v>
       </c>
-      <c r="AC17" s="1"/>
-      <c r="AD17" s="1"/>
-      <c r="AE17" s="1"/>
-      <c r="AF17" s="1"/>
-      <c r="AG17" s="1"/>
-      <c r="AH17" s="1" t="s">
+      <c r="AG17" t="s">
         <v>370</v>
       </c>
-      <c r="AI17" s="1"/>
-      <c r="AJ17" s="1"/>
-      <c r="AK17" s="1"/>
-      <c r="AL17" s="1"/>
-      <c r="AM17" s="1"/>
-      <c r="AN17" s="1"/>
-      <c r="AO17" s="1"/>
-      <c r="AP17" s="1"/>
-      <c r="AQ17" s="1"/>
-      <c r="AR17" s="1" t="s">
+      <c r="AQ17" t="s">
         <v>1609</v>
       </c>
-      <c r="AS17" s="1"/>
-      <c r="AT17" s="1"/>
-      <c r="AU17" s="1"/>
-      <c r="AV17" s="1"/>
-      <c r="AW17" s="1"/>
-      <c r="AX17" s="1" t="s">
+      <c r="AW17" t="s">
         <v>1722</v>
       </c>
-      <c r="AY17" s="1"/>
-      <c r="AZ17" s="1"/>
-      <c r="BA17" s="1"/>
-      <c r="BB17" s="1"/>
-      <c r="BC17" s="1"/>
-      <c r="BD17" s="1"/>
-      <c r="BE17" s="1"/>
-      <c r="BF17" s="1"/>
-      <c r="BG17" s="1"/>
-      <c r="BH17" s="1"/>
-      <c r="BI17" s="1" t="s">
+      <c r="BH17" t="s">
         <v>1353</v>
       </c>
-      <c r="BJ17" s="1"/>
-      <c r="BK17" s="1"/>
-      <c r="BL17" s="1"/>
-    </row>
-    <row r="18" spans="1:64">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1" t="s">
+      <c r="BJ17" t="s">
+        <v>1555</v>
+      </c>
+    </row>
+    <row r="18" spans="3:62">
+      <c r="C18" t="s">
         <v>1320</v>
       </c>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1" t="s">
+      <c r="F18" t="s">
         <v>1489</v>
       </c>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
-      <c r="P18" s="1" t="s">
+      <c r="O18" t="s">
         <v>2049</v>
       </c>
-      <c r="Q18" s="1"/>
-      <c r="R18" s="1" t="s">
+      <c r="Q18" t="s">
         <v>2050</v>
       </c>
-      <c r="S18" s="1"/>
-      <c r="T18" s="1"/>
-      <c r="U18" s="1"/>
-      <c r="V18" s="1"/>
-      <c r="W18" s="1"/>
-      <c r="X18" s="1"/>
-      <c r="Y18" s="1"/>
-      <c r="Z18" s="1"/>
-      <c r="AA18" s="1"/>
-      <c r="AB18" s="1" t="s">
+      <c r="AA18" t="s">
         <v>1439</v>
       </c>
-      <c r="AC18" s="1"/>
-      <c r="AD18" s="1"/>
-      <c r="AE18" s="1"/>
-      <c r="AF18" s="1"/>
-      <c r="AG18" s="1"/>
-      <c r="AH18" s="1" t="s">
+      <c r="AG18" t="s">
         <v>2051</v>
       </c>
-      <c r="AI18" s="1"/>
-      <c r="AJ18" s="1"/>
-      <c r="AK18" s="1"/>
-      <c r="AL18" s="1"/>
-      <c r="AM18" s="1"/>
-      <c r="AN18" s="1"/>
-      <c r="AO18" s="1"/>
-      <c r="AP18" s="1"/>
-      <c r="AQ18" s="1"/>
-      <c r="AR18" s="1" t="s">
+      <c r="AQ18" t="s">
         <v>271</v>
       </c>
-      <c r="AS18" s="1"/>
-      <c r="AT18" s="1"/>
-      <c r="AU18" s="1"/>
-      <c r="AV18" s="1"/>
-      <c r="AW18" s="1"/>
-      <c r="AX18" s="1" t="s">
+      <c r="AW18" t="s">
         <v>919</v>
       </c>
-      <c r="AY18" s="1"/>
-      <c r="AZ18" s="1"/>
-      <c r="BA18" s="1"/>
-      <c r="BB18" s="1"/>
-      <c r="BC18" s="1"/>
-      <c r="BD18" s="1"/>
-      <c r="BE18" s="1"/>
-      <c r="BF18" s="1"/>
-      <c r="BG18" s="1"/>
-      <c r="BH18" s="1"/>
-      <c r="BI18" s="1" t="s">
+      <c r="BH18" t="s">
         <v>1383</v>
       </c>
-      <c r="BJ18" s="1"/>
-      <c r="BK18" s="1"/>
-      <c r="BL18" s="1"/>
-    </row>
-    <row r="19" spans="1:64">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1" t="s">
+    </row>
+    <row r="19" spans="3:62">
+      <c r="C19" t="s">
         <v>1355</v>
       </c>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1" t="s">
+      <c r="F19" t="s">
         <v>1516</v>
       </c>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1" t="s">
+      <c r="O19" t="s">
         <v>2052</v>
       </c>
-      <c r="Q19" s="1"/>
-      <c r="R19" s="1" t="s">
+      <c r="Q19" t="s">
         <v>2053</v>
       </c>
-      <c r="S19" s="1"/>
-      <c r="T19" s="1"/>
-      <c r="U19" s="1"/>
-      <c r="V19" s="1"/>
-      <c r="W19" s="1"/>
-      <c r="X19" s="1"/>
-      <c r="Y19" s="1"/>
-      <c r="Z19" s="1"/>
-      <c r="AA19" s="1"/>
-      <c r="AB19" s="1" t="s">
+      <c r="AA19" t="s">
         <v>1557</v>
       </c>
-      <c r="AC19" s="1"/>
-      <c r="AD19" s="1"/>
-      <c r="AE19" s="1"/>
-      <c r="AF19" s="1"/>
-      <c r="AG19" s="1"/>
-      <c r="AH19" s="1" t="s">
+      <c r="AG19" t="s">
         <v>2054</v>
       </c>
-      <c r="AI19" s="1"/>
-      <c r="AJ19" s="1"/>
-      <c r="AK19" s="1"/>
-      <c r="AL19" s="1"/>
-      <c r="AM19" s="1"/>
-      <c r="AN19" s="1"/>
-      <c r="AO19" s="1"/>
-      <c r="AP19" s="1"/>
-      <c r="AQ19" s="1"/>
-      <c r="AR19" s="1" t="s">
+      <c r="AQ19" t="s">
         <v>1637</v>
       </c>
-      <c r="AS19" s="1"/>
-      <c r="AT19" s="1"/>
-      <c r="AU19" s="1"/>
-      <c r="AV19" s="1"/>
-      <c r="AW19" s="1"/>
-      <c r="AX19" s="1" t="s">
+      <c r="AW19" t="s">
         <v>989</v>
       </c>
-      <c r="AY19" s="1"/>
-      <c r="AZ19" s="1"/>
-      <c r="BA19" s="1"/>
-      <c r="BB19" s="1"/>
-      <c r="BC19" s="1"/>
-      <c r="BD19" s="1"/>
-      <c r="BE19" s="1"/>
-      <c r="BF19" s="1"/>
-      <c r="BG19" s="1"/>
-      <c r="BH19" s="1"/>
-      <c r="BI19" s="1"/>
-      <c r="BJ19" s="1"/>
-      <c r="BK19" s="1"/>
-      <c r="BL19" s="1"/>
-    </row>
-    <row r="20" spans="1:64">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1" t="s">
+      <c r="BH19" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="20" spans="3:62">
+      <c r="C20" t="s">
         <v>1384</v>
       </c>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1" t="s">
+      <c r="F20" t="s">
         <v>1487</v>
       </c>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-      <c r="P20" s="1" t="s">
+      <c r="O20" t="s">
         <v>2055</v>
       </c>
-      <c r="Q20" s="1"/>
-      <c r="R20" s="1" t="s">
+      <c r="Q20" t="s">
         <v>2056</v>
       </c>
-      <c r="S20" s="1"/>
-      <c r="T20" s="1"/>
-      <c r="U20" s="1"/>
-      <c r="V20" s="1"/>
-      <c r="W20" s="1"/>
-      <c r="X20" s="1"/>
-      <c r="Y20" s="1"/>
-      <c r="Z20" s="1"/>
-      <c r="AA20" s="1"/>
-      <c r="AB20" s="1" t="s">
+      <c r="AA20" t="s">
         <v>1290</v>
       </c>
-      <c r="AC20" s="1"/>
-      <c r="AD20" s="1"/>
-      <c r="AE20" s="1"/>
-      <c r="AF20" s="1"/>
-      <c r="AG20" s="1"/>
-      <c r="AH20" s="1" t="s">
+      <c r="AG20" t="s">
         <v>2057</v>
       </c>
-      <c r="AI20" s="1"/>
-      <c r="AJ20" s="1"/>
-      <c r="AK20" s="1"/>
-      <c r="AL20" s="1"/>
-      <c r="AM20" s="1"/>
-      <c r="AN20" s="1"/>
-      <c r="AO20" s="1"/>
-      <c r="AP20" s="1"/>
-      <c r="AQ20" s="1"/>
-      <c r="AR20" s="1" t="s">
+      <c r="AQ20" t="s">
         <v>889</v>
       </c>
-      <c r="AS20" s="1"/>
-      <c r="AT20" s="1"/>
-      <c r="AU20" s="1"/>
-      <c r="AV20" s="1"/>
-      <c r="AW20" s="1"/>
-      <c r="AX20" s="1" t="s">
+      <c r="AW20" t="s">
         <v>1744</v>
       </c>
-      <c r="AY20" s="1"/>
-      <c r="AZ20" s="1"/>
-      <c r="BA20" s="1"/>
-      <c r="BB20" s="1"/>
-      <c r="BC20" s="1"/>
-      <c r="BD20" s="1"/>
-      <c r="BE20" s="1"/>
-      <c r="BF20" s="1"/>
-      <c r="BG20" s="1"/>
-      <c r="BH20" s="1"/>
-      <c r="BI20" s="1"/>
-      <c r="BJ20" s="1"/>
-      <c r="BK20" s="1"/>
-      <c r="BL20" s="1"/>
-    </row>
-    <row r="21" spans="1:64">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1" t="s">
+    </row>
+    <row r="21" spans="3:62">
+      <c r="C21" t="s">
         <v>1405</v>
       </c>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1" t="s">
+      <c r="F21" t="s">
         <v>1559</v>
       </c>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-      <c r="P21" s="1" t="s">
+      <c r="O21" t="s">
         <v>2058</v>
       </c>
-      <c r="Q21" s="1"/>
-      <c r="R21" s="1" t="s">
+      <c r="Q21" t="s">
         <v>2059</v>
       </c>
-      <c r="S21" s="1"/>
-      <c r="T21" s="1"/>
-      <c r="U21" s="1"/>
-      <c r="V21" s="1"/>
-      <c r="W21" s="1"/>
-      <c r="X21" s="1"/>
-      <c r="Y21" s="1"/>
-      <c r="Z21" s="1"/>
-      <c r="AA21" s="1"/>
-      <c r="AB21" s="1" t="s">
+      <c r="AA21" t="s">
         <v>1750</v>
       </c>
-      <c r="AC21" s="1"/>
-      <c r="AD21" s="1"/>
-      <c r="AE21" s="1"/>
-      <c r="AF21" s="1"/>
-      <c r="AG21" s="1"/>
-      <c r="AH21" s="1" t="s">
+      <c r="AG21" t="s">
         <v>1961</v>
       </c>
-      <c r="AI21" s="1"/>
-      <c r="AJ21" s="1"/>
-      <c r="AK21" s="1"/>
-      <c r="AL21" s="1"/>
-      <c r="AM21" s="1"/>
-      <c r="AN21" s="1"/>
-      <c r="AO21" s="1"/>
-      <c r="AP21" s="1"/>
-      <c r="AQ21" s="1"/>
-      <c r="AR21" s="1" t="s">
+      <c r="AQ21" t="s">
         <v>1843</v>
       </c>
-      <c r="AS21" s="1"/>
-      <c r="AT21" s="1"/>
-      <c r="AU21" s="1"/>
-      <c r="AV21" s="1"/>
-      <c r="AW21" s="1"/>
-      <c r="AX21" s="1" t="s">
+      <c r="AW21" t="s">
         <v>901</v>
       </c>
-      <c r="AY21" s="1"/>
-      <c r="AZ21" s="1"/>
-      <c r="BA21" s="1"/>
-      <c r="BB21" s="1"/>
-      <c r="BC21" s="1"/>
-      <c r="BD21" s="1"/>
-      <c r="BE21" s="1"/>
-      <c r="BF21" s="1"/>
-      <c r="BG21" s="1"/>
-      <c r="BH21" s="1"/>
-      <c r="BI21" s="1"/>
-      <c r="BJ21" s="1"/>
-      <c r="BK21" s="1"/>
-      <c r="BL21" s="1"/>
-    </row>
-    <row r="22" spans="1:64">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1" t="s">
+    </row>
+    <row r="22" spans="3:62">
+      <c r="C22" t="s">
         <v>1431</v>
       </c>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1" t="s">
+      <c r="F22" t="s">
         <v>1578</v>
       </c>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1" t="s">
+      <c r="O22" t="s">
         <v>525</v>
       </c>
-      <c r="Q22" s="1"/>
-      <c r="R22" s="1" t="s">
+      <c r="Q22" t="s">
         <v>2060</v>
       </c>
-      <c r="S22" s="1"/>
-      <c r="T22" s="1"/>
-      <c r="U22" s="1"/>
-      <c r="V22" s="1"/>
-      <c r="W22" s="1"/>
-      <c r="X22" s="1"/>
-      <c r="Y22" s="1"/>
-      <c r="Z22" s="1"/>
-      <c r="AA22" s="1"/>
-      <c r="AB22" s="1"/>
-      <c r="AC22" s="1"/>
-      <c r="AD22" s="1"/>
-      <c r="AE22" s="1"/>
-      <c r="AF22" s="1"/>
-      <c r="AG22" s="1"/>
-      <c r="AH22" s="1" t="s">
+      <c r="AA22" t="s">
+        <v>1462</v>
+      </c>
+      <c r="AG22" t="s">
         <v>1978</v>
       </c>
-      <c r="AI22" s="1"/>
-      <c r="AJ22" s="1"/>
-      <c r="AK22" s="1"/>
-      <c r="AL22" s="1"/>
-      <c r="AM22" s="1"/>
-      <c r="AN22" s="1"/>
-      <c r="AO22" s="1"/>
-      <c r="AP22" s="1"/>
-      <c r="AQ22" s="1"/>
-      <c r="AR22" s="1" t="s">
+      <c r="AQ22" t="s">
         <v>1848</v>
       </c>
-      <c r="AS22" s="1"/>
-      <c r="AT22" s="1"/>
-      <c r="AU22" s="1"/>
-      <c r="AV22" s="1"/>
-      <c r="AW22" s="1"/>
-      <c r="AX22" s="1" t="s">
+      <c r="AW22" t="s">
         <v>1336</v>
       </c>
-      <c r="AY22" s="1"/>
-      <c r="AZ22" s="1"/>
-      <c r="BA22" s="1"/>
-      <c r="BB22" s="1"/>
-      <c r="BC22" s="1"/>
-      <c r="BD22" s="1"/>
-      <c r="BE22" s="1"/>
-      <c r="BF22" s="1"/>
-      <c r="BG22" s="1"/>
-      <c r="BH22" s="1"/>
-      <c r="BI22" s="1"/>
-      <c r="BJ22" s="1"/>
-      <c r="BK22" s="1"/>
-      <c r="BL22" s="1"/>
-    </row>
-    <row r="23" spans="1:64">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1" t="s">
+    </row>
+    <row r="23" spans="3:62">
+      <c r="C23" t="s">
         <v>1456</v>
       </c>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1" t="s">
+      <c r="F23" t="s">
         <v>1177</v>
       </c>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
-      <c r="P23" s="1" t="s">
+      <c r="O23" t="s">
         <v>2061</v>
       </c>
-      <c r="Q23" s="1"/>
-      <c r="R23" s="1" t="s">
+      <c r="Q23" t="s">
         <v>2062</v>
       </c>
-      <c r="S23" s="1"/>
-      <c r="T23" s="1"/>
-      <c r="U23" s="1"/>
-      <c r="V23" s="1"/>
-      <c r="W23" s="1"/>
-      <c r="X23" s="1"/>
-      <c r="Y23" s="1"/>
-      <c r="Z23" s="1"/>
-      <c r="AA23" s="1"/>
-      <c r="AB23" s="1"/>
-      <c r="AC23" s="1"/>
-      <c r="AD23" s="1"/>
-      <c r="AE23" s="1"/>
-      <c r="AF23" s="1"/>
-      <c r="AG23" s="1"/>
-      <c r="AH23" s="1" t="s">
+      <c r="AG23" t="s">
         <v>1990</v>
       </c>
-      <c r="AI23" s="1"/>
-      <c r="AJ23" s="1"/>
-      <c r="AK23" s="1"/>
-      <c r="AL23" s="1"/>
-      <c r="AM23" s="1"/>
-      <c r="AN23" s="1"/>
-      <c r="AO23" s="1"/>
-      <c r="AP23" s="1"/>
-      <c r="AQ23" s="1"/>
-      <c r="AR23" s="1" t="s">
+      <c r="AQ23" t="s">
         <v>1827</v>
       </c>
-      <c r="AS23" s="1"/>
-      <c r="AT23" s="1"/>
-      <c r="AU23" s="1"/>
-      <c r="AV23" s="1"/>
-      <c r="AW23" s="1"/>
-      <c r="AX23" s="1" t="s">
+      <c r="AW23" t="s">
         <v>1115</v>
       </c>
-      <c r="AY23" s="1"/>
-      <c r="AZ23" s="1"/>
-      <c r="BA23" s="1"/>
-      <c r="BB23" s="1"/>
-      <c r="BC23" s="1"/>
-      <c r="BD23" s="1"/>
-      <c r="BE23" s="1"/>
-      <c r="BF23" s="1"/>
-      <c r="BG23" s="1"/>
-      <c r="BH23" s="1"/>
-      <c r="BI23" s="1"/>
-      <c r="BJ23" s="1"/>
-      <c r="BK23" s="1"/>
-      <c r="BL23" s="1"/>
-    </row>
-    <row r="24" spans="1:64">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1" t="s">
+    </row>
+    <row r="24" spans="3:62">
+      <c r="C24" t="s">
         <v>1480</v>
       </c>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1" t="s">
+      <c r="F24" t="s">
         <v>1605</v>
       </c>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1" t="s">
+      <c r="O24" t="s">
         <v>590</v>
       </c>
-      <c r="Q24" s="1"/>
-      <c r="R24" s="1" t="s">
+      <c r="Q24" t="s">
         <v>2063</v>
       </c>
-      <c r="S24" s="1"/>
-      <c r="T24" s="1"/>
-      <c r="U24" s="1"/>
-      <c r="V24" s="1"/>
-      <c r="W24" s="1"/>
-      <c r="X24" s="1"/>
-      <c r="Y24" s="1"/>
-      <c r="Z24" s="1"/>
-      <c r="AA24" s="1"/>
-      <c r="AB24" s="1"/>
-      <c r="AC24" s="1"/>
-      <c r="AD24" s="1"/>
-      <c r="AE24" s="1"/>
-      <c r="AF24" s="1"/>
-      <c r="AG24" s="1"/>
-      <c r="AH24" s="1" t="s">
+      <c r="AG24" t="s">
         <v>2064</v>
       </c>
-      <c r="AI24" s="1"/>
-      <c r="AJ24" s="1"/>
-      <c r="AK24" s="1"/>
-      <c r="AL24" s="1"/>
-      <c r="AM24" s="1"/>
-      <c r="AN24" s="1"/>
-      <c r="AO24" s="1"/>
-      <c r="AP24" s="1"/>
-      <c r="AQ24" s="1"/>
-      <c r="AR24" s="1" t="s">
+      <c r="AQ24" t="s">
         <v>1837</v>
       </c>
-      <c r="AS24" s="1"/>
-      <c r="AT24" s="1"/>
-      <c r="AU24" s="1"/>
-      <c r="AV24" s="1"/>
-      <c r="AW24" s="1"/>
-      <c r="AX24" s="1" t="s">
+      <c r="AW24" t="s">
         <v>1777</v>
       </c>
-      <c r="AY24" s="1"/>
-      <c r="AZ24" s="1"/>
-      <c r="BA24" s="1"/>
-      <c r="BB24" s="1"/>
-      <c r="BC24" s="1"/>
-      <c r="BD24" s="1"/>
-      <c r="BE24" s="1"/>
-      <c r="BF24" s="1"/>
-      <c r="BG24" s="1"/>
-      <c r="BH24" s="1"/>
-      <c r="BI24" s="1"/>
-      <c r="BJ24" s="1"/>
-      <c r="BK24" s="1"/>
-      <c r="BL24" s="1"/>
-    </row>
-    <row r="25" spans="1:64">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1" t="s">
+    </row>
+    <row r="25" spans="3:62">
+      <c r="C25" t="s">
         <v>1508</v>
       </c>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-      <c r="P25" s="1" t="s">
+      <c r="F25" t="s">
+        <v>1618</v>
+      </c>
+      <c r="O25" t="s">
         <v>2065</v>
       </c>
-      <c r="Q25" s="1"/>
-      <c r="R25" s="1" t="s">
+      <c r="Q25" t="s">
         <v>2066</v>
       </c>
-      <c r="S25" s="1"/>
-      <c r="T25" s="1"/>
-      <c r="U25" s="1"/>
-      <c r="V25" s="1"/>
-      <c r="W25" s="1"/>
-      <c r="X25" s="1"/>
-      <c r="Y25" s="1"/>
-      <c r="Z25" s="1"/>
-      <c r="AA25" s="1"/>
-      <c r="AB25" s="1"/>
-      <c r="AC25" s="1"/>
-      <c r="AD25" s="1"/>
-      <c r="AE25" s="1"/>
-      <c r="AF25" s="1"/>
-      <c r="AG25" s="1"/>
-      <c r="AH25" s="1" t="s">
+      <c r="AG25" t="s">
         <v>2067</v>
       </c>
-      <c r="AI25" s="1"/>
-      <c r="AJ25" s="1"/>
-      <c r="AK25" s="1"/>
-      <c r="AL25" s="1"/>
-      <c r="AM25" s="1"/>
-      <c r="AN25" s="1"/>
-      <c r="AO25" s="1"/>
-      <c r="AP25" s="1"/>
-      <c r="AQ25" s="1"/>
-      <c r="AR25" s="1" t="s">
+      <c r="AQ25" t="s">
         <v>926</v>
       </c>
-      <c r="AS25" s="1"/>
-      <c r="AT25" s="1"/>
-      <c r="AU25" s="1"/>
-      <c r="AV25" s="1"/>
-      <c r="AW25" s="1"/>
-      <c r="AX25" s="1" t="s">
+      <c r="AW25" t="s">
         <v>1171</v>
       </c>
-      <c r="AY25" s="1"/>
-      <c r="AZ25" s="1"/>
-      <c r="BA25" s="1"/>
-      <c r="BB25" s="1"/>
-      <c r="BC25" s="1"/>
-      <c r="BD25" s="1"/>
-      <c r="BE25" s="1"/>
-      <c r="BF25" s="1"/>
-      <c r="BG25" s="1"/>
-      <c r="BH25" s="1"/>
-      <c r="BI25" s="1"/>
-      <c r="BJ25" s="1"/>
-      <c r="BK25" s="1"/>
-      <c r="BL25" s="1"/>
-    </row>
-    <row r="26" spans="1:64">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1" t="s">
+    </row>
+    <row r="26" spans="3:62">
+      <c r="C26" t="s">
         <v>703</v>
       </c>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
-      <c r="P26" s="1" t="s">
+      <c r="O26" t="s">
         <v>807</v>
       </c>
-      <c r="Q26" s="1"/>
-      <c r="R26" s="1" t="s">
+      <c r="Q26" t="s">
         <v>1963</v>
       </c>
-      <c r="S26" s="1"/>
-      <c r="T26" s="1"/>
-      <c r="U26" s="1"/>
-      <c r="V26" s="1"/>
-      <c r="W26" s="1"/>
-      <c r="X26" s="1"/>
-      <c r="Y26" s="1"/>
-      <c r="Z26" s="1"/>
-      <c r="AA26" s="1"/>
-      <c r="AB26" s="1"/>
-      <c r="AC26" s="1"/>
-      <c r="AD26" s="1"/>
-      <c r="AE26" s="1"/>
-      <c r="AF26" s="1"/>
-      <c r="AG26" s="1"/>
-      <c r="AH26" s="1" t="s">
+      <c r="AG26" t="s">
         <v>376</v>
       </c>
-      <c r="AI26" s="1"/>
-      <c r="AJ26" s="1"/>
-      <c r="AK26" s="1"/>
-      <c r="AL26" s="1"/>
-      <c r="AM26" s="1"/>
-      <c r="AN26" s="1"/>
-      <c r="AO26" s="1"/>
-      <c r="AP26" s="1"/>
-      <c r="AQ26" s="1"/>
-      <c r="AR26" s="1" t="s">
+      <c r="AQ26" t="s">
         <v>991</v>
       </c>
-      <c r="AS26" s="1"/>
-      <c r="AT26" s="1"/>
-      <c r="AU26" s="1"/>
-      <c r="AV26" s="1"/>
-      <c r="AW26" s="1"/>
-      <c r="AX26" s="1" t="s">
+      <c r="AW26" t="s">
         <v>1754</v>
       </c>
-      <c r="AY26" s="1"/>
-      <c r="AZ26" s="1"/>
-      <c r="BA26" s="1"/>
-      <c r="BB26" s="1"/>
-      <c r="BC26" s="1"/>
-      <c r="BD26" s="1"/>
-      <c r="BE26" s="1"/>
-      <c r="BF26" s="1"/>
-      <c r="BG26" s="1"/>
-      <c r="BH26" s="1"/>
-      <c r="BI26" s="1"/>
-      <c r="BJ26" s="1"/>
-      <c r="BK26" s="1"/>
-      <c r="BL26" s="1"/>
-    </row>
-    <row r="27" spans="1:64">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1" t="s">
+    </row>
+    <row r="27" spans="3:62">
+      <c r="C27" t="s">
         <v>677</v>
       </c>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-      <c r="P27" s="1" t="s">
+      <c r="O27" t="s">
         <v>2068</v>
       </c>
-      <c r="Q27" s="1"/>
-      <c r="R27" s="1" t="s">
+      <c r="Q27" t="s">
         <v>608</v>
       </c>
-      <c r="S27" s="1"/>
-      <c r="T27" s="1"/>
-      <c r="U27" s="1"/>
-      <c r="V27" s="1"/>
-      <c r="W27" s="1"/>
-      <c r="X27" s="1"/>
-      <c r="Y27" s="1"/>
-      <c r="Z27" s="1"/>
-      <c r="AA27" s="1"/>
-      <c r="AB27" s="1"/>
-      <c r="AC27" s="1"/>
-      <c r="AD27" s="1"/>
-      <c r="AE27" s="1"/>
-      <c r="AF27" s="1"/>
-      <c r="AG27" s="1"/>
-      <c r="AH27" s="1" t="s">
+      <c r="AG27" t="s">
         <v>991</v>
       </c>
-      <c r="AI27" s="1"/>
-      <c r="AJ27" s="1"/>
-      <c r="AK27" s="1"/>
-      <c r="AL27" s="1"/>
-      <c r="AM27" s="1"/>
-      <c r="AN27" s="1"/>
-      <c r="AO27" s="1"/>
-      <c r="AP27" s="1"/>
-      <c r="AQ27" s="1"/>
-      <c r="AR27" s="1" t="s">
+      <c r="AQ27" t="s">
         <v>1642</v>
       </c>
-      <c r="AS27" s="1"/>
-      <c r="AT27" s="1"/>
-      <c r="AU27" s="1"/>
-      <c r="AV27" s="1"/>
-      <c r="AW27" s="1"/>
-      <c r="AX27" s="1" t="s">
+      <c r="AW27" t="s">
         <v>1222</v>
       </c>
-      <c r="AY27" s="1"/>
-      <c r="AZ27" s="1"/>
-      <c r="BA27" s="1"/>
-      <c r="BB27" s="1"/>
-      <c r="BC27" s="1"/>
-      <c r="BD27" s="1"/>
-      <c r="BE27" s="1"/>
-      <c r="BF27" s="1"/>
-      <c r="BG27" s="1"/>
-      <c r="BH27" s="1"/>
-      <c r="BI27" s="1"/>
-      <c r="BJ27" s="1"/>
-      <c r="BK27" s="1"/>
-      <c r="BL27" s="1"/>
-    </row>
-    <row r="28" spans="1:64">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-      <c r="P28" s="1" t="s">
+    </row>
+    <row r="28" spans="3:62">
+      <c r="C28" t="s">
+        <v>647</v>
+      </c>
+      <c r="O28" t="s">
         <v>2069</v>
       </c>
-      <c r="Q28" s="1"/>
-      <c r="R28" s="1" t="s">
+      <c r="Q28" t="s">
         <v>644</v>
       </c>
-      <c r="S28" s="1"/>
-      <c r="T28" s="1"/>
-      <c r="U28" s="1"/>
-      <c r="V28" s="1"/>
-      <c r="W28" s="1"/>
-      <c r="X28" s="1"/>
-      <c r="Y28" s="1"/>
-      <c r="Z28" s="1"/>
-      <c r="AA28" s="1"/>
-      <c r="AB28" s="1"/>
-      <c r="AC28" s="1"/>
-      <c r="AD28" s="1"/>
-      <c r="AE28" s="1"/>
-      <c r="AF28" s="1"/>
-      <c r="AG28" s="1"/>
-      <c r="AH28" s="1" t="s">
+      <c r="AG28" t="s">
         <v>2045</v>
       </c>
-      <c r="AI28" s="1"/>
-      <c r="AJ28" s="1"/>
-      <c r="AK28" s="1"/>
-      <c r="AL28" s="1"/>
-      <c r="AM28" s="1"/>
-      <c r="AN28" s="1"/>
-      <c r="AO28" s="1"/>
-      <c r="AP28" s="1"/>
-      <c r="AQ28" s="1"/>
-      <c r="AR28" s="1" t="s">
+      <c r="AQ28" t="s">
         <v>553</v>
       </c>
-      <c r="AS28" s="1"/>
-      <c r="AT28" s="1"/>
-      <c r="AU28" s="1"/>
-      <c r="AV28" s="1"/>
-      <c r="AW28" s="1"/>
-      <c r="AX28" s="1" t="s">
+      <c r="AW28" t="s">
         <v>1267</v>
       </c>
-      <c r="AY28" s="1"/>
-      <c r="AZ28" s="1"/>
-      <c r="BA28" s="1"/>
-      <c r="BB28" s="1"/>
-      <c r="BC28" s="1"/>
-      <c r="BD28" s="1"/>
-      <c r="BE28" s="1"/>
-      <c r="BF28" s="1"/>
-      <c r="BG28" s="1"/>
-      <c r="BH28" s="1"/>
-      <c r="BI28" s="1"/>
-      <c r="BJ28" s="1"/>
-      <c r="BK28" s="1"/>
-      <c r="BL28" s="1"/>
-    </row>
-    <row r="29" spans="1:64">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-      <c r="P29" s="1" t="s">
+    </row>
+    <row r="29" spans="3:62">
+      <c r="O29" t="s">
         <v>2070</v>
       </c>
-      <c r="Q29" s="1"/>
-      <c r="R29" s="1" t="s">
+      <c r="Q29" t="s">
         <v>366</v>
       </c>
-      <c r="S29" s="1"/>
-      <c r="T29" s="1"/>
-      <c r="U29" s="1"/>
-      <c r="V29" s="1"/>
-      <c r="W29" s="1"/>
-      <c r="X29" s="1"/>
-      <c r="Y29" s="1"/>
-      <c r="Z29" s="1"/>
-      <c r="AA29" s="1"/>
-      <c r="AB29" s="1"/>
-      <c r="AC29" s="1"/>
-      <c r="AD29" s="1"/>
-      <c r="AE29" s="1"/>
-      <c r="AF29" s="1"/>
-      <c r="AG29" s="1"/>
-      <c r="AH29" s="1" t="s">
+      <c r="AG29" t="s">
         <v>2071</v>
       </c>
-      <c r="AI29" s="1"/>
-      <c r="AJ29" s="1"/>
-      <c r="AK29" s="1"/>
-      <c r="AL29" s="1"/>
-      <c r="AM29" s="1"/>
-      <c r="AN29" s="1"/>
-      <c r="AO29" s="1"/>
-      <c r="AP29" s="1"/>
-      <c r="AQ29" s="1"/>
-      <c r="AR29" s="1" t="s">
+      <c r="AQ29" t="s">
         <v>2072</v>
       </c>
-      <c r="AS29" s="1"/>
-      <c r="AT29" s="1"/>
-      <c r="AU29" s="1"/>
-      <c r="AV29" s="1"/>
-      <c r="AW29" s="1"/>
-      <c r="AX29" s="1" t="s">
+      <c r="AW29" t="s">
         <v>1763</v>
       </c>
-      <c r="AY29" s="1"/>
-      <c r="AZ29" s="1"/>
-      <c r="BA29" s="1"/>
-      <c r="BB29" s="1"/>
-      <c r="BC29" s="1"/>
-      <c r="BD29" s="1"/>
-      <c r="BE29" s="1"/>
-      <c r="BF29" s="1"/>
-      <c r="BG29" s="1"/>
-      <c r="BH29" s="1"/>
-      <c r="BI29" s="1"/>
-      <c r="BJ29" s="1"/>
-      <c r="BK29" s="1"/>
-      <c r="BL29" s="1"/>
-    </row>
-    <row r="30" spans="1:64">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1" t="s">
+    </row>
+    <row r="30" spans="3:62">
+      <c r="O30" t="s">
         <v>608</v>
       </c>
-      <c r="Q30" s="1"/>
-      <c r="R30" s="1" t="s">
+      <c r="Q30" t="s">
         <v>1004</v>
       </c>
-      <c r="S30" s="1"/>
-      <c r="T30" s="1"/>
-      <c r="U30" s="1"/>
-      <c r="V30" s="1"/>
-      <c r="W30" s="1"/>
-      <c r="X30" s="1"/>
-      <c r="Y30" s="1"/>
-      <c r="Z30" s="1"/>
-      <c r="AA30" s="1"/>
-      <c r="AB30" s="1"/>
-      <c r="AC30" s="1"/>
-      <c r="AD30" s="1"/>
-      <c r="AE30" s="1"/>
-      <c r="AF30" s="1"/>
-      <c r="AG30" s="1"/>
-      <c r="AH30" s="1" t="s">
+      <c r="AG30" t="s">
         <v>2073</v>
       </c>
-      <c r="AI30" s="1"/>
-      <c r="AJ30" s="1"/>
-      <c r="AK30" s="1"/>
-      <c r="AL30" s="1"/>
-      <c r="AM30" s="1"/>
-      <c r="AN30" s="1"/>
-      <c r="AO30" s="1"/>
-      <c r="AP30" s="1"/>
-      <c r="AQ30" s="1"/>
-      <c r="AR30" s="1" t="s">
+      <c r="AQ30" t="s">
         <v>2074</v>
       </c>
-      <c r="AS30" s="1"/>
-      <c r="AT30" s="1"/>
-      <c r="AU30" s="1"/>
-      <c r="AV30" s="1"/>
-      <c r="AW30" s="1"/>
-      <c r="AX30" s="1" t="s">
+      <c r="AW30" t="s">
         <v>906</v>
       </c>
-      <c r="AY30" s="1"/>
-      <c r="AZ30" s="1"/>
-      <c r="BA30" s="1"/>
-      <c r="BB30" s="1"/>
-      <c r="BC30" s="1"/>
-      <c r="BD30" s="1"/>
-      <c r="BE30" s="1"/>
-      <c r="BF30" s="1"/>
-      <c r="BG30" s="1"/>
-      <c r="BH30" s="1"/>
-      <c r="BI30" s="1"/>
-      <c r="BJ30" s="1"/>
-      <c r="BK30" s="1"/>
-      <c r="BL30" s="1"/>
-    </row>
-    <row r="31" spans="1:64">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-      <c r="P31" s="1" t="s">
+    </row>
+    <row r="31" spans="3:62">
+      <c r="O31" t="s">
         <v>644</v>
       </c>
-      <c r="Q31" s="1"/>
-      <c r="R31" s="1" t="s">
+      <c r="Q31" t="s">
         <v>1069</v>
       </c>
-      <c r="S31" s="1"/>
-      <c r="T31" s="1"/>
-      <c r="U31" s="1"/>
-      <c r="V31" s="1"/>
-      <c r="W31" s="1"/>
-      <c r="X31" s="1"/>
-      <c r="Y31" s="1"/>
-      <c r="Z31" s="1"/>
-      <c r="AA31" s="1"/>
-      <c r="AB31" s="1"/>
-      <c r="AC31" s="1"/>
-      <c r="AD31" s="1"/>
-      <c r="AE31" s="1"/>
-      <c r="AF31" s="1"/>
-      <c r="AG31" s="1"/>
-      <c r="AH31" s="1" t="s">
+      <c r="AG31" t="s">
         <v>2075</v>
       </c>
-      <c r="AI31" s="1"/>
-      <c r="AJ31" s="1"/>
-      <c r="AK31" s="1"/>
-      <c r="AL31" s="1"/>
-      <c r="AM31" s="1"/>
-      <c r="AN31" s="1"/>
-      <c r="AO31" s="1"/>
-      <c r="AP31" s="1"/>
-      <c r="AQ31" s="1"/>
-      <c r="AR31" s="1"/>
-      <c r="AS31" s="1"/>
-      <c r="AT31" s="1"/>
-      <c r="AU31" s="1"/>
-      <c r="AV31" s="1"/>
-      <c r="AW31" s="1"/>
-      <c r="AX31" s="1" t="s">
+      <c r="AQ31" t="s">
+        <v>2203</v>
+      </c>
+      <c r="AW31" t="s">
         <v>1346</v>
       </c>
-      <c r="AY31" s="1"/>
-      <c r="AZ31" s="1"/>
-      <c r="BA31" s="1"/>
-      <c r="BB31" s="1"/>
-      <c r="BC31" s="1"/>
-      <c r="BD31" s="1"/>
-      <c r="BE31" s="1"/>
-      <c r="BF31" s="1"/>
-      <c r="BG31" s="1"/>
-      <c r="BH31" s="1"/>
-      <c r="BI31" s="1"/>
-      <c r="BJ31" s="1"/>
-      <c r="BK31" s="1"/>
-      <c r="BL31" s="1"/>
-    </row>
-    <row r="32" spans="1:64">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
-      <c r="P32" s="1" t="s">
+    </row>
+    <row r="32" spans="3:62">
+      <c r="O32" t="s">
         <v>435</v>
       </c>
-      <c r="Q32" s="1"/>
-      <c r="R32" s="1"/>
-      <c r="S32" s="1"/>
-      <c r="T32" s="1"/>
-      <c r="U32" s="1"/>
-      <c r="V32" s="1"/>
-      <c r="W32" s="1"/>
-      <c r="X32" s="1"/>
-      <c r="Y32" s="1"/>
-      <c r="Z32" s="1"/>
-      <c r="AA32" s="1"/>
-      <c r="AB32" s="1"/>
-      <c r="AC32" s="1"/>
-      <c r="AD32" s="1"/>
-      <c r="AE32" s="1"/>
-      <c r="AF32" s="1"/>
-      <c r="AG32" s="1"/>
-      <c r="AH32" s="1" t="s">
+      <c r="Q32" t="s">
+        <v>2080</v>
+      </c>
+      <c r="AG32" t="s">
         <v>636</v>
       </c>
-      <c r="AI32" s="1"/>
-      <c r="AJ32" s="1"/>
-      <c r="AK32" s="1"/>
-      <c r="AL32" s="1"/>
-      <c r="AM32" s="1"/>
-      <c r="AN32" s="1"/>
-      <c r="AO32" s="1"/>
-      <c r="AP32" s="1"/>
-      <c r="AQ32" s="1"/>
-      <c r="AR32" s="1"/>
-      <c r="AS32" s="1"/>
-      <c r="AT32" s="1"/>
-      <c r="AU32" s="1"/>
-      <c r="AV32" s="1"/>
-      <c r="AW32" s="1"/>
-      <c r="AX32" s="1" t="s">
+      <c r="AW32" t="s">
         <v>1376</v>
       </c>
-      <c r="AY32" s="1"/>
-      <c r="AZ32" s="1"/>
-      <c r="BA32" s="1"/>
-      <c r="BB32" s="1"/>
-      <c r="BC32" s="1"/>
-      <c r="BD32" s="1"/>
-      <c r="BE32" s="1"/>
-      <c r="BF32" s="1"/>
-      <c r="BG32" s="1"/>
-      <c r="BH32" s="1"/>
-      <c r="BI32" s="1"/>
-      <c r="BJ32" s="1"/>
-      <c r="BK32" s="1"/>
-      <c r="BL32" s="1"/>
-    </row>
-    <row r="33" spans="1:64">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
-      <c r="O33" s="1"/>
-      <c r="P33" s="1" t="s">
+    </row>
+    <row r="33" spans="15:49">
+      <c r="O33" t="s">
         <v>662</v>
       </c>
-      <c r="Q33" s="1"/>
-      <c r="R33" s="1"/>
-      <c r="S33" s="1"/>
-      <c r="T33" s="1"/>
-      <c r="U33" s="1"/>
-      <c r="V33" s="1"/>
-      <c r="W33" s="1"/>
-      <c r="X33" s="1"/>
-      <c r="Y33" s="1"/>
-      <c r="Z33" s="1"/>
-      <c r="AA33" s="1"/>
-      <c r="AB33" s="1"/>
-      <c r="AC33" s="1"/>
-      <c r="AD33" s="1"/>
-      <c r="AE33" s="1"/>
-      <c r="AF33" s="1"/>
-      <c r="AG33" s="1"/>
-      <c r="AH33" s="1" t="s">
+      <c r="AG33" t="s">
         <v>2076</v>
       </c>
-      <c r="AI33" s="1"/>
-      <c r="AJ33" s="1"/>
-      <c r="AK33" s="1"/>
-      <c r="AL33" s="1"/>
-      <c r="AM33" s="1"/>
-      <c r="AN33" s="1"/>
-      <c r="AO33" s="1"/>
-      <c r="AP33" s="1"/>
-      <c r="AQ33" s="1"/>
-      <c r="AR33" s="1"/>
-      <c r="AS33" s="1"/>
-      <c r="AT33" s="1"/>
-      <c r="AU33" s="1"/>
-      <c r="AV33" s="1"/>
-      <c r="AW33" s="1"/>
-      <c r="AX33" s="1" t="s">
+      <c r="AW33" t="s">
         <v>1397</v>
       </c>
-      <c r="AY33" s="1"/>
-      <c r="AZ33" s="1"/>
-      <c r="BA33" s="1"/>
-      <c r="BB33" s="1"/>
-      <c r="BC33" s="1"/>
-      <c r="BD33" s="1"/>
-      <c r="BE33" s="1"/>
-      <c r="BF33" s="1"/>
-      <c r="BG33" s="1"/>
-      <c r="BH33" s="1"/>
-      <c r="BI33" s="1"/>
-      <c r="BJ33" s="1"/>
-      <c r="BK33" s="1"/>
-      <c r="BL33" s="1"/>
-    </row>
-    <row r="34" spans="1:64">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
-      <c r="P34" s="1" t="s">
+    </row>
+    <row r="34" spans="15:49">
+      <c r="O34" t="s">
         <v>366</v>
       </c>
-      <c r="Q34" s="1"/>
-      <c r="R34" s="1"/>
-      <c r="S34" s="1"/>
-      <c r="T34" s="1"/>
-      <c r="U34" s="1"/>
-      <c r="V34" s="1"/>
-      <c r="W34" s="1"/>
-      <c r="X34" s="1"/>
-      <c r="Y34" s="1"/>
-      <c r="Z34" s="1"/>
-      <c r="AA34" s="1"/>
-      <c r="AB34" s="1"/>
-      <c r="AC34" s="1"/>
-      <c r="AD34" s="1"/>
-      <c r="AE34" s="1"/>
-      <c r="AF34" s="1"/>
-      <c r="AG34" s="1"/>
-      <c r="AH34" s="1" t="s">
+      <c r="AG34" t="s">
         <v>2077</v>
       </c>
-      <c r="AI34" s="1"/>
-      <c r="AJ34" s="1"/>
-      <c r="AK34" s="1"/>
-      <c r="AL34" s="1"/>
-      <c r="AM34" s="1"/>
-      <c r="AN34" s="1"/>
-      <c r="AO34" s="1"/>
-      <c r="AP34" s="1"/>
-      <c r="AQ34" s="1"/>
-      <c r="AR34" s="1"/>
-      <c r="AS34" s="1"/>
-      <c r="AT34" s="1"/>
-      <c r="AU34" s="1"/>
-      <c r="AV34" s="1"/>
-      <c r="AW34" s="1"/>
-      <c r="AX34" s="1" t="s">
+      <c r="AW34" t="s">
         <v>1424</v>
       </c>
-      <c r="AY34" s="1"/>
-      <c r="AZ34" s="1"/>
-      <c r="BA34" s="1"/>
-      <c r="BB34" s="1"/>
-      <c r="BC34" s="1"/>
-      <c r="BD34" s="1"/>
-      <c r="BE34" s="1"/>
-      <c r="BF34" s="1"/>
-      <c r="BG34" s="1"/>
-      <c r="BH34" s="1"/>
-      <c r="BI34" s="1"/>
-      <c r="BJ34" s="1"/>
-      <c r="BK34" s="1"/>
-      <c r="BL34" s="1"/>
-    </row>
-    <row r="35" spans="1:64">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
-      <c r="P35" s="1" t="s">
+    </row>
+    <row r="35" spans="15:49">
+      <c r="O35" t="s">
         <v>1043</v>
       </c>
-      <c r="Q35" s="1"/>
-      <c r="R35" s="1"/>
-      <c r="S35" s="1"/>
-      <c r="T35" s="1"/>
-      <c r="U35" s="1"/>
-      <c r="V35" s="1"/>
-      <c r="W35" s="1"/>
-      <c r="X35" s="1"/>
-      <c r="Y35" s="1"/>
-      <c r="Z35" s="1"/>
-      <c r="AA35" s="1"/>
-      <c r="AB35" s="1"/>
-      <c r="AC35" s="1"/>
-      <c r="AD35" s="1"/>
-      <c r="AE35" s="1"/>
-      <c r="AF35" s="1"/>
-      <c r="AG35" s="1"/>
-      <c r="AH35" s="1" t="s">
+      <c r="AG35" t="s">
         <v>2078</v>
       </c>
-      <c r="AI35" s="1"/>
-      <c r="AJ35" s="1"/>
-      <c r="AK35" s="1"/>
-      <c r="AL35" s="1"/>
-      <c r="AM35" s="1"/>
-      <c r="AN35" s="1"/>
-      <c r="AO35" s="1"/>
-      <c r="AP35" s="1"/>
-      <c r="AQ35" s="1"/>
-      <c r="AR35" s="1"/>
-      <c r="AS35" s="1"/>
-      <c r="AT35" s="1"/>
-      <c r="AU35" s="1"/>
-      <c r="AV35" s="1"/>
-      <c r="AW35" s="1"/>
-      <c r="AX35" s="1" t="s">
+      <c r="AW35" t="s">
         <v>897</v>
       </c>
-      <c r="AY35" s="1"/>
-      <c r="AZ35" s="1"/>
-      <c r="BA35" s="1"/>
-      <c r="BB35" s="1"/>
-      <c r="BC35" s="1"/>
-      <c r="BD35" s="1"/>
-      <c r="BE35" s="1"/>
-      <c r="BF35" s="1"/>
-      <c r="BG35" s="1"/>
-      <c r="BH35" s="1"/>
-      <c r="BI35" s="1"/>
-      <c r="BJ35" s="1"/>
-      <c r="BK35" s="1"/>
-      <c r="BL35" s="1"/>
-    </row>
-    <row r="36" spans="1:64">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
-      <c r="M36" s="1"/>
-      <c r="N36" s="1"/>
-      <c r="O36" s="1"/>
-      <c r="P36" s="1" t="s">
+    </row>
+    <row r="36" spans="15:49">
+      <c r="O36" t="s">
         <v>271</v>
       </c>
-      <c r="Q36" s="1"/>
-      <c r="R36" s="1"/>
-      <c r="S36" s="1"/>
-      <c r="T36" s="1"/>
-      <c r="U36" s="1"/>
-      <c r="V36" s="1"/>
-      <c r="W36" s="1"/>
-      <c r="X36" s="1"/>
-      <c r="Y36" s="1"/>
-      <c r="Z36" s="1"/>
-      <c r="AA36" s="1"/>
-      <c r="AB36" s="1"/>
-      <c r="AC36" s="1"/>
-      <c r="AD36" s="1"/>
-      <c r="AE36" s="1"/>
-      <c r="AF36" s="1"/>
-      <c r="AG36" s="1"/>
-      <c r="AH36" s="1" t="s">
+      <c r="AG36" t="s">
         <v>2079</v>
       </c>
-      <c r="AI36" s="1"/>
-      <c r="AJ36" s="1"/>
-      <c r="AK36" s="1"/>
-      <c r="AL36" s="1"/>
-      <c r="AM36" s="1"/>
-      <c r="AN36" s="1"/>
-      <c r="AO36" s="1"/>
-      <c r="AP36" s="1"/>
-      <c r="AQ36" s="1"/>
-      <c r="AR36" s="1"/>
-      <c r="AS36" s="1"/>
-      <c r="AT36" s="1"/>
-      <c r="AU36" s="1"/>
-      <c r="AV36" s="1"/>
-      <c r="AW36" s="1"/>
-      <c r="AX36" s="1" t="s">
+      <c r="AW36" t="s">
         <v>1563</v>
       </c>
-      <c r="AY36" s="1"/>
-      <c r="AZ36" s="1"/>
-      <c r="BA36" s="1"/>
-      <c r="BB36" s="1"/>
-      <c r="BC36" s="1"/>
-      <c r="BD36" s="1"/>
-      <c r="BE36" s="1"/>
-      <c r="BF36" s="1"/>
-      <c r="BG36" s="1"/>
-      <c r="BH36" s="1"/>
-      <c r="BI36" s="1"/>
-      <c r="BJ36" s="1"/>
-      <c r="BK36" s="1"/>
-      <c r="BL36" s="1"/>
-    </row>
-    <row r="37" spans="1:64">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
-      <c r="M37" s="1"/>
-      <c r="N37" s="1"/>
-      <c r="O37" s="1"/>
-      <c r="P37" s="1" t="s">
+    </row>
+    <row r="37" spans="15:49">
+      <c r="O37" t="s">
         <v>2080</v>
       </c>
-      <c r="Q37" s="1"/>
-      <c r="R37" s="1"/>
-      <c r="S37" s="1"/>
-      <c r="T37" s="1"/>
-      <c r="U37" s="1"/>
-      <c r="V37" s="1"/>
-      <c r="W37" s="1"/>
-      <c r="X37" s="1"/>
-      <c r="Y37" s="1"/>
-      <c r="Z37" s="1"/>
-      <c r="AA37" s="1"/>
-      <c r="AB37" s="1"/>
-      <c r="AC37" s="1"/>
-      <c r="AD37" s="1"/>
-      <c r="AE37" s="1"/>
-      <c r="AF37" s="1"/>
-      <c r="AG37" s="1"/>
-      <c r="AH37" s="1" t="s">
+      <c r="AG37" t="s">
         <v>2081</v>
       </c>
-      <c r="AI37" s="1"/>
-      <c r="AJ37" s="1"/>
-      <c r="AK37" s="1"/>
-      <c r="AL37" s="1"/>
-      <c r="AM37" s="1"/>
-      <c r="AN37" s="1"/>
-      <c r="AO37" s="1"/>
-      <c r="AP37" s="1"/>
-      <c r="AQ37" s="1"/>
-      <c r="AR37" s="1"/>
-      <c r="AS37" s="1"/>
-      <c r="AT37" s="1"/>
-      <c r="AU37" s="1"/>
-      <c r="AV37" s="1"/>
-      <c r="AW37" s="1"/>
-      <c r="AX37" s="1" t="s">
+      <c r="AW37" t="s">
         <v>1732</v>
       </c>
-      <c r="AY37" s="1"/>
-      <c r="AZ37" s="1"/>
-      <c r="BA37" s="1"/>
-      <c r="BB37" s="1"/>
-      <c r="BC37" s="1"/>
-      <c r="BD37" s="1"/>
-      <c r="BE37" s="1"/>
-      <c r="BF37" s="1"/>
-      <c r="BG37" s="1"/>
-      <c r="BH37" s="1"/>
-      <c r="BI37" s="1"/>
-      <c r="BJ37" s="1"/>
-      <c r="BK37" s="1"/>
-      <c r="BL37" s="1"/>
-    </row>
-    <row r="38" spans="1:64">
-      <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
-      <c r="M38" s="1"/>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
-      <c r="P38" s="1" t="s">
+    </row>
+    <row r="38" spans="15:49">
+      <c r="O38" t="s">
         <v>991</v>
       </c>
-      <c r="Q38" s="1"/>
-      <c r="R38" s="1"/>
-      <c r="S38" s="1"/>
-      <c r="T38" s="1"/>
-      <c r="U38" s="1"/>
-      <c r="V38" s="1"/>
-      <c r="W38" s="1"/>
-      <c r="X38" s="1"/>
-      <c r="Y38" s="1"/>
-      <c r="Z38" s="1"/>
-      <c r="AA38" s="1"/>
-      <c r="AB38" s="1"/>
-      <c r="AC38" s="1"/>
-      <c r="AD38" s="1"/>
-      <c r="AE38" s="1"/>
-      <c r="AF38" s="1"/>
-      <c r="AG38" s="1"/>
-      <c r="AH38" s="1" t="s">
+      <c r="AG38" t="s">
         <v>2082</v>
       </c>
-      <c r="AI38" s="1"/>
-      <c r="AJ38" s="1"/>
-      <c r="AK38" s="1"/>
-      <c r="AL38" s="1"/>
-      <c r="AM38" s="1"/>
-      <c r="AN38" s="1"/>
-      <c r="AO38" s="1"/>
-      <c r="AP38" s="1"/>
-      <c r="AQ38" s="1"/>
-      <c r="AR38" s="1"/>
-      <c r="AS38" s="1"/>
-      <c r="AT38" s="1"/>
-      <c r="AU38" s="1"/>
-      <c r="AV38" s="1"/>
-      <c r="AW38" s="1"/>
-      <c r="AX38" s="1" t="s">
+      <c r="AW38" t="s">
         <v>1501</v>
       </c>
-      <c r="AY38" s="1"/>
-      <c r="AZ38" s="1"/>
-      <c r="BA38" s="1"/>
-      <c r="BB38" s="1"/>
-      <c r="BC38" s="1"/>
-      <c r="BD38" s="1"/>
-      <c r="BE38" s="1"/>
-      <c r="BF38" s="1"/>
-      <c r="BG38" s="1"/>
-      <c r="BH38" s="1"/>
-      <c r="BI38" s="1"/>
-      <c r="BJ38" s="1"/>
-      <c r="BK38" s="1"/>
-      <c r="BL38" s="1"/>
-    </row>
-    <row r="39" spans="1:64">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
-      <c r="M39" s="1"/>
-      <c r="N39" s="1"/>
-      <c r="O39" s="1"/>
-      <c r="P39" s="1" t="s">
+    </row>
+    <row r="39" spans="15:49">
+      <c r="O39" t="s">
         <v>889</v>
       </c>
-      <c r="Q39" s="1"/>
-      <c r="R39" s="1"/>
-      <c r="S39" s="1"/>
-      <c r="T39" s="1"/>
-      <c r="U39" s="1"/>
-      <c r="V39" s="1"/>
-      <c r="W39" s="1"/>
-      <c r="X39" s="1"/>
-      <c r="Y39" s="1"/>
-      <c r="Z39" s="1"/>
-      <c r="AA39" s="1"/>
-      <c r="AB39" s="1"/>
-      <c r="AC39" s="1"/>
-      <c r="AD39" s="1"/>
-      <c r="AE39" s="1"/>
-      <c r="AF39" s="1"/>
-      <c r="AG39" s="1"/>
-      <c r="AH39" s="1" t="s">
+      <c r="AG39" t="s">
         <v>366</v>
       </c>
-      <c r="AI39" s="1"/>
-      <c r="AJ39" s="1"/>
-      <c r="AK39" s="1"/>
-      <c r="AL39" s="1"/>
-      <c r="AM39" s="1"/>
-      <c r="AN39" s="1"/>
-      <c r="AO39" s="1"/>
-      <c r="AP39" s="1"/>
-      <c r="AQ39" s="1"/>
-      <c r="AR39" s="1"/>
-      <c r="AS39" s="1"/>
-      <c r="AT39" s="1"/>
-      <c r="AU39" s="1"/>
-      <c r="AV39" s="1"/>
-      <c r="AW39" s="1"/>
-      <c r="AX39" s="1" t="s">
+      <c r="AW39" t="s">
         <v>1527</v>
       </c>
-      <c r="AY39" s="1"/>
-      <c r="AZ39" s="1"/>
-      <c r="BA39" s="1"/>
-      <c r="BB39" s="1"/>
-      <c r="BC39" s="1"/>
-      <c r="BD39" s="1"/>
-      <c r="BE39" s="1"/>
-      <c r="BF39" s="1"/>
-      <c r="BG39" s="1"/>
-      <c r="BH39" s="1"/>
-      <c r="BI39" s="1"/>
-      <c r="BJ39" s="1"/>
-      <c r="BK39" s="1"/>
-      <c r="BL39" s="1"/>
-    </row>
-    <row r="40" spans="1:64">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
-      <c r="M40" s="1"/>
-      <c r="N40" s="1"/>
-      <c r="O40" s="1"/>
-      <c r="P40" s="1" t="s">
+    </row>
+    <row r="40" spans="15:49">
+      <c r="O40" t="s">
         <v>2083</v>
       </c>
-      <c r="Q40" s="1"/>
-      <c r="R40" s="1"/>
-      <c r="S40" s="1"/>
-      <c r="T40" s="1"/>
-      <c r="U40" s="1"/>
-      <c r="V40" s="1"/>
-      <c r="W40" s="1"/>
-      <c r="X40" s="1"/>
-      <c r="Y40" s="1"/>
-      <c r="Z40" s="1"/>
-      <c r="AA40" s="1"/>
-      <c r="AB40" s="1"/>
-      <c r="AC40" s="1"/>
-      <c r="AD40" s="1"/>
-      <c r="AE40" s="1"/>
-      <c r="AF40" s="1"/>
-      <c r="AG40" s="1"/>
-      <c r="AH40" s="1" t="s">
+      <c r="AG40" t="s">
         <v>1553</v>
       </c>
-      <c r="AI40" s="1"/>
-      <c r="AJ40" s="1"/>
-      <c r="AK40" s="1"/>
-      <c r="AL40" s="1"/>
-      <c r="AM40" s="1"/>
-      <c r="AN40" s="1"/>
-      <c r="AO40" s="1"/>
-      <c r="AP40" s="1"/>
-      <c r="AQ40" s="1"/>
-      <c r="AR40" s="1"/>
-      <c r="AS40" s="1"/>
-      <c r="AT40" s="1"/>
-      <c r="AU40" s="1"/>
-      <c r="AV40" s="1"/>
-      <c r="AW40" s="1"/>
-      <c r="AX40" s="1" t="s">
+      <c r="AW40" t="s">
         <v>1046</v>
       </c>
-      <c r="AY40" s="1"/>
-      <c r="AZ40" s="1"/>
-      <c r="BA40" s="1"/>
-      <c r="BB40" s="1"/>
-      <c r="BC40" s="1"/>
-      <c r="BD40" s="1"/>
-      <c r="BE40" s="1"/>
-      <c r="BF40" s="1"/>
-      <c r="BG40" s="1"/>
-      <c r="BH40" s="1"/>
-      <c r="BI40" s="1"/>
-      <c r="BJ40" s="1"/>
-      <c r="BK40" s="1"/>
-      <c r="BL40" s="1"/>
-    </row>
-    <row r="41" spans="1:64">
-      <c r="A41" s="1"/>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
-      <c r="O41" s="1"/>
-      <c r="P41" s="1" t="s">
+    </row>
+    <row r="41" spans="15:49">
+      <c r="O41" t="s">
         <v>2084</v>
       </c>
-      <c r="Q41" s="1"/>
-      <c r="R41" s="1"/>
-      <c r="S41" s="1"/>
-      <c r="T41" s="1"/>
-      <c r="U41" s="1"/>
-      <c r="V41" s="1"/>
-      <c r="W41" s="1"/>
-      <c r="X41" s="1"/>
-      <c r="Y41" s="1"/>
-      <c r="Z41" s="1"/>
-      <c r="AA41" s="1"/>
-      <c r="AB41" s="1"/>
-      <c r="AC41" s="1"/>
-      <c r="AD41" s="1"/>
-      <c r="AE41" s="1"/>
-      <c r="AF41" s="1"/>
-      <c r="AG41" s="1"/>
-      <c r="AH41" s="1" t="s">
+      <c r="AG41" t="s">
         <v>2085</v>
       </c>
-      <c r="AI41" s="1"/>
-      <c r="AJ41" s="1"/>
-      <c r="AK41" s="1"/>
-      <c r="AL41" s="1"/>
-      <c r="AM41" s="1"/>
-      <c r="AN41" s="1"/>
-      <c r="AO41" s="1"/>
-      <c r="AP41" s="1"/>
-      <c r="AQ41" s="1"/>
-      <c r="AR41" s="1"/>
-      <c r="AS41" s="1"/>
-      <c r="AT41" s="1"/>
-      <c r="AU41" s="1"/>
-      <c r="AV41" s="1"/>
-      <c r="AW41" s="1"/>
-      <c r="AX41" s="1" t="s">
+      <c r="AW41" t="s">
         <v>1114</v>
       </c>
-      <c r="AY41" s="1"/>
-      <c r="AZ41" s="1"/>
-      <c r="BA41" s="1"/>
-      <c r="BB41" s="1"/>
-      <c r="BC41" s="1"/>
-      <c r="BD41" s="1"/>
-      <c r="BE41" s="1"/>
-      <c r="BF41" s="1"/>
-      <c r="BG41" s="1"/>
-      <c r="BH41" s="1"/>
-      <c r="BI41" s="1"/>
-      <c r="BJ41" s="1"/>
-      <c r="BK41" s="1"/>
-      <c r="BL41" s="1"/>
-    </row>
-    <row r="42" spans="1:64">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
-      <c r="M42" s="1"/>
-      <c r="N42" s="1"/>
-      <c r="O42" s="1"/>
-      <c r="P42" s="1" t="s">
+    </row>
+    <row r="42" spans="15:49">
+      <c r="O42" t="s">
         <v>2086</v>
       </c>
-      <c r="Q42" s="1"/>
-      <c r="R42" s="1"/>
-      <c r="S42" s="1"/>
-      <c r="T42" s="1"/>
-      <c r="U42" s="1"/>
-      <c r="V42" s="1"/>
-      <c r="W42" s="1"/>
-      <c r="X42" s="1"/>
-      <c r="Y42" s="1"/>
-      <c r="Z42" s="1"/>
-      <c r="AA42" s="1"/>
-      <c r="AB42" s="1"/>
-      <c r="AC42" s="1"/>
-      <c r="AD42" s="1"/>
-      <c r="AE42" s="1"/>
-      <c r="AF42" s="1"/>
-      <c r="AG42" s="1"/>
-      <c r="AH42" s="1" t="s">
+      <c r="AG42" t="s">
         <v>2087</v>
       </c>
-      <c r="AI42" s="1"/>
-      <c r="AJ42" s="1"/>
-      <c r="AK42" s="1"/>
-      <c r="AL42" s="1"/>
-      <c r="AM42" s="1"/>
-      <c r="AN42" s="1"/>
-      <c r="AO42" s="1"/>
-      <c r="AP42" s="1"/>
-      <c r="AQ42" s="1"/>
-      <c r="AR42" s="1"/>
-      <c r="AS42" s="1"/>
-      <c r="AT42" s="1"/>
-      <c r="AU42" s="1"/>
-      <c r="AV42" s="1"/>
-      <c r="AW42" s="1"/>
-      <c r="AX42" s="1" t="s">
+      <c r="AW42" t="s">
         <v>1581</v>
       </c>
-      <c r="AY42" s="1"/>
-      <c r="AZ42" s="1"/>
-      <c r="BA42" s="1"/>
-      <c r="BB42" s="1"/>
-      <c r="BC42" s="1"/>
-      <c r="BD42" s="1"/>
-      <c r="BE42" s="1"/>
-      <c r="BF42" s="1"/>
-      <c r="BG42" s="1"/>
-      <c r="BH42" s="1"/>
-      <c r="BI42" s="1"/>
-      <c r="BJ42" s="1"/>
-      <c r="BK42" s="1"/>
-      <c r="BL42" s="1"/>
-    </row>
-    <row r="43" spans="1:64">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1"/>
-      <c r="N43" s="1"/>
-      <c r="O43" s="1"/>
-      <c r="P43" s="1" t="s">
+    </row>
+    <row r="43" spans="15:49">
+      <c r="O43" t="s">
         <v>2088</v>
       </c>
-      <c r="Q43" s="1"/>
-      <c r="R43" s="1"/>
-      <c r="S43" s="1"/>
-      <c r="T43" s="1"/>
-      <c r="U43" s="1"/>
-      <c r="V43" s="1"/>
-      <c r="W43" s="1"/>
-      <c r="X43" s="1"/>
-      <c r="Y43" s="1"/>
-      <c r="Z43" s="1"/>
-      <c r="AA43" s="1"/>
-      <c r="AB43" s="1"/>
-      <c r="AC43" s="1"/>
-      <c r="AD43" s="1"/>
-      <c r="AE43" s="1"/>
-      <c r="AF43" s="1"/>
-      <c r="AG43" s="1"/>
-      <c r="AH43" s="1" t="s">
+      <c r="AG43" t="s">
         <v>2089</v>
       </c>
-      <c r="AI43" s="1"/>
-      <c r="AJ43" s="1"/>
-      <c r="AK43" s="1"/>
-      <c r="AL43" s="1"/>
-      <c r="AM43" s="1"/>
-      <c r="AN43" s="1"/>
-      <c r="AO43" s="1"/>
-      <c r="AP43" s="1"/>
-      <c r="AQ43" s="1"/>
-      <c r="AR43" s="1"/>
-      <c r="AS43" s="1"/>
-      <c r="AT43" s="1"/>
-      <c r="AU43" s="1"/>
-      <c r="AV43" s="1"/>
-      <c r="AW43" s="1"/>
-      <c r="AX43" s="1" t="s">
+      <c r="AW43" t="s">
         <v>1548</v>
       </c>
-      <c r="AY43" s="1"/>
-      <c r="AZ43" s="1"/>
-      <c r="BA43" s="1"/>
-      <c r="BB43" s="1"/>
-      <c r="BC43" s="1"/>
-      <c r="BD43" s="1"/>
-      <c r="BE43" s="1"/>
-      <c r="BF43" s="1"/>
-      <c r="BG43" s="1"/>
-      <c r="BH43" s="1"/>
-      <c r="BI43" s="1"/>
-      <c r="BJ43" s="1"/>
-      <c r="BK43" s="1"/>
-      <c r="BL43" s="1"/>
-    </row>
-    <row r="44" spans="1:64">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
-      <c r="N44" s="1"/>
-      <c r="O44" s="1"/>
-      <c r="P44" s="1" t="s">
+    </row>
+    <row r="44" spans="15:49">
+      <c r="O44" t="s">
         <v>574</v>
       </c>
-      <c r="Q44" s="1"/>
-      <c r="R44" s="1"/>
-      <c r="S44" s="1"/>
-      <c r="T44" s="1"/>
-      <c r="U44" s="1"/>
-      <c r="V44" s="1"/>
-      <c r="W44" s="1"/>
-      <c r="X44" s="1"/>
-      <c r="Y44" s="1"/>
-      <c r="Z44" s="1"/>
-      <c r="AA44" s="1"/>
-      <c r="AB44" s="1"/>
-      <c r="AC44" s="1"/>
-      <c r="AD44" s="1"/>
-      <c r="AE44" s="1"/>
-      <c r="AF44" s="1"/>
-      <c r="AG44" s="1"/>
-      <c r="AH44" s="1" t="s">
+      <c r="AG44" t="s">
         <v>271</v>
       </c>
-      <c r="AI44" s="1"/>
-      <c r="AJ44" s="1"/>
-      <c r="AK44" s="1"/>
-      <c r="AL44" s="1"/>
-      <c r="AM44" s="1"/>
-      <c r="AN44" s="1"/>
-      <c r="AO44" s="1"/>
-      <c r="AP44" s="1"/>
-      <c r="AQ44" s="1"/>
-      <c r="AR44" s="1"/>
-      <c r="AS44" s="1"/>
-      <c r="AT44" s="1"/>
-      <c r="AU44" s="1"/>
-      <c r="AV44" s="1"/>
-      <c r="AW44" s="1"/>
-      <c r="AX44" s="1" t="s">
+      <c r="AW44" t="s">
         <v>1597</v>
       </c>
-      <c r="AY44" s="1"/>
-      <c r="AZ44" s="1"/>
-      <c r="BA44" s="1"/>
-      <c r="BB44" s="1"/>
-      <c r="BC44" s="1"/>
-      <c r="BD44" s="1"/>
-      <c r="BE44" s="1"/>
-      <c r="BF44" s="1"/>
-      <c r="BG44" s="1"/>
-      <c r="BH44" s="1"/>
-      <c r="BI44" s="1"/>
-      <c r="BJ44" s="1"/>
-      <c r="BK44" s="1"/>
-      <c r="BL44" s="1"/>
-    </row>
-    <row r="45" spans="1:64">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
-      <c r="K45" s="1"/>
-      <c r="L45" s="1"/>
-      <c r="M45" s="1"/>
-      <c r="N45" s="1"/>
-      <c r="O45" s="1"/>
-      <c r="P45" s="1" t="s">
+    </row>
+    <row r="45" spans="15:49">
+      <c r="O45" t="s">
         <v>2090</v>
       </c>
-      <c r="Q45" s="1"/>
-      <c r="R45" s="1"/>
-      <c r="S45" s="1"/>
-      <c r="T45" s="1"/>
-      <c r="U45" s="1"/>
-      <c r="V45" s="1"/>
-      <c r="W45" s="1"/>
-      <c r="X45" s="1"/>
-      <c r="Y45" s="1"/>
-      <c r="Z45" s="1"/>
-      <c r="AA45" s="1"/>
-      <c r="AB45" s="1"/>
-      <c r="AC45" s="1"/>
-      <c r="AD45" s="1"/>
-      <c r="AE45" s="1"/>
-      <c r="AF45" s="1"/>
-      <c r="AG45" s="1"/>
-      <c r="AH45" s="1" t="s">
+      <c r="AG45" t="s">
         <v>889</v>
       </c>
-      <c r="AI45" s="1"/>
-      <c r="AJ45" s="1"/>
-      <c r="AK45" s="1"/>
-      <c r="AL45" s="1"/>
-      <c r="AM45" s="1"/>
-      <c r="AN45" s="1"/>
-      <c r="AO45" s="1"/>
-      <c r="AP45" s="1"/>
-      <c r="AQ45" s="1"/>
-      <c r="AR45" s="1"/>
-      <c r="AS45" s="1"/>
-      <c r="AT45" s="1"/>
-      <c r="AU45" s="1"/>
-      <c r="AV45" s="1"/>
-      <c r="AW45" s="1"/>
-      <c r="AX45" s="1" t="s">
+      <c r="AW45" t="s">
         <v>525</v>
       </c>
-      <c r="AY45" s="1"/>
-      <c r="AZ45" s="1"/>
-      <c r="BA45" s="1"/>
-      <c r="BB45" s="1"/>
-      <c r="BC45" s="1"/>
-      <c r="BD45" s="1"/>
-      <c r="BE45" s="1"/>
-      <c r="BF45" s="1"/>
-      <c r="BG45" s="1"/>
-      <c r="BH45" s="1"/>
-      <c r="BI45" s="1"/>
-      <c r="BJ45" s="1"/>
-      <c r="BK45" s="1"/>
-      <c r="BL45" s="1"/>
-    </row>
-    <row r="46" spans="1:64">
-      <c r="A46" s="1"/>
-      <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
-      <c r="L46" s="1"/>
-      <c r="M46" s="1"/>
-      <c r="N46" s="1"/>
-      <c r="O46" s="1"/>
-      <c r="P46" s="1" t="s">
+    </row>
+    <row r="46" spans="15:49">
+      <c r="O46" t="s">
         <v>2091</v>
       </c>
-      <c r="Q46" s="1"/>
-      <c r="R46" s="1"/>
-      <c r="S46" s="1"/>
-      <c r="T46" s="1"/>
-      <c r="U46" s="1"/>
-      <c r="V46" s="1"/>
-      <c r="W46" s="1"/>
-      <c r="X46" s="1"/>
-      <c r="Y46" s="1"/>
-      <c r="Z46" s="1"/>
-      <c r="AA46" s="1"/>
-      <c r="AB46" s="1"/>
-      <c r="AC46" s="1"/>
-      <c r="AD46" s="1"/>
-      <c r="AE46" s="1"/>
-      <c r="AF46" s="1"/>
-      <c r="AG46" s="1"/>
-      <c r="AH46" s="1" t="s">
+      <c r="AG46" t="s">
         <v>643</v>
       </c>
-      <c r="AI46" s="1"/>
-      <c r="AJ46" s="1"/>
-      <c r="AK46" s="1"/>
-      <c r="AL46" s="1"/>
-      <c r="AM46" s="1"/>
-      <c r="AN46" s="1"/>
-      <c r="AO46" s="1"/>
-      <c r="AP46" s="1"/>
-      <c r="AQ46" s="1"/>
-      <c r="AR46" s="1"/>
-      <c r="AS46" s="1"/>
-      <c r="AT46" s="1"/>
-      <c r="AU46" s="1"/>
-      <c r="AV46" s="1"/>
-      <c r="AW46" s="1"/>
-      <c r="AX46" s="1" t="s">
+      <c r="AW46" t="s">
         <v>590</v>
       </c>
-      <c r="AY46" s="1"/>
-      <c r="AZ46" s="1"/>
-      <c r="BA46" s="1"/>
-      <c r="BB46" s="1"/>
-      <c r="BC46" s="1"/>
-      <c r="BD46" s="1"/>
-      <c r="BE46" s="1"/>
-      <c r="BF46" s="1"/>
-      <c r="BG46" s="1"/>
-      <c r="BH46" s="1"/>
-      <c r="BI46" s="1"/>
-      <c r="BJ46" s="1"/>
-      <c r="BK46" s="1"/>
-      <c r="BL46" s="1"/>
-    </row>
-    <row r="47" spans="1:64">
-      <c r="A47" s="1"/>
-      <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="1"/>
-      <c r="K47" s="1"/>
-      <c r="L47" s="1"/>
-      <c r="M47" s="1"/>
-      <c r="N47" s="1"/>
-      <c r="O47" s="1"/>
-      <c r="P47" s="1" t="s">
+    </row>
+    <row r="47" spans="15:49">
+      <c r="O47" t="s">
         <v>782</v>
       </c>
-      <c r="Q47" s="1"/>
-      <c r="R47" s="1"/>
-      <c r="S47" s="1"/>
-      <c r="T47" s="1"/>
-      <c r="U47" s="1"/>
-      <c r="V47" s="1"/>
-      <c r="W47" s="1"/>
-      <c r="X47" s="1"/>
-      <c r="Y47" s="1"/>
-      <c r="Z47" s="1"/>
-      <c r="AA47" s="1"/>
-      <c r="AB47" s="1"/>
-      <c r="AC47" s="1"/>
-      <c r="AD47" s="1"/>
-      <c r="AE47" s="1"/>
-      <c r="AF47" s="1"/>
-      <c r="AG47" s="1"/>
-      <c r="AH47" s="1" t="s">
+      <c r="AG47" t="s">
         <v>962</v>
       </c>
-      <c r="AI47" s="1"/>
-      <c r="AJ47" s="1"/>
-      <c r="AK47" s="1"/>
-      <c r="AL47" s="1"/>
-      <c r="AM47" s="1"/>
-      <c r="AN47" s="1"/>
-      <c r="AO47" s="1"/>
-      <c r="AP47" s="1"/>
-      <c r="AQ47" s="1"/>
-      <c r="AR47" s="1"/>
-      <c r="AS47" s="1"/>
-      <c r="AT47" s="1"/>
-      <c r="AU47" s="1"/>
-      <c r="AV47" s="1"/>
-      <c r="AW47" s="1"/>
-      <c r="AX47" s="1" t="s">
+      <c r="AW47" t="s">
         <v>1266</v>
       </c>
-      <c r="AY47" s="1"/>
-      <c r="AZ47" s="1"/>
-      <c r="BA47" s="1"/>
-      <c r="BB47" s="1"/>
-      <c r="BC47" s="1"/>
-      <c r="BD47" s="1"/>
-      <c r="BE47" s="1"/>
-      <c r="BF47" s="1"/>
-      <c r="BG47" s="1"/>
-      <c r="BH47" s="1"/>
-      <c r="BI47" s="1"/>
-      <c r="BJ47" s="1"/>
-      <c r="BK47" s="1"/>
-      <c r="BL47" s="1"/>
-    </row>
-    <row r="48" spans="1:64">
-      <c r="A48" s="1"/>
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
-      <c r="L48" s="1"/>
-      <c r="M48" s="1"/>
-      <c r="N48" s="1"/>
-      <c r="O48" s="1"/>
-      <c r="P48" s="1" t="s">
+    </row>
+    <row r="48" spans="15:49">
+      <c r="O48" t="s">
         <v>1843</v>
       </c>
-      <c r="Q48" s="1"/>
-      <c r="R48" s="1"/>
-      <c r="S48" s="1"/>
-      <c r="T48" s="1"/>
-      <c r="U48" s="1"/>
-      <c r="V48" s="1"/>
-      <c r="W48" s="1"/>
-      <c r="X48" s="1"/>
-      <c r="Y48" s="1"/>
-      <c r="Z48" s="1"/>
-      <c r="AA48" s="1"/>
-      <c r="AB48" s="1"/>
-      <c r="AC48" s="1"/>
-      <c r="AD48" s="1"/>
-      <c r="AE48" s="1"/>
-      <c r="AF48" s="1"/>
-      <c r="AG48" s="1"/>
-      <c r="AH48" s="1" t="s">
+      <c r="AG48" t="s">
         <v>606</v>
       </c>
-      <c r="AI48" s="1"/>
-      <c r="AJ48" s="1"/>
-      <c r="AK48" s="1"/>
-      <c r="AL48" s="1"/>
-      <c r="AM48" s="1"/>
-      <c r="AN48" s="1"/>
-      <c r="AO48" s="1"/>
-      <c r="AP48" s="1"/>
-      <c r="AQ48" s="1"/>
-      <c r="AR48" s="1"/>
-      <c r="AS48" s="1"/>
-      <c r="AT48" s="1"/>
-      <c r="AU48" s="1"/>
-      <c r="AV48" s="1"/>
-      <c r="AW48" s="1"/>
-      <c r="AX48" s="1" t="s">
+      <c r="AW48" t="s">
         <v>927</v>
       </c>
-      <c r="AY48" s="1"/>
-      <c r="AZ48" s="1"/>
-      <c r="BA48" s="1"/>
-      <c r="BB48" s="1"/>
-      <c r="BC48" s="1"/>
-      <c r="BD48" s="1"/>
-      <c r="BE48" s="1"/>
-      <c r="BF48" s="1"/>
-      <c r="BG48" s="1"/>
-      <c r="BH48" s="1"/>
-      <c r="BI48" s="1"/>
-      <c r="BJ48" s="1"/>
-      <c r="BK48" s="1"/>
-      <c r="BL48" s="1"/>
-    </row>
-    <row r="49" spans="1:64">
-      <c r="A49" s="1"/>
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
-      <c r="K49" s="1"/>
-      <c r="L49" s="1"/>
-      <c r="M49" s="1"/>
-      <c r="N49" s="1"/>
-      <c r="O49" s="1"/>
-      <c r="P49" s="1" t="s">
+    </row>
+    <row r="49" spans="15:49">
+      <c r="O49" t="s">
         <v>962</v>
       </c>
-      <c r="Q49" s="1"/>
-      <c r="R49" s="1"/>
-      <c r="S49" s="1"/>
-      <c r="T49" s="1"/>
-      <c r="U49" s="1"/>
-      <c r="V49" s="1"/>
-      <c r="W49" s="1"/>
-      <c r="X49" s="1"/>
-      <c r="Y49" s="1"/>
-      <c r="Z49" s="1"/>
-      <c r="AA49" s="1"/>
-      <c r="AB49" s="1"/>
-      <c r="AC49" s="1"/>
-      <c r="AD49" s="1"/>
-      <c r="AE49" s="1"/>
-      <c r="AF49" s="1"/>
-      <c r="AG49" s="1"/>
-      <c r="AH49" s="1" t="s">
+      <c r="AG49" t="s">
         <v>1047</v>
       </c>
-      <c r="AI49" s="1"/>
-      <c r="AJ49" s="1"/>
-      <c r="AK49" s="1"/>
-      <c r="AL49" s="1"/>
-      <c r="AM49" s="1"/>
-      <c r="AN49" s="1"/>
-      <c r="AO49" s="1"/>
-      <c r="AP49" s="1"/>
-      <c r="AQ49" s="1"/>
-      <c r="AR49" s="1"/>
-      <c r="AS49" s="1"/>
-      <c r="AT49" s="1"/>
-      <c r="AU49" s="1"/>
-      <c r="AV49" s="1"/>
-      <c r="AW49" s="1"/>
-      <c r="AX49" s="1" t="s">
+      <c r="AW49" t="s">
         <v>951</v>
       </c>
-      <c r="AY49" s="1"/>
-      <c r="AZ49" s="1"/>
-      <c r="BA49" s="1"/>
-      <c r="BB49" s="1"/>
-      <c r="BC49" s="1"/>
-      <c r="BD49" s="1"/>
-      <c r="BE49" s="1"/>
-      <c r="BF49" s="1"/>
-      <c r="BG49" s="1"/>
-      <c r="BH49" s="1"/>
-      <c r="BI49" s="1"/>
-      <c r="BJ49" s="1"/>
-      <c r="BK49" s="1"/>
-      <c r="BL49" s="1"/>
-    </row>
-    <row r="50" spans="1:64">
-      <c r="A50" s="1"/>
-      <c r="B50" s="1"/>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
-      <c r="K50" s="1"/>
-      <c r="L50" s="1"/>
-      <c r="M50" s="1"/>
-      <c r="N50" s="1"/>
-      <c r="O50" s="1"/>
-      <c r="P50" s="1" t="s">
+    </row>
+    <row r="50" spans="15:49">
+      <c r="O50" t="s">
         <v>1827</v>
       </c>
-      <c r="Q50" s="1"/>
-      <c r="R50" s="1"/>
-      <c r="S50" s="1"/>
-      <c r="T50" s="1"/>
-      <c r="U50" s="1"/>
-      <c r="V50" s="1"/>
-      <c r="W50" s="1"/>
-      <c r="X50" s="1"/>
-      <c r="Y50" s="1"/>
-      <c r="Z50" s="1"/>
-      <c r="AA50" s="1"/>
-      <c r="AB50" s="1"/>
-      <c r="AC50" s="1"/>
-      <c r="AD50" s="1"/>
-      <c r="AE50" s="1"/>
-      <c r="AF50" s="1"/>
-      <c r="AG50" s="1"/>
-      <c r="AH50" s="1" t="s">
+      <c r="AG50" t="s">
         <v>1821</v>
       </c>
-      <c r="AI50" s="1"/>
-      <c r="AJ50" s="1"/>
-      <c r="AK50" s="1"/>
-      <c r="AL50" s="1"/>
-      <c r="AM50" s="1"/>
-      <c r="AN50" s="1"/>
-      <c r="AO50" s="1"/>
-      <c r="AP50" s="1"/>
-      <c r="AQ50" s="1"/>
-      <c r="AR50" s="1"/>
-      <c r="AS50" s="1"/>
-      <c r="AT50" s="1"/>
-      <c r="AU50" s="1"/>
-      <c r="AV50" s="1"/>
-      <c r="AW50" s="1"/>
-      <c r="AX50" s="1" t="s">
+      <c r="AW50" t="s">
         <v>553</v>
       </c>
-      <c r="AY50" s="1"/>
-      <c r="AZ50" s="1"/>
-      <c r="BA50" s="1"/>
-      <c r="BB50" s="1"/>
-      <c r="BC50" s="1"/>
-      <c r="BD50" s="1"/>
-      <c r="BE50" s="1"/>
-      <c r="BF50" s="1"/>
-      <c r="BG50" s="1"/>
-      <c r="BH50" s="1"/>
-      <c r="BI50" s="1"/>
-      <c r="BJ50" s="1"/>
-      <c r="BK50" s="1"/>
-      <c r="BL50" s="1"/>
-    </row>
-    <row r="51" spans="1:64">
-      <c r="A51" s="1"/>
-      <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
-      <c r="K51" s="1"/>
-      <c r="L51" s="1"/>
-      <c r="M51" s="1"/>
-      <c r="N51" s="1"/>
-      <c r="O51" s="1"/>
-      <c r="P51" s="1" t="s">
+    </row>
+    <row r="51" spans="15:49">
+      <c r="O51" t="s">
         <v>235</v>
       </c>
-      <c r="Q51" s="1"/>
-      <c r="R51" s="1"/>
-      <c r="S51" s="1"/>
-      <c r="T51" s="1"/>
-      <c r="U51" s="1"/>
-      <c r="V51" s="1"/>
-      <c r="W51" s="1"/>
-      <c r="X51" s="1"/>
-      <c r="Y51" s="1"/>
-      <c r="Z51" s="1"/>
-      <c r="AA51" s="1"/>
-      <c r="AB51" s="1"/>
-      <c r="AC51" s="1"/>
-      <c r="AD51" s="1"/>
-      <c r="AE51" s="1"/>
-      <c r="AF51" s="1"/>
-      <c r="AG51" s="1"/>
-      <c r="AH51" s="1" t="s">
+      <c r="AG51" t="s">
         <v>1486</v>
       </c>
-      <c r="AI51" s="1"/>
-      <c r="AJ51" s="1"/>
-      <c r="AK51" s="1"/>
-      <c r="AL51" s="1"/>
-      <c r="AM51" s="1"/>
-      <c r="AN51" s="1"/>
-      <c r="AO51" s="1"/>
-      <c r="AP51" s="1"/>
-      <c r="AQ51" s="1"/>
-      <c r="AR51" s="1"/>
-      <c r="AS51" s="1"/>
-      <c r="AT51" s="1"/>
-      <c r="AU51" s="1"/>
-      <c r="AV51" s="1"/>
-      <c r="AW51" s="1"/>
-      <c r="AX51" s="1" t="s">
+      <c r="AW51" t="s">
         <v>2092</v>
       </c>
-      <c r="AY51" s="1"/>
-      <c r="AZ51" s="1"/>
-      <c r="BA51" s="1"/>
-      <c r="BB51" s="1"/>
-      <c r="BC51" s="1"/>
-      <c r="BD51" s="1"/>
-      <c r="BE51" s="1"/>
-      <c r="BF51" s="1"/>
-      <c r="BG51" s="1"/>
-      <c r="BH51" s="1"/>
-      <c r="BI51" s="1"/>
-      <c r="BJ51" s="1"/>
-      <c r="BK51" s="1"/>
-      <c r="BL51" s="1"/>
-    </row>
-    <row r="52" spans="1:64">
-      <c r="A52" s="1"/>
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
-      <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="1"/>
-      <c r="I52" s="1"/>
-      <c r="J52" s="1"/>
-      <c r="K52" s="1"/>
-      <c r="L52" s="1"/>
-      <c r="M52" s="1"/>
-      <c r="N52" s="1"/>
-      <c r="O52" s="1"/>
-      <c r="P52" s="1" t="s">
+    </row>
+    <row r="52" spans="15:49">
+      <c r="O52" t="s">
         <v>2093</v>
       </c>
-      <c r="Q52" s="1"/>
-      <c r="R52" s="1"/>
-      <c r="S52" s="1"/>
-      <c r="T52" s="1"/>
-      <c r="U52" s="1"/>
-      <c r="V52" s="1"/>
-      <c r="W52" s="1"/>
-      <c r="X52" s="1"/>
-      <c r="Y52" s="1"/>
-      <c r="Z52" s="1"/>
-      <c r="AA52" s="1"/>
-      <c r="AB52" s="1"/>
-      <c r="AC52" s="1"/>
-      <c r="AD52" s="1"/>
-      <c r="AE52" s="1"/>
-      <c r="AF52" s="1"/>
-      <c r="AG52" s="1"/>
-      <c r="AH52" s="1" t="s">
+      <c r="AG52" t="s">
         <v>1513</v>
       </c>
-      <c r="AI52" s="1"/>
-      <c r="AJ52" s="1"/>
-      <c r="AK52" s="1"/>
-      <c r="AL52" s="1"/>
-      <c r="AM52" s="1"/>
-      <c r="AN52" s="1"/>
-      <c r="AO52" s="1"/>
-      <c r="AP52" s="1"/>
-      <c r="AQ52" s="1"/>
-      <c r="AR52" s="1"/>
-      <c r="AS52" s="1"/>
-      <c r="AT52" s="1"/>
-      <c r="AU52" s="1"/>
-      <c r="AV52" s="1"/>
-      <c r="AW52" s="1"/>
-      <c r="AX52" s="1" t="s">
+      <c r="AW52" t="s">
         <v>2025</v>
       </c>
-      <c r="AY52" s="1"/>
-      <c r="AZ52" s="1"/>
-      <c r="BA52" s="1"/>
-      <c r="BB52" s="1"/>
-      <c r="BC52" s="1"/>
-      <c r="BD52" s="1"/>
-      <c r="BE52" s="1"/>
-      <c r="BF52" s="1"/>
-      <c r="BG52" s="1"/>
-      <c r="BH52" s="1"/>
-      <c r="BI52" s="1"/>
-      <c r="BJ52" s="1"/>
-      <c r="BK52" s="1"/>
-      <c r="BL52" s="1"/>
-    </row>
-    <row r="53" spans="1:64">
-      <c r="A53" s="1"/>
-      <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
-      <c r="D53" s="1"/>
-      <c r="E53" s="1"/>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="1"/>
-      <c r="I53" s="1"/>
-      <c r="J53" s="1"/>
-      <c r="K53" s="1"/>
-      <c r="L53" s="1"/>
-      <c r="M53" s="1"/>
-      <c r="N53" s="1"/>
-      <c r="O53" s="1"/>
-      <c r="P53" s="1"/>
-      <c r="Q53" s="1"/>
-      <c r="R53" s="1"/>
-      <c r="S53" s="1"/>
-      <c r="T53" s="1"/>
-      <c r="U53" s="1"/>
-      <c r="V53" s="1"/>
-      <c r="W53" s="1"/>
-      <c r="X53" s="1"/>
-      <c r="Y53" s="1"/>
-      <c r="Z53" s="1"/>
-      <c r="AA53" s="1"/>
-      <c r="AB53" s="1"/>
-      <c r="AC53" s="1"/>
-      <c r="AD53" s="1"/>
-      <c r="AE53" s="1"/>
-      <c r="AF53" s="1"/>
-      <c r="AG53" s="1"/>
-      <c r="AH53" s="1" t="s">
+    </row>
+    <row r="53" spans="15:49">
+      <c r="O53" t="s">
+        <v>2204</v>
+      </c>
+      <c r="AG53" t="s">
         <v>2090</v>
       </c>
-      <c r="AI53" s="1"/>
-      <c r="AJ53" s="1"/>
-      <c r="AK53" s="1"/>
-      <c r="AL53" s="1"/>
-      <c r="AM53" s="1"/>
-      <c r="AN53" s="1"/>
-      <c r="AO53" s="1"/>
-      <c r="AP53" s="1"/>
-      <c r="AQ53" s="1"/>
-      <c r="AR53" s="1"/>
-      <c r="AS53" s="1"/>
-      <c r="AT53" s="1"/>
-      <c r="AU53" s="1"/>
-      <c r="AV53" s="1"/>
-      <c r="AW53" s="1"/>
-      <c r="AX53" s="1" t="s">
+      <c r="AW53" t="s">
         <v>2094</v>
       </c>
-      <c r="AY53" s="1"/>
-      <c r="AZ53" s="1"/>
-      <c r="BA53" s="1"/>
-      <c r="BB53" s="1"/>
-      <c r="BC53" s="1"/>
-      <c r="BD53" s="1"/>
-      <c r="BE53" s="1"/>
-      <c r="BF53" s="1"/>
-      <c r="BG53" s="1"/>
-      <c r="BH53" s="1"/>
-      <c r="BI53" s="1"/>
-      <c r="BJ53" s="1"/>
-      <c r="BK53" s="1"/>
-      <c r="BL53" s="1"/>
-    </row>
-    <row r="54" spans="1:64">
-      <c r="A54" s="1"/>
-      <c r="B54" s="1"/>
-      <c r="C54" s="1"/>
-      <c r="D54" s="1"/>
-      <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
-      <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
-      <c r="L54" s="1"/>
-      <c r="M54" s="1"/>
-      <c r="N54" s="1"/>
-      <c r="O54" s="1"/>
-      <c r="P54" s="1"/>
-      <c r="Q54" s="1"/>
-      <c r="R54" s="1"/>
-      <c r="S54" s="1"/>
-      <c r="T54" s="1"/>
-      <c r="U54" s="1"/>
-      <c r="V54" s="1"/>
-      <c r="W54" s="1"/>
-      <c r="X54" s="1"/>
-      <c r="Y54" s="1"/>
-      <c r="Z54" s="1"/>
-      <c r="AA54" s="1"/>
-      <c r="AB54" s="1"/>
-      <c r="AC54" s="1"/>
-      <c r="AD54" s="1"/>
-      <c r="AE54" s="1"/>
-      <c r="AF54" s="1"/>
-      <c r="AG54" s="1"/>
-      <c r="AH54" s="1" t="s">
+    </row>
+    <row r="54" spans="15:49">
+      <c r="AG54" t="s">
         <v>761</v>
       </c>
-      <c r="AI54" s="1"/>
-      <c r="AJ54" s="1"/>
-      <c r="AK54" s="1"/>
-      <c r="AL54" s="1"/>
-      <c r="AM54" s="1"/>
-      <c r="AN54" s="1"/>
-      <c r="AO54" s="1"/>
-      <c r="AP54" s="1"/>
-      <c r="AQ54" s="1"/>
-      <c r="AR54" s="1"/>
-      <c r="AS54" s="1"/>
-      <c r="AT54" s="1"/>
-      <c r="AU54" s="1"/>
-      <c r="AV54" s="1"/>
-      <c r="AW54" s="1"/>
-      <c r="AX54" s="1" t="s">
+      <c r="AW54" t="s">
         <v>1047</v>
       </c>
-      <c r="AY54" s="1"/>
-      <c r="AZ54" s="1"/>
-      <c r="BA54" s="1"/>
-      <c r="BB54" s="1"/>
-      <c r="BC54" s="1"/>
-      <c r="BD54" s="1"/>
-      <c r="BE54" s="1"/>
-      <c r="BF54" s="1"/>
-      <c r="BG54" s="1"/>
-      <c r="BH54" s="1"/>
-      <c r="BI54" s="1"/>
-      <c r="BJ54" s="1"/>
-      <c r="BK54" s="1"/>
-      <c r="BL54" s="1"/>
-    </row>
-    <row r="55" spans="1:64">
-      <c r="A55" s="1"/>
-      <c r="B55" s="1"/>
-      <c r="C55" s="1"/>
-      <c r="D55" s="1"/>
-      <c r="E55" s="1"/>
-      <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
-      <c r="J55" s="1"/>
-      <c r="K55" s="1"/>
-      <c r="L55" s="1"/>
-      <c r="M55" s="1"/>
-      <c r="N55" s="1"/>
-      <c r="O55" s="1"/>
-      <c r="P55" s="1"/>
-      <c r="Q55" s="1"/>
-      <c r="R55" s="1"/>
-      <c r="S55" s="1"/>
-      <c r="T55" s="1"/>
-      <c r="U55" s="1"/>
-      <c r="V55" s="1"/>
-      <c r="W55" s="1"/>
-      <c r="X55" s="1"/>
-      <c r="Y55" s="1"/>
-      <c r="Z55" s="1"/>
-      <c r="AA55" s="1"/>
-      <c r="AB55" s="1"/>
-      <c r="AC55" s="1"/>
-      <c r="AD55" s="1"/>
-      <c r="AE55" s="1"/>
-      <c r="AF55" s="1"/>
-      <c r="AG55" s="1"/>
-      <c r="AH55" s="1" t="s">
+    </row>
+    <row r="55" spans="15:49">
+      <c r="AG55" t="s">
         <v>2095</v>
       </c>
-      <c r="AI55" s="1"/>
-      <c r="AJ55" s="1"/>
-      <c r="AK55" s="1"/>
-      <c r="AL55" s="1"/>
-      <c r="AM55" s="1"/>
-      <c r="AN55" s="1"/>
-      <c r="AO55" s="1"/>
-      <c r="AP55" s="1"/>
-      <c r="AQ55" s="1"/>
-      <c r="AR55" s="1"/>
-      <c r="AS55" s="1"/>
-      <c r="AT55" s="1"/>
-      <c r="AU55" s="1"/>
-      <c r="AV55" s="1"/>
-      <c r="AW55" s="1"/>
-      <c r="AX55" s="1" t="s">
+      <c r="AW55" t="s">
         <v>977</v>
       </c>
-      <c r="AY55" s="1"/>
-      <c r="AZ55" s="1"/>
-      <c r="BA55" s="1"/>
-      <c r="BB55" s="1"/>
-      <c r="BC55" s="1"/>
-      <c r="BD55" s="1"/>
-      <c r="BE55" s="1"/>
-      <c r="BF55" s="1"/>
-      <c r="BG55" s="1"/>
-      <c r="BH55" s="1"/>
-      <c r="BI55" s="1"/>
-      <c r="BJ55" s="1"/>
-      <c r="BK55" s="1"/>
-      <c r="BL55" s="1"/>
-    </row>
-    <row r="56" spans="1:64">
-      <c r="A56" s="1"/>
-      <c r="B56" s="1"/>
-      <c r="C56" s="1"/>
-      <c r="D56" s="1"/>
-      <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="1"/>
-      <c r="I56" s="1"/>
-      <c r="J56" s="1"/>
-      <c r="K56" s="1"/>
-      <c r="L56" s="1"/>
-      <c r="M56" s="1"/>
-      <c r="N56" s="1"/>
-      <c r="O56" s="1"/>
-      <c r="P56" s="1"/>
-      <c r="Q56" s="1"/>
-      <c r="R56" s="1"/>
-      <c r="S56" s="1"/>
-      <c r="T56" s="1"/>
-      <c r="U56" s="1"/>
-      <c r="V56" s="1"/>
-      <c r="W56" s="1"/>
-      <c r="X56" s="1"/>
-      <c r="Y56" s="1"/>
-      <c r="Z56" s="1"/>
-      <c r="AA56" s="1"/>
-      <c r="AB56" s="1"/>
-      <c r="AC56" s="1"/>
-      <c r="AD56" s="1"/>
-      <c r="AE56" s="1"/>
-      <c r="AF56" s="1"/>
-      <c r="AG56" s="1"/>
-      <c r="AH56" s="1" t="s">
+    </row>
+    <row r="56" spans="15:49">
+      <c r="AG56" t="s">
         <v>2096</v>
       </c>
-      <c r="AI56" s="1"/>
-      <c r="AJ56" s="1"/>
-      <c r="AK56" s="1"/>
-      <c r="AL56" s="1"/>
-      <c r="AM56" s="1"/>
-      <c r="AN56" s="1"/>
-      <c r="AO56" s="1"/>
-      <c r="AP56" s="1"/>
-      <c r="AQ56" s="1"/>
-      <c r="AR56" s="1"/>
-      <c r="AS56" s="1"/>
-      <c r="AT56" s="1"/>
-      <c r="AU56" s="1"/>
-      <c r="AV56" s="1"/>
-      <c r="AW56" s="1"/>
-      <c r="AX56" s="1" t="s">
+      <c r="AW56" t="s">
         <v>235</v>
       </c>
-      <c r="AY56" s="1"/>
-      <c r="AZ56" s="1"/>
-      <c r="BA56" s="1"/>
-      <c r="BB56" s="1"/>
-      <c r="BC56" s="1"/>
-      <c r="BD56" s="1"/>
-      <c r="BE56" s="1"/>
-      <c r="BF56" s="1"/>
-      <c r="BG56" s="1"/>
-      <c r="BH56" s="1"/>
-      <c r="BI56" s="1"/>
-      <c r="BJ56" s="1"/>
-      <c r="BK56" s="1"/>
-      <c r="BL56" s="1"/>
-    </row>
-    <row r="57" spans="1:64">
-      <c r="A57" s="1"/>
-      <c r="B57" s="1"/>
-      <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
-      <c r="E57" s="1"/>
-      <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
-      <c r="J57" s="1"/>
-      <c r="K57" s="1"/>
-      <c r="L57" s="1"/>
-      <c r="M57" s="1"/>
-      <c r="N57" s="1"/>
-      <c r="O57" s="1"/>
-      <c r="P57" s="1"/>
-      <c r="Q57" s="1"/>
-      <c r="R57" s="1"/>
-      <c r="S57" s="1"/>
-      <c r="T57" s="1"/>
-      <c r="U57" s="1"/>
-      <c r="V57" s="1"/>
-      <c r="W57" s="1"/>
-      <c r="X57" s="1"/>
-      <c r="Y57" s="1"/>
-      <c r="Z57" s="1"/>
-      <c r="AA57" s="1"/>
-      <c r="AB57" s="1"/>
-      <c r="AC57" s="1"/>
-      <c r="AD57" s="1"/>
-      <c r="AE57" s="1"/>
-      <c r="AF57" s="1"/>
-      <c r="AG57" s="1"/>
-      <c r="AH57" s="1" t="s">
+    </row>
+    <row r="57" spans="15:49">
+      <c r="AG57" t="s">
         <v>2097</v>
       </c>
-      <c r="AI57" s="1"/>
-      <c r="AJ57" s="1"/>
-      <c r="AK57" s="1"/>
-      <c r="AL57" s="1"/>
-      <c r="AM57" s="1"/>
-      <c r="AN57" s="1"/>
-      <c r="AO57" s="1"/>
-      <c r="AP57" s="1"/>
-      <c r="AQ57" s="1"/>
-      <c r="AR57" s="1"/>
-      <c r="AS57" s="1"/>
-      <c r="AT57" s="1"/>
-      <c r="AU57" s="1"/>
-      <c r="AV57" s="1"/>
-      <c r="AW57" s="1"/>
-      <c r="AX57" s="1"/>
-      <c r="AY57" s="1"/>
-      <c r="AZ57" s="1"/>
-      <c r="BA57" s="1"/>
-      <c r="BB57" s="1"/>
-      <c r="BC57" s="1"/>
-      <c r="BD57" s="1"/>
-      <c r="BE57" s="1"/>
-      <c r="BF57" s="1"/>
-      <c r="BG57" s="1"/>
-      <c r="BH57" s="1"/>
-      <c r="BI57" s="1"/>
-      <c r="BJ57" s="1"/>
-      <c r="BK57" s="1"/>
-      <c r="BL57" s="1"/>
-    </row>
-    <row r="58" spans="1:64">
-      <c r="A58" s="1"/>
-      <c r="B58" s="1"/>
-      <c r="C58" s="1"/>
-      <c r="D58" s="1"/>
-      <c r="E58" s="1"/>
-      <c r="F58" s="1"/>
-      <c r="G58" s="1"/>
-      <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="1"/>
-      <c r="K58" s="1"/>
-      <c r="L58" s="1"/>
-      <c r="M58" s="1"/>
-      <c r="N58" s="1"/>
-      <c r="O58" s="1"/>
-      <c r="P58" s="1"/>
-      <c r="Q58" s="1"/>
-      <c r="R58" s="1"/>
-      <c r="S58" s="1"/>
-      <c r="T58" s="1"/>
-      <c r="U58" s="1"/>
-      <c r="V58" s="1"/>
-      <c r="W58" s="1"/>
-      <c r="X58" s="1"/>
-      <c r="Y58" s="1"/>
-      <c r="Z58" s="1"/>
-      <c r="AA58" s="1"/>
-      <c r="AB58" s="1"/>
-      <c r="AC58" s="1"/>
-      <c r="AD58" s="1"/>
-      <c r="AE58" s="1"/>
-      <c r="AF58" s="1"/>
-      <c r="AG58" s="1"/>
-      <c r="AH58" s="1" t="s">
+      <c r="AW57" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="58" spans="15:49">
+      <c r="AG58" t="s">
         <v>2098</v>
       </c>
-      <c r="AI58" s="1"/>
-      <c r="AJ58" s="1"/>
-      <c r="AK58" s="1"/>
-      <c r="AL58" s="1"/>
-      <c r="AM58" s="1"/>
-      <c r="AN58" s="1"/>
-      <c r="AO58" s="1"/>
-      <c r="AP58" s="1"/>
-      <c r="AQ58" s="1"/>
-      <c r="AR58" s="1"/>
-      <c r="AS58" s="1"/>
-      <c r="AT58" s="1"/>
-      <c r="AU58" s="1"/>
-      <c r="AV58" s="1"/>
-      <c r="AW58" s="1"/>
-      <c r="AX58" s="1"/>
-      <c r="AY58" s="1"/>
-      <c r="AZ58" s="1"/>
-      <c r="BA58" s="1"/>
-      <c r="BB58" s="1"/>
-      <c r="BC58" s="1"/>
-      <c r="BD58" s="1"/>
-      <c r="BE58" s="1"/>
-      <c r="BF58" s="1"/>
-      <c r="BG58" s="1"/>
-      <c r="BH58" s="1"/>
-      <c r="BI58" s="1"/>
-      <c r="BJ58" s="1"/>
-      <c r="BK58" s="1"/>
-      <c r="BL58" s="1"/>
-    </row>
-    <row r="59" spans="1:64">
-      <c r="A59" s="1"/>
-      <c r="B59" s="1"/>
-      <c r="C59" s="1"/>
-      <c r="D59" s="1"/>
-      <c r="E59" s="1"/>
-      <c r="F59" s="1"/>
-      <c r="G59" s="1"/>
-      <c r="H59" s="1"/>
-      <c r="I59" s="1"/>
-      <c r="J59" s="1"/>
-      <c r="K59" s="1"/>
-      <c r="L59" s="1"/>
-      <c r="M59" s="1"/>
-      <c r="N59" s="1"/>
-      <c r="O59" s="1"/>
-      <c r="P59" s="1"/>
-      <c r="Q59" s="1"/>
-      <c r="R59" s="1"/>
-      <c r="S59" s="1"/>
-      <c r="T59" s="1"/>
-      <c r="U59" s="1"/>
-      <c r="V59" s="1"/>
-      <c r="W59" s="1"/>
-      <c r="X59" s="1"/>
-      <c r="Y59" s="1"/>
-      <c r="Z59" s="1"/>
-      <c r="AA59" s="1"/>
-      <c r="AB59" s="1"/>
-      <c r="AC59" s="1"/>
-      <c r="AD59" s="1"/>
-      <c r="AE59" s="1"/>
-      <c r="AF59" s="1"/>
-      <c r="AG59" s="1"/>
-      <c r="AH59" s="1" t="s">
+    </row>
+    <row r="59" spans="15:49">
+      <c r="AG59" t="s">
         <v>2099</v>
       </c>
-      <c r="AI59" s="1"/>
-      <c r="AJ59" s="1"/>
-      <c r="AK59" s="1"/>
-      <c r="AL59" s="1"/>
-      <c r="AM59" s="1"/>
-      <c r="AN59" s="1"/>
-      <c r="AO59" s="1"/>
-      <c r="AP59" s="1"/>
-      <c r="AQ59" s="1"/>
-      <c r="AR59" s="1"/>
-      <c r="AS59" s="1"/>
-      <c r="AT59" s="1"/>
-      <c r="AU59" s="1"/>
-      <c r="AV59" s="1"/>
-      <c r="AW59" s="1"/>
-      <c r="AX59" s="1"/>
-      <c r="AY59" s="1"/>
-      <c r="AZ59" s="1"/>
-      <c r="BA59" s="1"/>
-      <c r="BB59" s="1"/>
-      <c r="BC59" s="1"/>
-      <c r="BD59" s="1"/>
-      <c r="BE59" s="1"/>
-      <c r="BF59" s="1"/>
-      <c r="BG59" s="1"/>
-      <c r="BH59" s="1"/>
-      <c r="BI59" s="1"/>
-      <c r="BJ59" s="1"/>
-      <c r="BK59" s="1"/>
-      <c r="BL59" s="1"/>
-    </row>
-    <row r="60" spans="1:64">
-      <c r="A60" s="1"/>
-      <c r="B60" s="1"/>
-      <c r="C60" s="1"/>
-      <c r="D60" s="1"/>
-      <c r="E60" s="1"/>
-      <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
-      <c r="H60" s="1"/>
-      <c r="I60" s="1"/>
-      <c r="J60" s="1"/>
-      <c r="K60" s="1"/>
-      <c r="L60" s="1"/>
-      <c r="M60" s="1"/>
-      <c r="N60" s="1"/>
-      <c r="O60" s="1"/>
-      <c r="P60" s="1"/>
-      <c r="Q60" s="1"/>
-      <c r="R60" s="1"/>
-      <c r="S60" s="1"/>
-      <c r="T60" s="1"/>
-      <c r="U60" s="1"/>
-      <c r="V60" s="1"/>
-      <c r="W60" s="1"/>
-      <c r="X60" s="1"/>
-      <c r="Y60" s="1"/>
-      <c r="Z60" s="1"/>
-      <c r="AA60" s="1"/>
-      <c r="AB60" s="1"/>
-      <c r="AC60" s="1"/>
-      <c r="AD60" s="1"/>
-      <c r="AE60" s="1"/>
-      <c r="AF60" s="1"/>
-      <c r="AG60" s="1"/>
-      <c r="AH60" s="1" t="s">
+    </row>
+    <row r="60" spans="15:49">
+      <c r="AG60" t="s">
         <v>2100</v>
       </c>
-      <c r="AI60" s="1"/>
-      <c r="AJ60" s="1"/>
-      <c r="AK60" s="1"/>
-      <c r="AL60" s="1"/>
-      <c r="AM60" s="1"/>
-      <c r="AN60" s="1"/>
-      <c r="AO60" s="1"/>
-      <c r="AP60" s="1"/>
-      <c r="AQ60" s="1"/>
-      <c r="AR60" s="1"/>
-      <c r="AS60" s="1"/>
-      <c r="AT60" s="1"/>
-      <c r="AU60" s="1"/>
-      <c r="AV60" s="1"/>
-      <c r="AW60" s="1"/>
-      <c r="AX60" s="1"/>
-      <c r="AY60" s="1"/>
-      <c r="AZ60" s="1"/>
-      <c r="BA60" s="1"/>
-      <c r="BB60" s="1"/>
-      <c r="BC60" s="1"/>
-      <c r="BD60" s="1"/>
-      <c r="BE60" s="1"/>
-      <c r="BF60" s="1"/>
-      <c r="BG60" s="1"/>
-      <c r="BH60" s="1"/>
-      <c r="BI60" s="1"/>
-      <c r="BJ60" s="1"/>
-      <c r="BK60" s="1"/>
-      <c r="BL60" s="1"/>
-    </row>
-    <row r="61" spans="1:64">
-      <c r="A61" s="1"/>
-      <c r="B61" s="1"/>
-      <c r="C61" s="1"/>
-      <c r="D61" s="1"/>
-      <c r="E61" s="1"/>
-      <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
-      <c r="H61" s="1"/>
-      <c r="I61" s="1"/>
-      <c r="J61" s="1"/>
-      <c r="K61" s="1"/>
-      <c r="L61" s="1"/>
-      <c r="M61" s="1"/>
-      <c r="N61" s="1"/>
-      <c r="O61" s="1"/>
-      <c r="P61" s="1"/>
-      <c r="Q61" s="1"/>
-      <c r="R61" s="1"/>
-      <c r="S61" s="1"/>
-      <c r="T61" s="1"/>
-      <c r="U61" s="1"/>
-      <c r="V61" s="1"/>
-      <c r="W61" s="1"/>
-      <c r="X61" s="1"/>
-      <c r="Y61" s="1"/>
-      <c r="Z61" s="1"/>
-      <c r="AA61" s="1"/>
-      <c r="AB61" s="1"/>
-      <c r="AC61" s="1"/>
-      <c r="AD61" s="1"/>
-      <c r="AE61" s="1"/>
-      <c r="AF61" s="1"/>
-      <c r="AG61" s="1"/>
-      <c r="AH61" s="1" t="s">
+    </row>
+    <row r="61" spans="15:49">
+      <c r="AG61" t="s">
         <v>1843</v>
       </c>
-      <c r="AI61" s="1"/>
-      <c r="AJ61" s="1"/>
-      <c r="AK61" s="1"/>
-      <c r="AL61" s="1"/>
-      <c r="AM61" s="1"/>
-      <c r="AN61" s="1"/>
-      <c r="AO61" s="1"/>
-      <c r="AP61" s="1"/>
-      <c r="AQ61" s="1"/>
-      <c r="AR61" s="1"/>
-      <c r="AS61" s="1"/>
-      <c r="AT61" s="1"/>
-      <c r="AU61" s="1"/>
-      <c r="AV61" s="1"/>
-      <c r="AW61" s="1"/>
-      <c r="AX61" s="1"/>
-      <c r="AY61" s="1"/>
-      <c r="AZ61" s="1"/>
-      <c r="BA61" s="1"/>
-      <c r="BB61" s="1"/>
-      <c r="BC61" s="1"/>
-      <c r="BD61" s="1"/>
-      <c r="BE61" s="1"/>
-      <c r="BF61" s="1"/>
-      <c r="BG61" s="1"/>
-      <c r="BH61" s="1"/>
-      <c r="BI61" s="1"/>
-      <c r="BJ61" s="1"/>
-      <c r="BK61" s="1"/>
-      <c r="BL61" s="1"/>
-    </row>
-    <row r="62" spans="1:64">
-      <c r="A62" s="1"/>
-      <c r="B62" s="1"/>
-      <c r="C62" s="1"/>
-      <c r="D62" s="1"/>
-      <c r="E62" s="1"/>
-      <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
-      <c r="I62" s="1"/>
-      <c r="J62" s="1"/>
-      <c r="K62" s="1"/>
-      <c r="L62" s="1"/>
-      <c r="M62" s="1"/>
-      <c r="N62" s="1"/>
-      <c r="O62" s="1"/>
-      <c r="P62" s="1"/>
-      <c r="Q62" s="1"/>
-      <c r="R62" s="1"/>
-      <c r="S62" s="1"/>
-      <c r="T62" s="1"/>
-      <c r="U62" s="1"/>
-      <c r="V62" s="1"/>
-      <c r="W62" s="1"/>
-      <c r="X62" s="1"/>
-      <c r="Y62" s="1"/>
-      <c r="Z62" s="1"/>
-      <c r="AA62" s="1"/>
-      <c r="AB62" s="1"/>
-      <c r="AC62" s="1"/>
-      <c r="AD62" s="1"/>
-      <c r="AE62" s="1"/>
-      <c r="AF62" s="1"/>
-      <c r="AG62" s="1"/>
-      <c r="AH62" s="1" t="s">
+    </row>
+    <row r="62" spans="15:49">
+      <c r="AG62" t="s">
         <v>1944</v>
       </c>
-      <c r="AI62" s="1"/>
-      <c r="AJ62" s="1"/>
-      <c r="AK62" s="1"/>
-      <c r="AL62" s="1"/>
-      <c r="AM62" s="1"/>
-      <c r="AN62" s="1"/>
-      <c r="AO62" s="1"/>
-      <c r="AP62" s="1"/>
-      <c r="AQ62" s="1"/>
-      <c r="AR62" s="1"/>
-      <c r="AS62" s="1"/>
-      <c r="AT62" s="1"/>
-      <c r="AU62" s="1"/>
-      <c r="AV62" s="1"/>
-      <c r="AW62" s="1"/>
-      <c r="AX62" s="1"/>
-      <c r="AY62" s="1"/>
-      <c r="AZ62" s="1"/>
-      <c r="BA62" s="1"/>
-      <c r="BB62" s="1"/>
-      <c r="BC62" s="1"/>
-      <c r="BD62" s="1"/>
-      <c r="BE62" s="1"/>
-      <c r="BF62" s="1"/>
-      <c r="BG62" s="1"/>
-      <c r="BH62" s="1"/>
-      <c r="BI62" s="1"/>
-      <c r="BJ62" s="1"/>
-      <c r="BK62" s="1"/>
-      <c r="BL62" s="1"/>
-    </row>
-    <row r="63" spans="1:64">
-      <c r="A63" s="1"/>
-      <c r="B63" s="1"/>
-      <c r="C63" s="1"/>
-      <c r="D63" s="1"/>
-      <c r="E63" s="1"/>
-      <c r="F63" s="1"/>
-      <c r="G63" s="1"/>
-      <c r="H63" s="1"/>
-      <c r="I63" s="1"/>
-      <c r="J63" s="1"/>
-      <c r="K63" s="1"/>
-      <c r="L63" s="1"/>
-      <c r="M63" s="1"/>
-      <c r="N63" s="1"/>
-      <c r="O63" s="1"/>
-      <c r="P63" s="1"/>
-      <c r="Q63" s="1"/>
-      <c r="R63" s="1"/>
-      <c r="S63" s="1"/>
-      <c r="T63" s="1"/>
-      <c r="U63" s="1"/>
-      <c r="V63" s="1"/>
-      <c r="W63" s="1"/>
-      <c r="X63" s="1"/>
-      <c r="Y63" s="1"/>
-      <c r="Z63" s="1"/>
-      <c r="AA63" s="1"/>
-      <c r="AB63" s="1"/>
-      <c r="AC63" s="1"/>
-      <c r="AD63" s="1"/>
-      <c r="AE63" s="1"/>
-      <c r="AF63" s="1"/>
-      <c r="AG63" s="1"/>
-      <c r="AH63" s="1" t="s">
+    </row>
+    <row r="63" spans="15:49">
+      <c r="AG63" t="s">
         <v>1945</v>
       </c>
-      <c r="AI63" s="1"/>
-      <c r="AJ63" s="1"/>
-      <c r="AK63" s="1"/>
-      <c r="AL63" s="1"/>
-      <c r="AM63" s="1"/>
-      <c r="AN63" s="1"/>
-      <c r="AO63" s="1"/>
-      <c r="AP63" s="1"/>
-      <c r="AQ63" s="1"/>
-      <c r="AR63" s="1"/>
-      <c r="AS63" s="1"/>
-      <c r="AT63" s="1"/>
-      <c r="AU63" s="1"/>
-      <c r="AV63" s="1"/>
-      <c r="AW63" s="1"/>
-      <c r="AX63" s="1"/>
-      <c r="AY63" s="1"/>
-      <c r="AZ63" s="1"/>
-      <c r="BA63" s="1"/>
-      <c r="BB63" s="1"/>
-      <c r="BC63" s="1"/>
-      <c r="BD63" s="1"/>
-      <c r="BE63" s="1"/>
-      <c r="BF63" s="1"/>
-      <c r="BG63" s="1"/>
-      <c r="BH63" s="1"/>
-      <c r="BI63" s="1"/>
-      <c r="BJ63" s="1"/>
-      <c r="BK63" s="1"/>
-      <c r="BL63" s="1"/>
-    </row>
-    <row r="64" spans="1:64">
-      <c r="A64" s="1"/>
-      <c r="B64" s="1"/>
-      <c r="C64" s="1"/>
-      <c r="D64" s="1"/>
-      <c r="E64" s="1"/>
-      <c r="F64" s="1"/>
-      <c r="G64" s="1"/>
-      <c r="H64" s="1"/>
-      <c r="I64" s="1"/>
-      <c r="J64" s="1"/>
-      <c r="K64" s="1"/>
-      <c r="L64" s="1"/>
-      <c r="M64" s="1"/>
-      <c r="N64" s="1"/>
-      <c r="O64" s="1"/>
-      <c r="P64" s="1"/>
-      <c r="Q64" s="1"/>
-      <c r="R64" s="1"/>
-      <c r="S64" s="1"/>
-      <c r="T64" s="1"/>
-      <c r="U64" s="1"/>
-      <c r="V64" s="1"/>
-      <c r="W64" s="1"/>
-      <c r="X64" s="1"/>
-      <c r="Y64" s="1"/>
-      <c r="Z64" s="1"/>
-      <c r="AA64" s="1"/>
-      <c r="AB64" s="1"/>
-      <c r="AC64" s="1"/>
-      <c r="AD64" s="1"/>
-      <c r="AE64" s="1"/>
-      <c r="AF64" s="1"/>
-      <c r="AG64" s="1"/>
-      <c r="AH64" s="1" t="s">
+    </row>
+    <row r="64" spans="15:49">
+      <c r="AG64" t="s">
         <v>1827</v>
       </c>
-      <c r="AI64" s="1"/>
-      <c r="AJ64" s="1"/>
-      <c r="AK64" s="1"/>
-      <c r="AL64" s="1"/>
-      <c r="AM64" s="1"/>
-      <c r="AN64" s="1"/>
-      <c r="AO64" s="1"/>
-      <c r="AP64" s="1"/>
-      <c r="AQ64" s="1"/>
-      <c r="AR64" s="1"/>
-      <c r="AS64" s="1"/>
-      <c r="AT64" s="1"/>
-      <c r="AU64" s="1"/>
-      <c r="AV64" s="1"/>
-      <c r="AW64" s="1"/>
-      <c r="AX64" s="1"/>
-      <c r="AY64" s="1"/>
-      <c r="AZ64" s="1"/>
-      <c r="BA64" s="1"/>
-      <c r="BB64" s="1"/>
-      <c r="BC64" s="1"/>
-      <c r="BD64" s="1"/>
-      <c r="BE64" s="1"/>
-      <c r="BF64" s="1"/>
-      <c r="BG64" s="1"/>
-      <c r="BH64" s="1"/>
-      <c r="BI64" s="1"/>
-      <c r="BJ64" s="1"/>
-      <c r="BK64" s="1"/>
-      <c r="BL64" s="1"/>
-    </row>
-    <row r="65" spans="1:64">
-      <c r="A65" s="1"/>
-      <c r="B65" s="1"/>
-      <c r="C65" s="1"/>
-      <c r="D65" s="1"/>
-      <c r="E65" s="1"/>
-      <c r="F65" s="1"/>
-      <c r="G65" s="1"/>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
-      <c r="J65" s="1"/>
-      <c r="K65" s="1"/>
-      <c r="L65" s="1"/>
-      <c r="M65" s="1"/>
-      <c r="N65" s="1"/>
-      <c r="O65" s="1"/>
-      <c r="P65" s="1"/>
-      <c r="Q65" s="1"/>
-      <c r="R65" s="1"/>
-      <c r="S65" s="1"/>
-      <c r="T65" s="1"/>
-      <c r="U65" s="1"/>
-      <c r="V65" s="1"/>
-      <c r="W65" s="1"/>
-      <c r="X65" s="1"/>
-      <c r="Y65" s="1"/>
-      <c r="Z65" s="1"/>
-      <c r="AA65" s="1"/>
-      <c r="AB65" s="1"/>
-      <c r="AC65" s="1"/>
-      <c r="AD65" s="1"/>
-      <c r="AE65" s="1"/>
-      <c r="AF65" s="1"/>
-      <c r="AG65" s="1"/>
-      <c r="AH65" s="1" t="s">
+    </row>
+    <row r="65" spans="33:33">
+      <c r="AG65" t="s">
         <v>2101</v>
       </c>
-      <c r="AI65" s="1"/>
-      <c r="AJ65" s="1"/>
-      <c r="AK65" s="1"/>
-      <c r="AL65" s="1"/>
-      <c r="AM65" s="1"/>
-      <c r="AN65" s="1"/>
-      <c r="AO65" s="1"/>
-      <c r="AP65" s="1"/>
-      <c r="AQ65" s="1"/>
-      <c r="AR65" s="1"/>
-      <c r="AS65" s="1"/>
-      <c r="AT65" s="1"/>
-      <c r="AU65" s="1"/>
-      <c r="AV65" s="1"/>
-      <c r="AW65" s="1"/>
-      <c r="AX65" s="1"/>
-      <c r="AY65" s="1"/>
-      <c r="AZ65" s="1"/>
-      <c r="BA65" s="1"/>
-      <c r="BB65" s="1"/>
-      <c r="BC65" s="1"/>
-      <c r="BD65" s="1"/>
-      <c r="BE65" s="1"/>
-      <c r="BF65" s="1"/>
-      <c r="BG65" s="1"/>
-      <c r="BH65" s="1"/>
-      <c r="BI65" s="1"/>
-      <c r="BJ65" s="1"/>
-      <c r="BK65" s="1"/>
-      <c r="BL65" s="1"/>
-    </row>
-    <row r="66" spans="1:64">
-      <c r="A66" s="1"/>
-      <c r="B66" s="1"/>
-      <c r="C66" s="1"/>
-      <c r="D66" s="1"/>
-      <c r="E66" s="1"/>
-      <c r="F66" s="1"/>
-      <c r="G66" s="1"/>
-      <c r="H66" s="1"/>
-      <c r="I66" s="1"/>
-      <c r="J66" s="1"/>
-      <c r="K66" s="1"/>
-      <c r="L66" s="1"/>
-      <c r="M66" s="1"/>
-      <c r="N66" s="1"/>
-      <c r="O66" s="1"/>
-      <c r="P66" s="1"/>
-      <c r="Q66" s="1"/>
-      <c r="R66" s="1"/>
-      <c r="S66" s="1"/>
-      <c r="T66" s="1"/>
-      <c r="U66" s="1"/>
-      <c r="V66" s="1"/>
-      <c r="W66" s="1"/>
-      <c r="X66" s="1"/>
-      <c r="Y66" s="1"/>
-      <c r="Z66" s="1"/>
-      <c r="AA66" s="1"/>
-      <c r="AB66" s="1"/>
-      <c r="AC66" s="1"/>
-      <c r="AD66" s="1"/>
-      <c r="AE66" s="1"/>
-      <c r="AF66" s="1"/>
-      <c r="AG66" s="1"/>
-      <c r="AH66" s="1" t="s">
+    </row>
+    <row r="66" spans="33:33">
+      <c r="AG66" t="s">
         <v>235</v>
       </c>
-      <c r="AI66" s="1"/>
-      <c r="AJ66" s="1"/>
-      <c r="AK66" s="1"/>
-      <c r="AL66" s="1"/>
-      <c r="AM66" s="1"/>
-      <c r="AN66" s="1"/>
-      <c r="AO66" s="1"/>
-      <c r="AP66" s="1"/>
-      <c r="AQ66" s="1"/>
-      <c r="AR66" s="1"/>
-      <c r="AS66" s="1"/>
-      <c r="AT66" s="1"/>
-      <c r="AU66" s="1"/>
-      <c r="AV66" s="1"/>
-      <c r="AW66" s="1"/>
-      <c r="AX66" s="1"/>
-      <c r="AY66" s="1"/>
-      <c r="AZ66" s="1"/>
-      <c r="BA66" s="1"/>
-      <c r="BB66" s="1"/>
-      <c r="BC66" s="1"/>
-      <c r="BD66" s="1"/>
-      <c r="BE66" s="1"/>
-      <c r="BF66" s="1"/>
-      <c r="BG66" s="1"/>
-      <c r="BH66" s="1"/>
-      <c r="BI66" s="1"/>
-      <c r="BJ66" s="1"/>
-      <c r="BK66" s="1"/>
-      <c r="BL66" s="1"/>
-    </row>
-    <row r="67" spans="1:64">
-      <c r="A67" s="1"/>
-      <c r="B67" s="1"/>
-      <c r="C67" s="1"/>
-      <c r="D67" s="1"/>
-      <c r="E67" s="1"/>
-      <c r="F67" s="1"/>
-      <c r="G67" s="1"/>
-      <c r="H67" s="1"/>
-      <c r="I67" s="1"/>
-      <c r="J67" s="1"/>
-      <c r="K67" s="1"/>
-      <c r="L67" s="1"/>
-      <c r="M67" s="1"/>
-      <c r="N67" s="1"/>
-      <c r="O67" s="1"/>
-      <c r="P67" s="1"/>
-      <c r="Q67" s="1"/>
-      <c r="R67" s="1"/>
-      <c r="S67" s="1"/>
-      <c r="T67" s="1"/>
-      <c r="U67" s="1"/>
-      <c r="V67" s="1"/>
-      <c r="W67" s="1"/>
-      <c r="X67" s="1"/>
-      <c r="Y67" s="1"/>
-      <c r="Z67" s="1"/>
-      <c r="AA67" s="1"/>
-      <c r="AB67" s="1"/>
-      <c r="AC67" s="1"/>
-      <c r="AD67" s="1"/>
-      <c r="AE67" s="1"/>
-      <c r="AF67" s="1"/>
-      <c r="AG67" s="1"/>
-      <c r="AH67" s="1" t="s">
+    </row>
+    <row r="67" spans="33:33">
+      <c r="AG67" t="s">
         <v>2093</v>
       </c>
-      <c r="AI67" s="1"/>
-      <c r="AJ67" s="1"/>
-      <c r="AK67" s="1"/>
-      <c r="AL67" s="1"/>
-      <c r="AM67" s="1"/>
-      <c r="AN67" s="1"/>
-      <c r="AO67" s="1"/>
-      <c r="AP67" s="1"/>
-      <c r="AQ67" s="1"/>
-      <c r="AR67" s="1"/>
-      <c r="AS67" s="1"/>
-      <c r="AT67" s="1"/>
-      <c r="AU67" s="1"/>
-      <c r="AV67" s="1"/>
-      <c r="AW67" s="1"/>
-      <c r="AX67" s="1"/>
-      <c r="AY67" s="1"/>
-      <c r="AZ67" s="1"/>
-      <c r="BA67" s="1"/>
-      <c r="BB67" s="1"/>
-      <c r="BC67" s="1"/>
-      <c r="BD67" s="1"/>
-      <c r="BE67" s="1"/>
-      <c r="BF67" s="1"/>
-      <c r="BG67" s="1"/>
-      <c r="BH67" s="1"/>
-      <c r="BI67" s="1"/>
-      <c r="BJ67" s="1"/>
-      <c r="BK67" s="1"/>
-      <c r="BL67" s="1"/>
-    </row>
-    <row r="68" spans="1:64">
-      <c r="A68" s="1"/>
-      <c r="B68" s="1"/>
-      <c r="C68" s="1"/>
-      <c r="D68" s="1"/>
-      <c r="E68" s="1"/>
-      <c r="F68" s="1"/>
-      <c r="G68" s="1"/>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
-      <c r="J68" s="1"/>
-      <c r="K68" s="1"/>
-      <c r="L68" s="1"/>
-      <c r="M68" s="1"/>
-      <c r="N68" s="1"/>
-      <c r="O68" s="1"/>
-      <c r="P68" s="1"/>
-      <c r="Q68" s="1"/>
-      <c r="R68" s="1"/>
-      <c r="S68" s="1"/>
-      <c r="T68" s="1"/>
-      <c r="U68" s="1"/>
-      <c r="V68" s="1"/>
-      <c r="W68" s="1"/>
-      <c r="X68" s="1"/>
-      <c r="Y68" s="1"/>
-      <c r="Z68" s="1"/>
-      <c r="AA68" s="1"/>
-      <c r="AB68" s="1"/>
-      <c r="AC68" s="1"/>
-      <c r="AD68" s="1"/>
-      <c r="AE68" s="1"/>
-      <c r="AF68" s="1"/>
-      <c r="AG68" s="1"/>
-      <c r="AH68" s="1" t="s">
+    </row>
+    <row r="68" spans="33:33">
+      <c r="AG68" t="s">
         <v>2102</v>
       </c>
-      <c r="AI68" s="1"/>
-      <c r="AJ68" s="1"/>
-      <c r="AK68" s="1"/>
-      <c r="AL68" s="1"/>
-      <c r="AM68" s="1"/>
-      <c r="AN68" s="1"/>
-      <c r="AO68" s="1"/>
-      <c r="AP68" s="1"/>
-      <c r="AQ68" s="1"/>
-      <c r="AR68" s="1"/>
-      <c r="AS68" s="1"/>
-      <c r="AT68" s="1"/>
-      <c r="AU68" s="1"/>
-      <c r="AV68" s="1"/>
-      <c r="AW68" s="1"/>
-      <c r="AX68" s="1"/>
-      <c r="AY68" s="1"/>
-      <c r="AZ68" s="1"/>
-      <c r="BA68" s="1"/>
-      <c r="BB68" s="1"/>
-      <c r="BC68" s="1"/>
-      <c r="BD68" s="1"/>
-      <c r="BE68" s="1"/>
-      <c r="BF68" s="1"/>
-      <c r="BG68" s="1"/>
-      <c r="BH68" s="1"/>
-      <c r="BI68" s="1"/>
-      <c r="BJ68" s="1"/>
-      <c r="BK68" s="1"/>
-      <c r="BL68" s="1"/>
+    </row>
+    <row r="69" spans="33:33">
+      <c r="AG69" t="s">
+        <v>2205</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/TMS Database mapping.xlsx
+++ b/TMS Database mapping.xlsx
@@ -7097,9 +7097,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -7108,6 +7105,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -56035,194 +56035,194 @@
     <col min="63" max="63" width="22.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:63" s="33" customFormat="1">
-      <c r="A2" s="33" t="s">
+    <row r="2" spans="1:63" s="32" customFormat="1">
+      <c r="A2" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="C2" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="33" t="s">
+      <c r="D2" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="33" t="s">
+      <c r="E2" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="34" t="s">
+      <c r="F2" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="G2" s="33" t="s">
+      <c r="G2" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="H2" s="33" t="s">
+      <c r="H2" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="I2" s="33" t="s">
+      <c r="I2" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="J2" s="33" t="s">
+      <c r="J2" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="K2" s="33" t="s">
+      <c r="K2" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="L2" s="33" t="s">
+      <c r="L2" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="M2" s="33" t="s">
+      <c r="M2" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="N2" s="33" t="s">
+      <c r="N2" s="32" t="s">
         <v>71</v>
       </c>
-      <c r="O2" s="34" t="s">
+      <c r="O2" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="P2" s="34" t="s">
+      <c r="P2" s="33" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="34" t="s">
+      <c r="Q2" s="33" t="s">
         <v>82</v>
       </c>
-      <c r="R2" s="33" t="s">
+      <c r="R2" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="S2" s="33" t="s">
+      <c r="S2" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="T2" s="34" t="s">
+      <c r="T2" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="U2" s="33" t="s">
+      <c r="U2" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="V2" s="34" t="s">
+      <c r="V2" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="W2" s="33" t="s">
+      <c r="W2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="X2" s="35" t="s">
+      <c r="X2" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="Y2" s="35" t="s">
+      <c r="Y2" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="Z2" s="35" t="s">
+      <c r="Z2" s="34" t="s">
         <v>108</v>
       </c>
-      <c r="AA2" s="35" t="s">
+      <c r="AA2" s="34" t="s">
         <v>113</v>
       </c>
-      <c r="AB2" s="35" t="s">
+      <c r="AB2" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="AC2" s="33" t="s">
+      <c r="AC2" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="AD2" s="33" t="s">
+      <c r="AD2" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="AE2" s="33" t="s">
+      <c r="AE2" s="32" t="s">
         <v>130</v>
       </c>
-      <c r="AF2" s="33" t="s">
+      <c r="AF2" s="32" t="s">
         <v>134</v>
       </c>
-      <c r="AG2" s="34" t="s">
+      <c r="AG2" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="AH2" s="33" t="s">
+      <c r="AH2" s="32" t="s">
         <v>139</v>
       </c>
-      <c r="AI2" s="33" t="s">
+      <c r="AI2" s="32" t="s">
         <v>143</v>
       </c>
-      <c r="AJ2" s="33" t="s">
+      <c r="AJ2" s="32" t="s">
         <v>147</v>
       </c>
-      <c r="AK2" s="33" t="s">
+      <c r="AK2" s="32" t="s">
         <v>150</v>
       </c>
-      <c r="AL2" s="33" t="s">
+      <c r="AL2" s="32" t="s">
         <v>154</v>
       </c>
-      <c r="AM2" s="33" t="s">
+      <c r="AM2" s="32" t="s">
         <v>158</v>
       </c>
-      <c r="AN2" s="33" t="s">
+      <c r="AN2" s="32" t="s">
         <v>161</v>
       </c>
-      <c r="AO2" s="33" t="s">
+      <c r="AO2" s="32" t="s">
         <v>164</v>
       </c>
-      <c r="AP2" s="34" t="s">
+      <c r="AP2" s="33" t="s">
         <v>168</v>
       </c>
-      <c r="AQ2" s="34" t="s">
+      <c r="AQ2" s="33" t="s">
         <v>172</v>
       </c>
-      <c r="AR2" s="33" t="s">
+      <c r="AR2" s="32" t="s">
         <v>176</v>
       </c>
-      <c r="AS2" s="33" t="s">
+      <c r="AS2" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="AT2" s="33" t="s">
+      <c r="AT2" s="32" t="s">
         <v>181</v>
       </c>
-      <c r="AU2" s="34" t="s">
+      <c r="AU2" s="33" t="s">
         <v>183</v>
       </c>
-      <c r="AV2" s="33" t="s">
+      <c r="AV2" s="32" t="s">
         <v>190</v>
       </c>
-      <c r="AW2" s="34" t="s">
+      <c r="AW2" s="33" t="s">
         <v>194</v>
       </c>
-      <c r="AX2" s="34" t="s">
+      <c r="AX2" s="33" t="s">
         <v>196</v>
       </c>
-      <c r="AY2" s="33" t="s">
+      <c r="AY2" s="32" t="s">
         <v>202</v>
       </c>
-      <c r="AZ2" s="33" t="s">
+      <c r="AZ2" s="32" t="s">
         <v>205</v>
       </c>
-      <c r="BA2" s="34" t="s">
+      <c r="BA2" s="33" t="s">
         <v>208</v>
       </c>
-      <c r="BB2" s="33" t="s">
+      <c r="BB2" s="32" t="s">
         <v>211</v>
       </c>
-      <c r="BC2" s="33" t="s">
+      <c r="BC2" s="32" t="s">
         <v>215</v>
       </c>
-      <c r="BD2" s="34" t="s">
+      <c r="BD2" s="33" t="s">
         <v>219</v>
       </c>
-      <c r="BE2" s="33" t="s">
+      <c r="BE2" s="32" t="s">
         <v>223</v>
       </c>
-      <c r="BF2" s="33" t="s">
+      <c r="BF2" s="32" t="s">
         <v>227</v>
       </c>
-      <c r="BG2" s="34" t="s">
+      <c r="BG2" s="33" t="s">
         <v>231</v>
       </c>
-      <c r="BH2" s="33" t="s">
+      <c r="BH2" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="BI2" s="33" t="s">
+      <c r="BI2" s="32" t="s">
         <v>236</v>
       </c>
-      <c r="BJ2" s="33" t="s">
+      <c r="BJ2" s="32" t="s">
         <v>238</v>
       </c>
-      <c r="BK2" s="33" t="s">
+      <c r="BK2" s="32" t="s">
         <v>240</v>
       </c>
     </row>
@@ -56324,7 +56324,7 @@
         <v>360</v>
       </c>
       <c r="AG3" t="s">
-        <v>360</v>
+        <v>1951</v>
       </c>
       <c r="AH3" t="s">
         <v>360</v>
@@ -56515,7 +56515,7 @@
         <v>1453</v>
       </c>
       <c r="AG4" t="s">
-        <v>1951</v>
+        <v>643</v>
       </c>
       <c r="AH4" t="s">
         <v>1453</v>
@@ -56688,7 +56688,7 @@
         <v>1970</v>
       </c>
       <c r="AG5" t="s">
-        <v>1971</v>
+        <v>2100</v>
       </c>
       <c r="AH5" t="s">
         <v>1972</v>
@@ -56846,7 +56846,7 @@
         <v>376</v>
       </c>
       <c r="AG6" t="s">
-        <v>640</v>
+        <v>1971</v>
       </c>
       <c r="AH6" t="s">
         <v>376</v>
@@ -56992,7 +56992,7 @@
         <v>1089</v>
       </c>
       <c r="AG7" t="s">
-        <v>1996</v>
+        <v>640</v>
       </c>
       <c r="AI7" t="s">
         <v>1089</v>
@@ -57126,7 +57126,7 @@
         <v>1148</v>
       </c>
       <c r="AG8" t="s">
-        <v>2006</v>
+        <v>1996</v>
       </c>
       <c r="AI8" t="s">
         <v>1148</v>
@@ -57239,7 +57239,7 @@
         <v>1022</v>
       </c>
       <c r="AG9" t="s">
-        <v>2015</v>
+        <v>962</v>
       </c>
       <c r="AI9" t="s">
         <v>1022</v>
@@ -57322,7 +57322,7 @@
         <v>525</v>
       </c>
       <c r="AG10" t="s">
-        <v>944</v>
+        <v>2006</v>
       </c>
       <c r="AK10" t="s">
         <v>626</v>
@@ -57375,7 +57375,7 @@
         <v>2026</v>
       </c>
       <c r="AG11" t="s">
-        <v>808</v>
+        <v>2015</v>
       </c>
       <c r="AK11" t="s">
         <v>590</v>
@@ -57425,7 +57425,7 @@
         <v>2029</v>
       </c>
       <c r="AG12" t="s">
-        <v>2030</v>
+        <v>889</v>
       </c>
       <c r="AQ12" t="s">
         <v>2031</v>
@@ -57472,7 +57472,7 @@
         <v>2034</v>
       </c>
       <c r="AG13" t="s">
-        <v>2035</v>
+        <v>606</v>
       </c>
       <c r="AQ13" t="s">
         <v>2036</v>
@@ -57516,7 +57516,7 @@
         <v>2041</v>
       </c>
       <c r="AG14" t="s">
-        <v>2042</v>
+        <v>944</v>
       </c>
       <c r="AQ14" t="s">
         <v>1084</v>
@@ -57551,7 +57551,7 @@
         <v>1876</v>
       </c>
       <c r="AG15" t="s">
-        <v>1960</v>
+        <v>808</v>
       </c>
       <c r="AQ15" t="s">
         <v>2044</v>
@@ -57586,7 +57586,7 @@
         <v>1412</v>
       </c>
       <c r="AG16" t="s">
-        <v>2047</v>
+        <v>2085</v>
       </c>
       <c r="AQ16" t="s">
         <v>962</v>
@@ -57621,7 +57621,7 @@
         <v>1880</v>
       </c>
       <c r="AG17" t="s">
-        <v>370</v>
+        <v>2030</v>
       </c>
       <c r="AQ17" t="s">
         <v>1609</v>
@@ -57653,7 +57653,7 @@
         <v>1439</v>
       </c>
       <c r="AG18" t="s">
-        <v>2051</v>
+        <v>1047</v>
       </c>
       <c r="AQ18" t="s">
         <v>271</v>
@@ -57682,7 +57682,7 @@
         <v>1557</v>
       </c>
       <c r="AG19" t="s">
-        <v>2054</v>
+        <v>1821</v>
       </c>
       <c r="AQ19" t="s">
         <v>1637</v>
@@ -57711,7 +57711,7 @@
         <v>1290</v>
       </c>
       <c r="AG20" t="s">
-        <v>2057</v>
+        <v>2035</v>
       </c>
       <c r="AQ20" t="s">
         <v>889</v>
@@ -57737,7 +57737,7 @@
         <v>1750</v>
       </c>
       <c r="AG21" t="s">
-        <v>1961</v>
+        <v>2042</v>
       </c>
       <c r="AQ21" t="s">
         <v>1843</v>
@@ -57763,7 +57763,7 @@
         <v>1462</v>
       </c>
       <c r="AG22" t="s">
-        <v>1978</v>
+        <v>2096</v>
       </c>
       <c r="AQ22" t="s">
         <v>1848</v>
@@ -57786,7 +57786,7 @@
         <v>2062</v>
       </c>
       <c r="AG23" t="s">
-        <v>1990</v>
+        <v>1960</v>
       </c>
       <c r="AQ23" t="s">
         <v>1827</v>
@@ -57809,7 +57809,7 @@
         <v>2063</v>
       </c>
       <c r="AG24" t="s">
-        <v>2064</v>
+        <v>2047</v>
       </c>
       <c r="AQ24" t="s">
         <v>1837</v>
@@ -57832,7 +57832,7 @@
         <v>2066</v>
       </c>
       <c r="AG25" t="s">
-        <v>2067</v>
+        <v>370</v>
       </c>
       <c r="AQ25" t="s">
         <v>926</v>
@@ -57852,7 +57852,7 @@
         <v>1963</v>
       </c>
       <c r="AG26" t="s">
-        <v>376</v>
+        <v>2097</v>
       </c>
       <c r="AQ26" t="s">
         <v>991</v>
@@ -57872,7 +57872,7 @@
         <v>608</v>
       </c>
       <c r="AG27" t="s">
-        <v>991</v>
+        <v>2098</v>
       </c>
       <c r="AQ27" t="s">
         <v>1642</v>
@@ -57892,7 +57892,7 @@
         <v>644</v>
       </c>
       <c r="AG28" t="s">
-        <v>2045</v>
+        <v>2051</v>
       </c>
       <c r="AQ28" t="s">
         <v>553</v>
@@ -57909,7 +57909,7 @@
         <v>366</v>
       </c>
       <c r="AG29" t="s">
-        <v>2071</v>
+        <v>360</v>
       </c>
       <c r="AQ29" t="s">
         <v>2072</v>
@@ -57926,7 +57926,7 @@
         <v>1004</v>
       </c>
       <c r="AG30" t="s">
-        <v>2073</v>
+        <v>2054</v>
       </c>
       <c r="AQ30" t="s">
         <v>2074</v>
@@ -57943,7 +57943,7 @@
         <v>1069</v>
       </c>
       <c r="AG31" t="s">
-        <v>2075</v>
+        <v>2057</v>
       </c>
       <c r="AQ31" t="s">
         <v>2203</v>
@@ -57960,7 +57960,7 @@
         <v>2080</v>
       </c>
       <c r="AG32" t="s">
-        <v>636</v>
+        <v>1961</v>
       </c>
       <c r="AW32" t="s">
         <v>1376</v>
@@ -57971,7 +57971,7 @@
         <v>662</v>
       </c>
       <c r="AG33" t="s">
-        <v>2076</v>
+        <v>1978</v>
       </c>
       <c r="AW33" t="s">
         <v>1397</v>
@@ -57982,7 +57982,7 @@
         <v>366</v>
       </c>
       <c r="AG34" t="s">
-        <v>2077</v>
+        <v>1990</v>
       </c>
       <c r="AW34" t="s">
         <v>1424</v>
@@ -57993,7 +57993,7 @@
         <v>1043</v>
       </c>
       <c r="AG35" t="s">
-        <v>2078</v>
+        <v>2064</v>
       </c>
       <c r="AW35" t="s">
         <v>897</v>
@@ -58004,7 +58004,7 @@
         <v>271</v>
       </c>
       <c r="AG36" t="s">
-        <v>2079</v>
+        <v>2067</v>
       </c>
       <c r="AW36" t="s">
         <v>1563</v>
@@ -58015,7 +58015,7 @@
         <v>2080</v>
       </c>
       <c r="AG37" t="s">
-        <v>2081</v>
+        <v>2205</v>
       </c>
       <c r="AW37" t="s">
         <v>1732</v>
@@ -58026,7 +58026,7 @@
         <v>991</v>
       </c>
       <c r="AG38" t="s">
-        <v>2082</v>
+        <v>2102</v>
       </c>
       <c r="AW38" t="s">
         <v>1501</v>
@@ -58037,7 +58037,7 @@
         <v>889</v>
       </c>
       <c r="AG39" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AW39" t="s">
         <v>1527</v>
@@ -58048,7 +58048,7 @@
         <v>2083</v>
       </c>
       <c r="AG40" t="s">
-        <v>1553</v>
+        <v>991</v>
       </c>
       <c r="AW40" t="s">
         <v>1046</v>
@@ -58059,7 +58059,7 @@
         <v>2084</v>
       </c>
       <c r="AG41" t="s">
-        <v>2085</v>
+        <v>2095</v>
       </c>
       <c r="AW41" t="s">
         <v>1114</v>
@@ -58070,7 +58070,7 @@
         <v>2086</v>
       </c>
       <c r="AG42" t="s">
-        <v>2087</v>
+        <v>235</v>
       </c>
       <c r="AW42" t="s">
         <v>1581</v>
@@ -58081,7 +58081,7 @@
         <v>2088</v>
       </c>
       <c r="AG43" t="s">
-        <v>2089</v>
+        <v>1486</v>
       </c>
       <c r="AW43" t="s">
         <v>1548</v>
@@ -58092,7 +58092,7 @@
         <v>574</v>
       </c>
       <c r="AG44" t="s">
-        <v>271</v>
+        <v>1513</v>
       </c>
       <c r="AW44" t="s">
         <v>1597</v>
@@ -58103,7 +58103,7 @@
         <v>2090</v>
       </c>
       <c r="AG45" t="s">
-        <v>889</v>
+        <v>2045</v>
       </c>
       <c r="AW45" t="s">
         <v>525</v>
@@ -58114,7 +58114,7 @@
         <v>2091</v>
       </c>
       <c r="AG46" t="s">
-        <v>643</v>
+        <v>2071</v>
       </c>
       <c r="AW46" t="s">
         <v>590</v>
@@ -58125,7 +58125,7 @@
         <v>782</v>
       </c>
       <c r="AG47" t="s">
-        <v>962</v>
+        <v>2073</v>
       </c>
       <c r="AW47" t="s">
         <v>1266</v>
@@ -58136,7 +58136,7 @@
         <v>1843</v>
       </c>
       <c r="AG48" t="s">
-        <v>606</v>
+        <v>2075</v>
       </c>
       <c r="AW48" t="s">
         <v>927</v>
@@ -58147,7 +58147,7 @@
         <v>962</v>
       </c>
       <c r="AG49" t="s">
-        <v>1047</v>
+        <v>636</v>
       </c>
       <c r="AW49" t="s">
         <v>951</v>
@@ -58158,7 +58158,7 @@
         <v>1827</v>
       </c>
       <c r="AG50" t="s">
-        <v>1821</v>
+        <v>1827</v>
       </c>
       <c r="AW50" t="s">
         <v>553</v>
@@ -58169,7 +58169,7 @@
         <v>235</v>
       </c>
       <c r="AG51" t="s">
-        <v>1486</v>
+        <v>2101</v>
       </c>
       <c r="AW51" t="s">
         <v>2092</v>
@@ -58180,7 +58180,7 @@
         <v>2093</v>
       </c>
       <c r="AG52" t="s">
-        <v>1513</v>
+        <v>2093</v>
       </c>
       <c r="AW52" t="s">
         <v>2025</v>
@@ -58191,7 +58191,7 @@
         <v>2204</v>
       </c>
       <c r="AG53" t="s">
-        <v>2090</v>
+        <v>1944</v>
       </c>
       <c r="AW53" t="s">
         <v>2094</v>
@@ -58199,7 +58199,7 @@
     </row>
     <row r="54" spans="15:49">
       <c r="AG54" t="s">
-        <v>761</v>
+        <v>1945</v>
       </c>
       <c r="AW54" t="s">
         <v>1047</v>
@@ -58207,7 +58207,7 @@
     </row>
     <row r="55" spans="15:49">
       <c r="AG55" t="s">
-        <v>2095</v>
+        <v>1843</v>
       </c>
       <c r="AW55" t="s">
         <v>977</v>
@@ -58215,7 +58215,7 @@
     </row>
     <row r="56" spans="15:49">
       <c r="AG56" t="s">
-        <v>2096</v>
+        <v>271</v>
       </c>
       <c r="AW56" t="s">
         <v>235</v>
@@ -58223,7 +58223,7 @@
     </row>
     <row r="57" spans="15:49">
       <c r="AG57" t="s">
-        <v>2097</v>
+        <v>2076</v>
       </c>
       <c r="AW57" t="s">
         <v>271</v>
@@ -58231,65 +58231,68 @@
     </row>
     <row r="58" spans="15:49">
       <c r="AG58" t="s">
-        <v>2098</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="59" spans="15:49">
       <c r="AG59" t="s">
-        <v>2099</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="60" spans="15:49">
       <c r="AG60" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="61" spans="15:49">
       <c r="AG61" t="s">
-        <v>1843</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="62" spans="15:49">
       <c r="AG62" t="s">
-        <v>1944</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="63" spans="15:49">
       <c r="AG63" t="s">
-        <v>1945</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="64" spans="15:49">
       <c r="AG64" t="s">
-        <v>1827</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="65" spans="33:33">
       <c r="AG65" t="s">
-        <v>2101</v>
+        <v>761</v>
       </c>
     </row>
     <row r="66" spans="33:33">
       <c r="AG66" t="s">
-        <v>235</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="67" spans="33:33">
       <c r="AG67" t="s">
-        <v>2093</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="68" spans="33:33">
       <c r="AG68" t="s">
-        <v>2102</v>
+        <v>366</v>
       </c>
     </row>
     <row r="69" spans="33:33">
       <c r="AG69" t="s">
-        <v>2205</v>
+        <v>1553</v>
       </c>
     </row>
   </sheetData>
+  <sortState ref="AG3:AG69">
+    <sortCondition ref="AG3"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -63637,10 +63640,10 @@
       <c r="C1" s="17" t="s">
         <v>2145</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="35" t="s">
         <v>2146</v>
       </c>
-      <c r="G1" s="32"/>
+      <c r="G1" s="35"/>
       <c r="H1" s="17" t="s">
         <v>2147</v>
       </c>
